--- a/copa_copilot_datos.xlsx
+++ b/copa_copilot_datos.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://controlesempresarialesltda-my.sharepoint.com/personal/jriverat_coem_co/Documents/Escritorio/VsCode/Copa_Copilot_BaseCode/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://controlesempresarialesltda-my.sharepoint.com/personal/marango_coem_co/Documents/GitHub/COEM/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="285" documentId="11_7B0F6A10CFB5B9B3AED9E795B9A4719BFA1CF949" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1668ECC0-5FBB-447D-9B3B-D00AF9C623DC}"/>
+  <xr:revisionPtr revIDLastSave="288" documentId="11_7B0F6A10CFB5B9B3AED9E795B9A4719BFA1CF949" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9FBE25CD-B34B-4BB6-AFD6-B5E3220C3AFE}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView minimized="1" xWindow="24" yWindow="24" windowWidth="23016" windowHeight="12216" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Copa Copilot" sheetId="1" r:id="rId1"/>
@@ -76,19 +76,19 @@
     <t>Eliminado</t>
   </si>
   <si>
-    <t>Equipo 1</t>
-  </si>
-  <si>
-    <t>Equipo 2</t>
-  </si>
-  <si>
-    <t>Equipo 3</t>
-  </si>
-  <si>
     <t>Equipo 4</t>
   </si>
   <si>
     <t>Equipo 5</t>
+  </si>
+  <si>
+    <t>Romy Mendoza</t>
+  </si>
+  <si>
+    <t>William Correa</t>
+  </si>
+  <si>
+    <t>Jenifer Rodriguez</t>
   </si>
 </sst>
 </file>
@@ -483,7 +483,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:F6"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="6" customWidth="1"/>
     <col min="2" max="2" width="16" customWidth="1"/>
@@ -493,7 +493,7 @@
     <col min="6" max="6" width="16" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -513,12 +513,12 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A2" s="2">
         <v>1</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C2" s="2">
         <v>0</v>
@@ -533,12 +533,12 @@
         <v>6</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A3" s="2">
         <v>2</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="C3" s="2">
         <v>0</v>
@@ -553,12 +553,12 @@
         <v>6</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A4" s="2">
         <v>3</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C4" s="2">
         <v>0</v>
@@ -573,12 +573,12 @@
         <v>6</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A5" s="2">
         <v>4</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="C5" s="2">
         <v>0</v>
@@ -593,12 +593,12 @@
         <v>6</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A6" s="2">
         <v>5</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="C6" s="2">
         <v>0</v>
@@ -634,29 +634,29 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:F8"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="10.5703125" customWidth="1"/>
-    <col min="2" max="2" width="9.85546875" customWidth="1"/>
-    <col min="3" max="3" width="14.5703125" customWidth="1"/>
-    <col min="4" max="4" width="10.85546875" customWidth="1"/>
+    <col min="1" max="1" width="10.5546875" customWidth="1"/>
+    <col min="2" max="2" width="9.88671875" customWidth="1"/>
+    <col min="3" max="3" width="14.5546875" customWidth="1"/>
+    <col min="4" max="4" width="10.88671875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>7</v>
       </c>
       <c r="B1" s="1" t="str">
         <f>'Copa Copilot'!B2</f>
-        <v>Equipo 1</v>
+        <v>Romy Mendoza</v>
       </c>
       <c r="C1" s="1" t="str">
         <f>'Copa Copilot'!B3</f>
-        <v>Equipo 2</v>
+        <v>William Correa</v>
       </c>
       <c r="D1" s="1" t="str">
         <f>'Copa Copilot'!B4</f>
-        <v>Equipo 3</v>
+        <v>Jenifer Rodriguez</v>
       </c>
       <c r="E1" s="1" t="str">
         <f>'Copa Copilot'!B5</f>
@@ -667,7 +667,7 @@
         <v>Equipo 5</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
         <v>8</v>
       </c>
@@ -687,7 +687,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
         <v>9</v>
       </c>
@@ -707,7 +707,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
         <v>10</v>
       </c>
@@ -727,7 +727,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
       <c r="D8" s="3"/>
     </row>
   </sheetData>
@@ -740,19 +740,19 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9E6B92DB-9C5C-437E-84B0-C727C5D5C893}">
   <dimension ref="A1:A3"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>12</v>
       </c>

--- a/copa_copilot_datos.xlsx
+++ b/copa_copilot_datos.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://controlesempresarialesltda-my.sharepoint.com/personal/marango_coem_co/Documents/GitHub/COEM/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="288" documentId="11_7B0F6A10CFB5B9B3AED9E795B9A4719BFA1CF949" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9FBE25CD-B34B-4BB6-AFD6-B5E3220C3AFE}"/>
+  <xr:revisionPtr revIDLastSave="313" documentId="11_7B0F6A10CFB5B9B3AED9E795B9A4719BFA1CF949" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{AEEB76CE-35A5-43FC-9FEB-A9AA976DB2C0}"/>
   <bookViews>
-    <workbookView minimized="1" xWindow="24" yWindow="24" windowWidth="23016" windowHeight="12216" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Copa Copilot" sheetId="1" r:id="rId1"/>
@@ -35,23 +35,14 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="17">
   <si>
     <t>Pos</t>
   </si>
   <si>
-    <t>Area</t>
-  </si>
-  <si>
     <t>Usuarios_Activos_Pct</t>
   </si>
   <si>
-    <t>Interacciones</t>
-  </si>
-  <si>
-    <t>Goles</t>
-  </si>
-  <si>
     <t>Estado</t>
   </si>
   <si>
@@ -76,12 +67,6 @@
     <t>Eliminado</t>
   </si>
   <si>
-    <t>Equipo 4</t>
-  </si>
-  <si>
-    <t>Equipo 5</t>
-  </si>
-  <si>
     <t>Romy Mendoza</t>
   </si>
   <si>
@@ -89,13 +74,29 @@
   </si>
   <si>
     <t>Jenifer Rodriguez</t>
+  </si>
+  <si>
+    <t>Comercial</t>
+  </si>
+  <si>
+    <t>Oportunidades</t>
+  </si>
+  <si>
+    <t>Cuota</t>
+  </si>
+  <si>
+    <t>Sandra Echeverry</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5" x14ac:knownFonts="1">
+  <numFmts count="2">
+    <numFmt numFmtId="44" formatCode="_-&quot;$&quot;\ * #,##0.00_-;\-&quot;$&quot;\ * #,##0.00_-;_-&quot;$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="165" formatCode="_-&quot;$&quot;\ * #,##0_-;\-&quot;$&quot;\ * #,##0_-;_-&quot;$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
+  </numFmts>
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -126,6 +127,13 @@
     </font>
     <font>
       <sz val="8"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -168,10 +176,11 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="44" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -180,8 +189,12 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Moneda" xfId="1" builtinId="4"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -482,14 +495,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F6"/>
+  <dimension ref="A1:F5"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="6" customWidth="1"/>
     <col min="2" max="2" width="16" customWidth="1"/>
     <col min="3" max="3" width="22" customWidth="1"/>
     <col min="4" max="4" width="16" customWidth="1"/>
-    <col min="5" max="5" width="10" customWidth="1"/>
+    <col min="5" max="5" width="15.109375" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="16" customWidth="1"/>
   </cols>
   <sheetData>
@@ -498,19 +511,19 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="F1" s="1" t="s">
         <v>2</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>5</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.3">
@@ -518,19 +531,19 @@
         <v>1</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="C2" s="2">
-        <v>0</v>
-      </c>
-      <c r="D2" s="2">
-        <v>0</v>
+        <v>12</v>
+      </c>
+      <c r="D2" s="4">
+        <v>50000000</v>
       </c>
       <c r="E2" s="2">
-        <v>0</v>
+        <v>43</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.3">
@@ -538,19 +551,19 @@
         <v>2</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="C3" s="2">
-        <v>0</v>
-      </c>
-      <c r="D3" s="2">
-        <v>0</v>
+        <v>42</v>
+      </c>
+      <c r="D3" s="4">
+        <v>100000000</v>
       </c>
       <c r="E3" s="2">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.3">
@@ -558,19 +571,19 @@
         <v>3</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="C4" s="2">
-        <v>0</v>
-      </c>
-      <c r="D4" s="2">
-        <v>0</v>
+        <v>78</v>
+      </c>
+      <c r="D4" s="4">
+        <v>20000000</v>
       </c>
       <c r="E4" s="2">
-        <v>0</v>
+        <v>76</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.3">
@@ -578,39 +591,19 @@
         <v>4</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="C5" s="2">
-        <v>0</v>
-      </c>
-      <c r="D5" s="2">
-        <v>0</v>
+        <v>34</v>
+      </c>
+      <c r="D5" s="4">
+        <v>200000000</v>
       </c>
       <c r="E5" s="2">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A6" s="2">
-        <v>5</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="C6" s="2">
-        <v>0</v>
-      </c>
-      <c r="D6" s="2">
-        <v>0</v>
-      </c>
-      <c r="E6" s="2">
-        <v>0</v>
-      </c>
-      <c r="F6" s="2" t="s">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
   </sheetData>
@@ -623,7 +616,7 @@
           <x14:formula1>
             <xm:f>Estados!$A$1:$A$3</xm:f>
           </x14:formula1>
-          <xm:sqref>F2:F6</xm:sqref>
+          <xm:sqref>F2:F5</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>
@@ -644,7 +637,7 @@
   <sheetData>
     <row r="1" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="B1" s="1" t="str">
         <f>'Copa Copilot'!B2</f>
@@ -660,16 +653,16 @@
       </c>
       <c r="E1" s="1" t="str">
         <f>'Copa Copilot'!B5</f>
-        <v>Equipo 4</v>
-      </c>
-      <c r="F1" s="1" t="str">
-        <f>'Copa Copilot'!B6</f>
-        <v>Equipo 5</v>
+        <v>Sandra Echeverry</v>
+      </c>
+      <c r="F1" s="1" t="e">
+        <f>'Copa Copilot'!#REF!</f>
+        <v>#REF!</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="B2" s="2">
         <v>0</v>
@@ -689,7 +682,7 @@
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="B3" s="2">
         <v>0</v>
@@ -709,7 +702,7 @@
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="B4" s="2">
         <v>0</v>
@@ -744,17 +737,17 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
     </row>
   </sheetData>

--- a/copa_copilot_datos.xlsx
+++ b/copa_copilot_datos.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://controlesempresarialesltda-my.sharepoint.com/personal/marango_coem_co/Documents/GitHub/COEM/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="313" documentId="11_7B0F6A10CFB5B9B3AED9E795B9A4719BFA1CF949" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{AEEB76CE-35A5-43FC-9FEB-A9AA976DB2C0}"/>
+  <xr:revisionPtr revIDLastSave="326" documentId="11_7B0F6A10CFB5B9B3AED9E795B9A4719BFA1CF949" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{038E965F-BADD-42E5-AEA8-D7C1BAA3FA3F}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView minimized="1" xWindow="24" yWindow="24" windowWidth="23016" windowHeight="12216" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Copa Copilot" sheetId="1" r:id="rId1"/>
@@ -64,9 +64,6 @@
     <t>Clasificado</t>
   </si>
   <si>
-    <t>Eliminado</t>
-  </si>
-  <si>
     <t>Romy Mendoza</t>
   </si>
   <si>
@@ -86,6 +83,9 @@
   </si>
   <si>
     <t>Sandra Echeverry</t>
+  </si>
+  <si>
+    <t>Valle de la oportunidad</t>
   </si>
 </sst>
 </file>
@@ -94,7 +94,7 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="2">
     <numFmt numFmtId="44" formatCode="_-&quot;$&quot;\ * #,##0.00_-;\-&quot;$&quot;\ * #,##0.00_-;_-&quot;$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
-    <numFmt numFmtId="165" formatCode="_-&quot;$&quot;\ * #,##0_-;\-&quot;$&quot;\ * #,##0_-;_-&quot;$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="164" formatCode="_-&quot;$&quot;\ * #,##0_-;\-&quot;$&quot;\ * #,##0_-;_-&quot;$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
   </numFmts>
   <fonts count="6" x14ac:knownFonts="1">
     <font>
@@ -189,7 +189,7 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -503,7 +503,7 @@
     <col min="3" max="3" width="22" customWidth="1"/>
     <col min="4" max="4" width="16" customWidth="1"/>
     <col min="5" max="5" width="15.109375" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="16" customWidth="1"/>
+    <col min="6" max="6" width="20.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
@@ -511,16 +511,16 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>1</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F1" s="1" t="s">
         <v>2</v>
@@ -531,7 +531,7 @@
         <v>1</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C2" s="2">
         <v>12</v>
@@ -543,7 +543,7 @@
         <v>43</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>3</v>
+        <v>16</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.3">
@@ -551,7 +551,7 @@
         <v>2</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C3" s="2">
         <v>42</v>
@@ -563,7 +563,7 @@
         <v>23</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>3</v>
+        <v>8</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.3">
@@ -571,7 +571,7 @@
         <v>3</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C4" s="2">
         <v>78</v>
@@ -583,7 +583,7 @@
         <v>76</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>3</v>
+        <v>8</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.3">
@@ -591,7 +591,7 @@
         <v>4</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C5" s="2">
         <v>34</v>
@@ -630,9 +630,10 @@
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="10.5546875" customWidth="1"/>
-    <col min="2" max="2" width="9.88671875" customWidth="1"/>
-    <col min="3" max="3" width="14.5546875" customWidth="1"/>
-    <col min="4" max="4" width="10.88671875" customWidth="1"/>
+    <col min="2" max="2" width="15.44140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="14.88671875" bestFit="1" customWidth="1"/>
+    <col min="4" max="5" width="17.109375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="7" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
@@ -734,6 +735,9 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9E6B92DB-9C5C-437E-84B0-C727C5D5C893}">
   <dimension ref="A1:A3"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="19.88671875" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
@@ -747,7 +751,7 @@
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>9</v>
+        <v>16</v>
       </c>
     </row>
   </sheetData>

--- a/copa_copilot_datos.xlsx
+++ b/copa_copilot_datos.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://controlesempresarialesltda-my.sharepoint.com/personal/marango_coem_co/Documents/GitHub/COEM/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="326" documentId="11_7B0F6A10CFB5B9B3AED9E795B9A4719BFA1CF949" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{038E965F-BADD-42E5-AEA8-D7C1BAA3FA3F}"/>
+  <xr:revisionPtr revIDLastSave="349" documentId="11_7B0F6A10CFB5B9B3AED9E795B9A4719BFA1CF949" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6A2A0663-6B70-44AF-A760-048A485CAE6F}"/>
   <bookViews>
     <workbookView minimized="1" xWindow="24" yWindow="24" windowWidth="23016" windowHeight="12216" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,17 +35,11 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="25">
   <si>
     <t>Pos</t>
   </si>
   <si>
-    <t>Usuarios_Activos_Pct</t>
-  </si>
-  <si>
-    <t>Estado</t>
-  </si>
-  <si>
     <t>En Carrera</t>
   </si>
   <si>
@@ -64,39 +58,68 @@
     <t>Clasificado</t>
   </si>
   <si>
-    <t>Romy Mendoza</t>
-  </si>
-  <si>
-    <t>William Correa</t>
-  </si>
-  <si>
-    <t>Jenifer Rodriguez</t>
-  </si>
-  <si>
     <t>Comercial</t>
   </si>
   <si>
-    <t>Oportunidades</t>
-  </si>
-  <si>
     <t>Cuota</t>
   </si>
   <si>
-    <t>Sandra Echeverry</t>
-  </si>
-  <si>
     <t>Valle de la oportunidad</t>
+  </si>
+  <si>
+    <t>ECHEVERRY SANDRA</t>
+  </si>
+  <si>
+    <t>RODRIGUEZ CONTRERAS JENIFFER LORENA</t>
+  </si>
+  <si>
+    <t>ESPINOSA ORTIZ DEISON FERNANDO</t>
+  </si>
+  <si>
+    <t>MENDOZA SALAZAR ROMY VALENTINA</t>
+  </si>
+  <si>
+    <t>NN OCCIDE_SMC_001 1</t>
+  </si>
+  <si>
+    <t>COLLAZOS PRIETO JUAN FELIPE</t>
+  </si>
+  <si>
+    <t>NN OCCIDE_SMC_001 2</t>
+  </si>
+  <si>
+    <t>NN OCCIDE_CORPO_001 2</t>
+  </si>
+  <si>
+    <t>CORREA CORPUS WILLIAM ERNESTO</t>
+  </si>
+  <si>
+    <t>NN OCCIDE_ENTER_001</t>
+  </si>
+  <si>
+    <t>CHARRY OCHOA VIVIANA ANDREA</t>
+  </si>
+  <si>
+    <t>% de cumplimiento</t>
+  </si>
+  <si>
+    <t>Utilidad Bruta</t>
+  </si>
+  <si>
+    <t>Compromiso</t>
+  </si>
+  <si>
+    <t>Falta</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="2">
-    <numFmt numFmtId="44" formatCode="_-&quot;$&quot;\ * #,##0.00_-;\-&quot;$&quot;\ * #,##0.00_-;_-&quot;$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
-    <numFmt numFmtId="164" formatCode="_-&quot;$&quot;\ * #,##0_-;\-&quot;$&quot;\ * #,##0_-;_-&quot;$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
+  <numFmts count="1">
+    <numFmt numFmtId="6" formatCode="&quot;$&quot;\ #,##0;[Red]\-&quot;$&quot;\ #,##0"/>
   </numFmts>
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="10" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -132,14 +155,39 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <b/>
       <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FF000000"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color rgb="FFFFD700"/>
+      <name val="Calibri"/>
+      <family val="2"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -151,8 +199,32 @@
         <fgColor rgb="FF1A472A"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD9E082"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF63BE7B"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB84"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF8696B"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -175,12 +247,22 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFFFD700"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFFFD700"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="44" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -189,12 +271,39 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="6" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="7" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="7" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="10" fontId="7" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="6" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="7" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="2">
-    <cellStyle name="Moneda" xfId="1" builtinId="4"/>
+  <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -495,132 +604,290 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F5"/>
+  <dimension ref="A1:G12"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="6" customWidth="1"/>
-    <col min="2" max="2" width="16" customWidth="1"/>
-    <col min="3" max="3" width="22" customWidth="1"/>
-    <col min="4" max="4" width="16" customWidth="1"/>
-    <col min="5" max="5" width="15.109375" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="20.6640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="36.88671875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="19.109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.5546875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.109375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12.5546875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="13.21875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="D1" s="13" t="s">
+        <v>8</v>
+      </c>
+      <c r="E1" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="F1" s="13" t="s">
+        <v>23</v>
+      </c>
+      <c r="G1" s="14" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A2" s="4">
+        <v>1</v>
+      </c>
+      <c r="B2" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C2" s="7">
+        <v>8.5900000000000004E-2</v>
+      </c>
+      <c r="D2" s="6">
+        <v>79166667</v>
+      </c>
+      <c r="E2" s="6">
+        <v>6796610</v>
+      </c>
+      <c r="F2" s="6">
+        <v>12900000</v>
+      </c>
+      <c r="G2" s="11">
+        <v>-6103390</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A3" s="4">
+        <v>2</v>
+      </c>
+      <c r="B3" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C3" s="8">
+        <v>0.3478</v>
+      </c>
+      <c r="D3" s="6">
+        <v>16666667</v>
+      </c>
+      <c r="E3" s="6">
+        <v>5797076</v>
+      </c>
+      <c r="F3" s="6">
+        <v>6400000</v>
+      </c>
+      <c r="G3" s="11">
+        <v>-602924</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A4" s="4">
+        <v>3</v>
+      </c>
+      <c r="B4" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="C1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="D1" s="1" t="s">
+      <c r="C4" s="9"/>
+      <c r="D4" s="6">
+        <v>0</v>
+      </c>
+      <c r="E4" s="6">
+        <v>67217</v>
+      </c>
+      <c r="F4" s="6">
+        <v>67217</v>
+      </c>
+      <c r="G4" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A5" s="4">
+        <v>4</v>
+      </c>
+      <c r="B5" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C5" s="10">
+        <v>2.9999999999999997E-4</v>
+      </c>
+      <c r="D5" s="6">
+        <v>79166667</v>
+      </c>
+      <c r="E5" s="6">
+        <v>26868</v>
+      </c>
+      <c r="F5" s="6">
+        <v>30259000</v>
+      </c>
+      <c r="G5" s="11">
+        <v>-30232132</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A6" s="4">
+        <v>5</v>
+      </c>
+      <c r="B6" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="E1" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A2" s="2">
-        <v>1</v>
-      </c>
-      <c r="B2" s="2" t="s">
+      <c r="C6" s="12">
+        <v>0</v>
+      </c>
+      <c r="D6" s="6">
+        <v>25000000</v>
+      </c>
+      <c r="E6" s="6">
+        <v>0</v>
+      </c>
+      <c r="F6" s="6">
+        <v>0</v>
+      </c>
+      <c r="G6" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A7" s="4">
+        <v>6</v>
+      </c>
+      <c r="B7" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="C7" s="9"/>
+      <c r="D7" s="6">
+        <v>0</v>
+      </c>
+      <c r="E7" s="6">
+        <v>0</v>
+      </c>
+      <c r="F7" s="6">
+        <v>0</v>
+      </c>
+      <c r="G7" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A8" s="4">
+        <v>7</v>
+      </c>
+      <c r="B8" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="C8" s="9"/>
+      <c r="D8" s="6">
+        <v>0</v>
+      </c>
+      <c r="E8" s="6">
+        <v>0</v>
+      </c>
+      <c r="F8" s="6">
+        <v>0</v>
+      </c>
+      <c r="G8" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A9" s="4">
+        <v>8</v>
+      </c>
+      <c r="B9" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="C9" s="12">
+        <v>0</v>
+      </c>
+      <c r="D9" s="6">
+        <v>58333333</v>
+      </c>
+      <c r="E9" s="6">
+        <v>0</v>
+      </c>
+      <c r="F9" s="6">
+        <v>0</v>
+      </c>
+      <c r="G9" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A10" s="4">
         <v>9</v>
       </c>
-      <c r="C2" s="2">
-        <v>12</v>
-      </c>
-      <c r="D2" s="4">
-        <v>50000000</v>
-      </c>
-      <c r="E2" s="2">
-        <v>43</v>
-      </c>
-      <c r="F2" s="2" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A3" s="2">
-        <v>2</v>
-      </c>
-      <c r="B3" s="2" t="s">
+      <c r="B10" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="C10" s="12">
+        <v>0</v>
+      </c>
+      <c r="D10" s="6">
+        <v>54166667</v>
+      </c>
+      <c r="E10" s="6">
+        <v>0</v>
+      </c>
+      <c r="F10" s="6">
+        <v>129000000</v>
+      </c>
+      <c r="G10" s="11">
+        <v>-129000000</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A11" s="4">
         <v>10</v>
       </c>
-      <c r="C3" s="2">
-        <v>42</v>
-      </c>
-      <c r="D3" s="4">
-        <v>100000000</v>
-      </c>
-      <c r="E3" s="2">
-        <v>23</v>
-      </c>
-      <c r="F3" s="2" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A4" s="2">
-        <v>3</v>
-      </c>
-      <c r="B4" s="2" t="s">
+      <c r="B11" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="C11" s="12">
+        <v>0</v>
+      </c>
+      <c r="D11" s="6">
+        <v>79166667</v>
+      </c>
+      <c r="E11" s="6">
+        <v>0</v>
+      </c>
+      <c r="F11" s="6">
+        <v>0</v>
+      </c>
+      <c r="G11" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A12" s="4">
         <v>11</v>
       </c>
-      <c r="C4" s="2">
-        <v>78</v>
-      </c>
-      <c r="D4" s="4">
-        <v>20000000</v>
-      </c>
-      <c r="E4" s="2">
-        <v>76</v>
-      </c>
-      <c r="F4" s="2" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A5" s="2">
-        <v>4</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="C5" s="2">
-        <v>34</v>
-      </c>
-      <c r="D5" s="4">
-        <v>200000000</v>
-      </c>
-      <c r="E5" s="2">
-        <v>14</v>
-      </c>
-      <c r="F5" s="2" t="s">
-        <v>3</v>
+      <c r="B12" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="C12" s="9"/>
+      <c r="D12" s="6">
+        <v>0</v>
+      </c>
+      <c r="E12" s="11">
+        <v>-112956</v>
+      </c>
+      <c r="F12" s="6">
+        <v>0</v>
+      </c>
+      <c r="G12" s="11">
+        <v>-112956</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
-      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1">
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{964AB81A-23CD-4DFB-907A-57AEFED3C48D}">
-          <x14:formula1>
-            <xm:f>Estados!$A$1:$A$3</xm:f>
-          </x14:formula1>
-          <xm:sqref>F2:F5</xm:sqref>
-        </x14:dataValidation>
-      </x14:dataValidations>
-    </ext>
-  </extLst>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -638,23 +905,23 @@
   <sheetData>
     <row r="1" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="B1" s="1" t="str">
         <f>'Copa Copilot'!B2</f>
-        <v>Romy Mendoza</v>
+        <v>ECHEVERRY SANDRA</v>
       </c>
       <c r="C1" s="1" t="str">
         <f>'Copa Copilot'!B3</f>
-        <v>William Correa</v>
+        <v>RODRIGUEZ CONTRERAS JENIFFER LORENA</v>
       </c>
       <c r="D1" s="1" t="str">
         <f>'Copa Copilot'!B4</f>
-        <v>Jenifer Rodriguez</v>
+        <v>ESPINOSA ORTIZ DEISON FERNANDO</v>
       </c>
       <c r="E1" s="1" t="str">
         <f>'Copa Copilot'!B5</f>
-        <v>Sandra Echeverry</v>
+        <v>MENDOZA SALAZAR ROMY VALENTINA</v>
       </c>
       <c r="F1" s="1" t="e">
         <f>'Copa Copilot'!#REF!</f>
@@ -663,7 +930,7 @@
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="B2" s="2">
         <v>0</v>
@@ -683,7 +950,7 @@
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="B3" s="2">
         <v>0</v>
@@ -703,7 +970,7 @@
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="B4" s="2">
         <v>0</v>
@@ -741,17 +1008,17 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
     </row>
   </sheetData>

--- a/copa_copilot_datos.xlsx
+++ b/copa_copilot_datos.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30317"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://controlesempresarialesltda-my.sharepoint.com/personal/marango_coem_co/Documents/GitHub/COEM/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="349" documentId="11_7B0F6A10CFB5B9B3AED9E795B9A4719BFA1CF949" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6A2A0663-6B70-44AF-A760-048A485CAE6F}"/>
+  <xr:revisionPtr revIDLastSave="358" documentId="11_7B0F6A10CFB5B9B3AED9E795B9A4719BFA1CF949" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{AE31D637-6937-43EA-95D8-F1497F73878D}"/>
   <bookViews>
     <workbookView minimized="1" xWindow="24" yWindow="24" windowWidth="23016" windowHeight="12216" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -17,8 +17,11 @@
     <sheet name="Actividad Semanal" sheetId="2" r:id="rId2"/>
     <sheet name="Estados" sheetId="3" r:id="rId3"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="191028"/>
   <extLst>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
+      <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
         <xcalcf:feature name="microsoft.com:RD"/>
@@ -35,91 +38,151 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="69" uniqueCount="46">
   <si>
     <t>Pos</t>
   </si>
   <si>
+    <t>Comercial</t>
+  </si>
+  <si>
+    <t>% de cumplimiento</t>
+  </si>
+  <si>
+    <t>Cuota</t>
+  </si>
+  <si>
+    <t>Utilidad Bruta</t>
+  </si>
+  <si>
+    <t>Compromiso</t>
+  </si>
+  <si>
+    <t>Falta</t>
+  </si>
+  <si>
+    <t>ECHEVERRY SANDRA</t>
+  </si>
+  <si>
+    <t>$79.166.667</t>
+  </si>
+  <si>
+    <t>$ 10.812.168</t>
+  </si>
+  <si>
+    <t>$10.812.168</t>
+  </si>
+  <si>
+    <t>-$ 0</t>
+  </si>
+  <si>
+    <t>MENDOZA SALAZAR ROMY VALENTINA</t>
+  </si>
+  <si>
+    <t>$ 7.191.749</t>
+  </si>
+  <si>
+    <t>$35.000.000</t>
+  </si>
+  <si>
+    <t>-$ 27.808.251</t>
+  </si>
+  <si>
+    <t>RODRIGUEZ CONTRERAS JENIFFER LORENA</t>
+  </si>
+  <si>
+    <t>$16.666.667</t>
+  </si>
+  <si>
+    <t>$ 6.309.992</t>
+  </si>
+  <si>
+    <t>$7.500.000</t>
+  </si>
+  <si>
+    <t>-$ 1.190.008</t>
+  </si>
+  <si>
+    <t>ESPINOSA ORTIZ DEISON FERNANDO</t>
+  </si>
+  <si>
+    <t>$0</t>
+  </si>
+  <si>
+    <t>$ 67.217</t>
+  </si>
+  <si>
+    <t>$67.217</t>
+  </si>
+  <si>
+    <t>$ 0</t>
+  </si>
+  <si>
+    <t>NN OCCIDE_SMC_001 1</t>
+  </si>
+  <si>
+    <t>$25.000.000</t>
+  </si>
+  <si>
+    <t>NN OCCIDE_ENTER_001 1</t>
+  </si>
+  <si>
+    <t>NN OCCIDE_SMC_001 2</t>
+  </si>
+  <si>
+    <t>COLLAZOS PRIETO JUAN FELIPE</t>
+  </si>
+  <si>
+    <t>CORREA CORPUS WILLIAM ERNESTO</t>
+  </si>
+  <si>
+    <t>$54.166.667</t>
+  </si>
+  <si>
+    <t>$119.500.000</t>
+  </si>
+  <si>
+    <t>-$ 119.500.000</t>
+  </si>
+  <si>
+    <t>NN OCCIDE_CORPO_001 1</t>
+  </si>
+  <si>
+    <t>$58.333.333</t>
+  </si>
+  <si>
+    <t>CHARRY OCHOA VIVIANA ANDREA</t>
+  </si>
+  <si>
+    <t>-$ 112.956</t>
+  </si>
+  <si>
+    <t>Semana</t>
+  </si>
+  <si>
+    <t>Semana 1</t>
+  </si>
+  <si>
+    <t>Semana 2</t>
+  </si>
+  <si>
+    <t>Semana 3</t>
+  </si>
+  <si>
+    <t>Clasificado</t>
+  </si>
+  <si>
     <t>En Carrera</t>
   </si>
   <si>
-    <t>Semana</t>
-  </si>
-  <si>
-    <t>Semana 1</t>
-  </si>
-  <si>
-    <t>Semana 2</t>
-  </si>
-  <si>
-    <t>Semana 3</t>
-  </si>
-  <si>
-    <t>Clasificado</t>
-  </si>
-  <si>
-    <t>Comercial</t>
-  </si>
-  <si>
-    <t>Cuota</t>
-  </si>
-  <si>
     <t>Valle de la oportunidad</t>
-  </si>
-  <si>
-    <t>ECHEVERRY SANDRA</t>
-  </si>
-  <si>
-    <t>RODRIGUEZ CONTRERAS JENIFFER LORENA</t>
-  </si>
-  <si>
-    <t>ESPINOSA ORTIZ DEISON FERNANDO</t>
-  </si>
-  <si>
-    <t>MENDOZA SALAZAR ROMY VALENTINA</t>
-  </si>
-  <si>
-    <t>NN OCCIDE_SMC_001 1</t>
-  </si>
-  <si>
-    <t>COLLAZOS PRIETO JUAN FELIPE</t>
-  </si>
-  <si>
-    <t>NN OCCIDE_SMC_001 2</t>
-  </si>
-  <si>
-    <t>NN OCCIDE_CORPO_001 2</t>
-  </si>
-  <si>
-    <t>CORREA CORPUS WILLIAM ERNESTO</t>
-  </si>
-  <si>
-    <t>NN OCCIDE_ENTER_001</t>
-  </si>
-  <si>
-    <t>CHARRY OCHOA VIVIANA ANDREA</t>
-  </si>
-  <si>
-    <t>% de cumplimiento</t>
-  </si>
-  <si>
-    <t>Utilidad Bruta</t>
-  </si>
-  <si>
-    <t>Compromiso</t>
-  </si>
-  <si>
-    <t>Falta</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="1">
-    <numFmt numFmtId="6" formatCode="&quot;$&quot;\ #,##0;[Red]\-&quot;$&quot;\ #,##0"/>
-  </numFmts>
-  <fonts count="10" x14ac:knownFonts="1">
+  <fonts count="9">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -153,12 +216,6 @@
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color theme="1"/>
-      <name val="Times New Roman"/>
-      <family val="1"/>
     </font>
     <font>
       <b/>
@@ -201,26 +258,26 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFD9E082"/>
-        <bgColor indexed="64"/>
+        <fgColor rgb="FFD0DE82"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE5E483"/>
+        <bgColor rgb="FF000000"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF63BE7B"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB84"/>
-        <bgColor indexed="64"/>
+        <bgColor rgb="FF000000"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFF8696B"/>
-        <bgColor indexed="64"/>
+        <bgColor rgb="FF000000"/>
       </patternFill>
     </fill>
   </fills>
@@ -262,7 +319,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -271,37 +328,21 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="6" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="10" fontId="7" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="10" fontId="7" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="10" fontId="7" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="6" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="10" fontId="7" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="10" fontId="6" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="10" fontId="6" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="10" fontId="6" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="10" fontId="6" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -605,283 +646,283 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:G12"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="14.45"/>
   <cols>
     <col min="1" max="1" width="6" customWidth="1"/>
-    <col min="2" max="2" width="36.88671875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="19.109375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.5546875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.109375" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="12.5546875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="13.21875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="36.85546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="19.140625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.5703125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.140625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="15" customWidth="1"/>
+    <col min="7" max="7" width="13.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7" ht="15.6">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C1" s="13" t="s">
-        <v>21</v>
-      </c>
-      <c r="D1" s="13" t="s">
-        <v>8</v>
-      </c>
-      <c r="E1" s="13" t="s">
-        <v>22</v>
-      </c>
-      <c r="F1" s="13" t="s">
-        <v>23</v>
-      </c>
-      <c r="G1" s="14" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
+        <v>1</v>
+      </c>
+      <c r="C1" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="6" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" ht="15">
       <c r="A2" s="4">
         <v>1</v>
       </c>
-      <c r="B2" s="5" t="s">
+      <c r="B2" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C2" s="8">
+        <v>0.1366</v>
+      </c>
+      <c r="D2" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E2" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="F2" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="C2" s="7">
-        <v>8.5900000000000004E-2</v>
-      </c>
-      <c r="D2" s="6">
-        <v>79166667</v>
-      </c>
-      <c r="E2" s="6">
-        <v>6796610</v>
-      </c>
-      <c r="F2" s="6">
-        <v>12900000</v>
-      </c>
-      <c r="G2" s="11">
-        <v>-6103390</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="G2" s="10" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" ht="15">
       <c r="A3" s="4">
         <v>2</v>
       </c>
-      <c r="B3" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C3" s="8">
-        <v>0.3478</v>
-      </c>
-      <c r="D3" s="6">
-        <v>16666667</v>
-      </c>
-      <c r="E3" s="6">
-        <v>5797076</v>
-      </c>
-      <c r="F3" s="6">
-        <v>6400000</v>
-      </c>
-      <c r="G3" s="11">
-        <v>-602924</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="B3" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="C3" s="9">
+        <v>9.0800000000000006E-2</v>
+      </c>
+      <c r="D3" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E3" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="F3" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="G3" s="10" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" ht="15">
       <c r="A4" s="4">
         <v>3</v>
       </c>
-      <c r="B4" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="C4" s="9"/>
-      <c r="D4" s="6">
-        <v>0</v>
-      </c>
-      <c r="E4" s="6">
-        <v>67217</v>
-      </c>
-      <c r="F4" s="6">
-        <v>67217</v>
-      </c>
-      <c r="G4" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="B4" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="C4" s="11">
+        <v>0.37859999999999999</v>
+      </c>
+      <c r="D4" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="E4" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="F4" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="G4" s="10" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" ht="15">
       <c r="A5" s="4">
         <v>4</v>
       </c>
-      <c r="B5" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="C5" s="10">
-        <v>2.9999999999999997E-4</v>
-      </c>
-      <c r="D5" s="6">
-        <v>79166667</v>
-      </c>
-      <c r="E5" s="6">
-        <v>26868</v>
-      </c>
-      <c r="F5" s="6">
-        <v>30259000</v>
-      </c>
-      <c r="G5" s="11">
-        <v>-30232132</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="B5" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="C5" s="7"/>
+      <c r="D5" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="E5" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="F5" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="G5" s="7" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" ht="15">
       <c r="A6" s="4">
         <v>5</v>
       </c>
-      <c r="B6" s="5" t="s">
-        <v>14</v>
+      <c r="B6" s="7" t="s">
+        <v>26</v>
       </c>
       <c r="C6" s="12">
         <v>0</v>
       </c>
-      <c r="D6" s="6">
-        <v>25000000</v>
-      </c>
-      <c r="E6" s="6">
-        <v>0</v>
-      </c>
-      <c r="F6" s="6">
-        <v>0</v>
-      </c>
-      <c r="G6" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="D6" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="E6" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="F6" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="G6" s="7" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" ht="15">
       <c r="A7" s="4">
         <v>6</v>
       </c>
-      <c r="B7" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="C7" s="9"/>
-      <c r="D7" s="6">
-        <v>0</v>
-      </c>
-      <c r="E7" s="6">
-        <v>0</v>
-      </c>
-      <c r="F7" s="6">
-        <v>0</v>
-      </c>
-      <c r="G7" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="B7" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="C7" s="12">
+        <v>0</v>
+      </c>
+      <c r="D7" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E7" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="F7" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="G7" s="7" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" ht="15">
       <c r="A8" s="4">
         <v>7</v>
       </c>
-      <c r="B8" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="C8" s="9"/>
-      <c r="D8" s="6">
-        <v>0</v>
-      </c>
-      <c r="E8" s="6">
-        <v>0</v>
-      </c>
-      <c r="F8" s="6">
-        <v>0</v>
-      </c>
-      <c r="G8" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="B8" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="C8" s="7"/>
+      <c r="D8" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="E8" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="F8" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="G8" s="7" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" ht="15">
       <c r="A9" s="4">
         <v>8</v>
       </c>
-      <c r="B9" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="C9" s="12">
-        <v>0</v>
-      </c>
-      <c r="D9" s="6">
-        <v>58333333</v>
-      </c>
-      <c r="E9" s="6">
-        <v>0</v>
-      </c>
-      <c r="F9" s="6">
-        <v>0</v>
-      </c>
-      <c r="G9" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="B9" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="C9" s="7"/>
+      <c r="D9" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="E9" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="F9" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="G9" s="7" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" ht="15">
       <c r="A10" s="4">
         <v>9</v>
       </c>
-      <c r="B10" s="5" t="s">
-        <v>18</v>
+      <c r="B10" s="7" t="s">
+        <v>31</v>
       </c>
       <c r="C10" s="12">
         <v>0</v>
       </c>
-      <c r="D10" s="6">
-        <v>54166667</v>
-      </c>
-      <c r="E10" s="6">
-        <v>0</v>
-      </c>
-      <c r="F10" s="6">
-        <v>129000000</v>
-      </c>
-      <c r="G10" s="11">
-        <v>-129000000</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="D10" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="E10" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="F10" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="G10" s="10" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" ht="15">
       <c r="A11" s="4">
         <v>10</v>
       </c>
-      <c r="B11" s="5" t="s">
-        <v>19</v>
+      <c r="B11" s="7" t="s">
+        <v>35</v>
       </c>
       <c r="C11" s="12">
         <v>0</v>
       </c>
-      <c r="D11" s="6">
-        <v>79166667</v>
-      </c>
-      <c r="E11" s="6">
-        <v>0</v>
-      </c>
-      <c r="F11" s="6">
-        <v>0</v>
-      </c>
-      <c r="G11" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="D11" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="E11" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="F11" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="G11" s="7" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" ht="15">
       <c r="A12" s="4">
         <v>11</v>
       </c>
-      <c r="B12" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="C12" s="9"/>
-      <c r="D12" s="6">
-        <v>0</v>
-      </c>
-      <c r="E12" s="11">
-        <v>-112956</v>
-      </c>
-      <c r="F12" s="6">
-        <v>0</v>
-      </c>
-      <c r="G12" s="11">
-        <v>-112956</v>
+      <c r="B12" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="C12" s="7"/>
+      <c r="D12" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="E12" s="10" t="s">
+        <v>38</v>
+      </c>
+      <c r="F12" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="G12" s="10" t="s">
+        <v>38</v>
       </c>
     </row>
   </sheetData>
@@ -894,18 +935,18 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:F8"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="14.45"/>
   <cols>
-    <col min="1" max="1" width="10.5546875" customWidth="1"/>
-    <col min="2" max="2" width="15.44140625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="14.88671875" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="17.109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="10.5703125" customWidth="1"/>
+    <col min="2" max="2" width="15.42578125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="14.85546875" bestFit="1" customWidth="1"/>
+    <col min="4" max="5" width="17.140625" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="7" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:6" ht="15.6">
       <c r="A1" s="1" t="s">
-        <v>2</v>
+        <v>39</v>
       </c>
       <c r="B1" s="1" t="str">
         <f>'Copa Copilot'!B2</f>
@@ -913,24 +954,24 @@
       </c>
       <c r="C1" s="1" t="str">
         <f>'Copa Copilot'!B3</f>
-        <v>RODRIGUEZ CONTRERAS JENIFFER LORENA</v>
+        <v>MENDOZA SALAZAR ROMY VALENTINA</v>
       </c>
       <c r="D1" s="1" t="str">
         <f>'Copa Copilot'!B4</f>
-        <v>ESPINOSA ORTIZ DEISON FERNANDO</v>
+        <v>RODRIGUEZ CONTRERAS JENIFFER LORENA</v>
       </c>
       <c r="E1" s="1" t="str">
         <f>'Copa Copilot'!B5</f>
-        <v>MENDOZA SALAZAR ROMY VALENTINA</v>
+        <v>ESPINOSA ORTIZ DEISON FERNANDO</v>
       </c>
       <c r="F1" s="1" t="e">
         <f>'Copa Copilot'!#REF!</f>
         <v>#REF!</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:6">
       <c r="A2" s="2" t="s">
-        <v>3</v>
+        <v>40</v>
       </c>
       <c r="B2" s="2">
         <v>0</v>
@@ -948,9 +989,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:6">
       <c r="A3" s="2" t="s">
-        <v>4</v>
+        <v>41</v>
       </c>
       <c r="B3" s="2">
         <v>0</v>
@@ -968,9 +1009,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:6">
       <c r="A4" s="2" t="s">
-        <v>5</v>
+        <v>42</v>
       </c>
       <c r="B4" s="2">
         <v>0</v>
@@ -988,7 +1029,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:6">
       <c r="D8" s="3"/>
     </row>
   </sheetData>
@@ -1001,24 +1042,24 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9E6B92DB-9C5C-437E-84B0-C727C5D5C893}">
   <dimension ref="A1:A3"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="14.45"/>
   <cols>
-    <col min="1" max="1" width="19.88671875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="19.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:1">
       <c r="A1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1">
       <c r="A2" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.3">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1">
       <c r="A3" t="s">
-        <v>9</v>
+        <v>45</v>
       </c>
     </row>
   </sheetData>

--- a/copa_copilot_datos.xlsx
+++ b/copa_copilot_datos.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://controlesempresarialesltda-my.sharepoint.com/personal/marango_coem_co/Documents/GitHub/COEM/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="358" documentId="11_7B0F6A10CFB5B9B3AED9E795B9A4719BFA1CF949" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{AE31D637-6937-43EA-95D8-F1497F73878D}"/>
+  <xr:revisionPtr revIDLastSave="366" documentId="11_7B0F6A10CFB5B9B3AED9E795B9A4719BFA1CF949" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{026BEBDE-97EB-4247-B260-1D1B6C2A191D}"/>
   <bookViews>
     <workbookView minimized="1" xWindow="24" yWindow="24" windowWidth="23016" windowHeight="12216" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -337,12 +337,12 @@
     <xf numFmtId="0" fontId="8" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="10" fontId="6" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="10" fontId="6" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="10" fontId="6" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="10" fontId="6" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="10" fontId="6" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="10" fontId="6" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1"/>
+    <xf numFmtId="10" fontId="6" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="10" fontId="6" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>

--- a/copa_copilot_datos.xlsx
+++ b/copa_copilot_datos.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://controlesempresarialesltda-my.sharepoint.com/personal/marango_coem_co/Documents/GitHub/COEM/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="395" documentId="11_7B0F6A10CFB5B9B3AED9E795B9A4719BFA1CF949" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9D5C343D-6A74-4955-BB63-B7B3D1219DCB}"/>
+  <xr:revisionPtr revIDLastSave="409" documentId="11_7B0F6A10CFB5B9B3AED9E795B9A4719BFA1CF949" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6C087213-8B4B-4E89-BFC6-85113B3735C4}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="31">
   <si>
     <t>Pos</t>
   </si>
@@ -122,15 +122,22 @@
   </si>
   <si>
     <t>VALERO VELA LUZ EDIT</t>
+  </si>
+  <si>
+    <t>Gap</t>
+  </si>
+  <si>
+    <t>Total general</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="2">
+  <numFmts count="3">
     <numFmt numFmtId="6" formatCode="&quot;$&quot;\ #,##0;[Red]\-&quot;$&quot;\ #,##0"/>
     <numFmt numFmtId="169" formatCode="&quot;$&quot;#,##0"/>
+    <numFmt numFmtId="170" formatCode="&quot;$&quot;#,##0;[Red]\-&quot;$&quot;#,##0"/>
   </numFmts>
   <fonts count="7" x14ac:knownFonts="1">
     <font>
@@ -155,11 +162,13 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FF000000"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
@@ -180,7 +189,7 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -195,11 +204,17 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="4" tint="0.79998168889431442"/>
-        <bgColor theme="4" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="3" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="4">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -233,25 +248,16 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="thin">
-        <color theme="4" tint="0.39997558519241921"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="6" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -262,12 +268,21 @@
     <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="169" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="170" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="10" fontId="3" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="169" fontId="3" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="6" fontId="3" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="170" fontId="6" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -574,7 +589,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G10"/>
+  <dimension ref="A1:G12"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="6" customWidth="1"/>
@@ -582,8 +597,8 @@
     <col min="3" max="3" width="19.109375" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="11.5546875" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="14.109375" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="13" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.88671875" customWidth="1"/>
+    <col min="6" max="6" width="13.33203125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="12.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
@@ -613,204 +628,219 @@
       <c r="A2" s="2">
         <v>1</v>
       </c>
-      <c r="B2" s="8" t="s">
+      <c r="B2" s="7" t="s">
         <v>7</v>
       </c>
       <c r="C2" s="4">
         <v>0.42515786460001193</v>
       </c>
-      <c r="D2" s="9">
+      <c r="D2" s="8">
         <v>16666666.666666199</v>
       </c>
       <c r="E2" s="3">
         <v>7085964.4100000039</v>
       </c>
-      <c r="F2" s="7">
+      <c r="F2" s="3">
         <v>7500000</v>
       </c>
-      <c r="G2" s="7">
-        <v>9166666.6669999994</v>
+      <c r="G2" s="3">
+        <f>+F2-E2</f>
+        <v>414035.58999999613</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3" s="2">
         <v>2</v>
       </c>
-      <c r="B3" s="8" t="s">
+      <c r="B3" s="7" t="s">
         <v>6</v>
       </c>
       <c r="C3" s="4">
         <v>0.13657475911579028</v>
       </c>
-      <c r="D3" s="9">
+      <c r="D3" s="8">
         <v>79166666.666666195</v>
       </c>
       <c r="E3" s="3">
         <v>10812168.430000007</v>
       </c>
-      <c r="F3" s="7">
+      <c r="F3" s="3">
         <v>10812168.43</v>
       </c>
-      <c r="G3" s="7">
-        <v>68354498.239999995</v>
+      <c r="G3" s="3">
+        <f>+F3-E3</f>
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A4" s="2">
         <v>3</v>
       </c>
-      <c r="B4" s="8" t="s">
+      <c r="B4" s="7" t="s">
         <v>9</v>
       </c>
       <c r="C4" s="4">
         <v>9.0843144252632818E-2</v>
       </c>
-      <c r="D4" s="9">
+      <c r="D4" s="8">
         <v>79166666.666665599</v>
       </c>
       <c r="E4" s="3">
         <v>7191748.9199999943</v>
       </c>
-      <c r="F4" s="7">
+      <c r="F4" s="3">
         <v>35000000</v>
       </c>
-      <c r="G4" s="7">
-        <v>44166666.670000002</v>
+      <c r="G4" s="3">
+        <f>+F4-E4</f>
+        <v>27808251.080000006</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A5" s="2">
         <v>4</v>
       </c>
-      <c r="B5" s="8" t="s">
+      <c r="B5" s="7" t="s">
         <v>14</v>
       </c>
       <c r="C5" s="4">
         <v>8.4914693538463218E-2</v>
       </c>
-      <c r="D5" s="9">
+      <c r="D5" s="8">
         <v>54166666.666665591</v>
       </c>
       <c r="E5" s="3">
         <v>4599545.900000006</v>
       </c>
-      <c r="F5" s="7">
+      <c r="F5" s="3">
         <v>119500000</v>
       </c>
-      <c r="G5" s="7">
-        <v>-65333333.329999998</v>
+      <c r="G5" s="3">
+        <f>+F5-E5</f>
+        <v>114900454.09999999</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A6" s="2">
         <v>5</v>
       </c>
-      <c r="B6" s="8" t="s">
+      <c r="B6" s="7" t="s">
         <v>10</v>
       </c>
       <c r="C6" s="4">
         <v>0</v>
       </c>
-      <c r="D6" s="9">
+      <c r="D6" s="8">
         <v>25000000.000000101</v>
       </c>
       <c r="E6" s="3">
         <v>0</v>
       </c>
-      <c r="F6" s="7">
-        <v>0</v>
-      </c>
-      <c r="G6" s="7">
-        <v>25000000</v>
+      <c r="F6" s="3">
+        <v>0</v>
+      </c>
+      <c r="G6" s="3">
+        <f>+F6-E6</f>
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A7" s="2">
         <v>6</v>
       </c>
-      <c r="B7" s="8" t="s">
+      <c r="B7" s="7" t="s">
         <v>21</v>
       </c>
       <c r="C7" s="4">
         <v>0</v>
       </c>
-      <c r="D7" s="9">
+      <c r="D7" s="8">
         <v>79166666.666666195</v>
       </c>
       <c r="E7" s="3">
         <v>0</v>
       </c>
-      <c r="F7" s="7">
-        <v>0</v>
-      </c>
-      <c r="G7" s="7">
-        <v>79166666.670000002</v>
+      <c r="F7" s="3">
+        <v>0</v>
+      </c>
+      <c r="G7" s="3">
+        <f>+F7-E7</f>
+        <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A8" s="2">
         <v>7</v>
       </c>
-      <c r="B8" s="8" t="s">
+      <c r="B8" s="7" t="s">
         <v>8</v>
       </c>
       <c r="C8" s="4"/>
-      <c r="D8" s="9">
+      <c r="D8" s="8">
         <v>0</v>
       </c>
       <c r="E8" s="3">
         <v>67216.850000000093</v>
       </c>
-      <c r="F8" s="7">
+      <c r="F8" s="3">
         <v>67216.850000000006</v>
       </c>
-      <c r="G8" s="7">
-        <v>-67216.850000000006</v>
+      <c r="G8" s="3">
+        <f>+F8-E8</f>
+        <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A9" s="2">
         <v>8</v>
       </c>
-      <c r="B9" s="8" t="s">
+      <c r="B9" s="7" t="s">
         <v>16</v>
       </c>
       <c r="C9" s="4"/>
-      <c r="D9" s="9">
+      <c r="D9" s="8">
         <v>0</v>
       </c>
       <c r="E9" s="3">
         <v>-112955.9999999993</v>
       </c>
-      <c r="F9" s="7">
+      <c r="F9" s="3">
         <v>-112956</v>
       </c>
-      <c r="G9" s="7">
-        <v>112956</v>
+      <c r="G9" s="3">
+        <f>+F9-E9</f>
+        <v>-6.9849193096160889E-10</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A10" s="2">
         <v>9</v>
       </c>
-      <c r="B10" s="8" t="s">
+      <c r="B10" s="7" t="s">
         <v>22</v>
       </c>
       <c r="C10" s="4">
         <v>0</v>
       </c>
-      <c r="D10" s="9">
+      <c r="D10" s="8">
         <v>58333333.333329812</v>
       </c>
       <c r="E10" s="3">
         <v>0</v>
       </c>
-      <c r="F10" s="7">
-        <v>0</v>
-      </c>
-      <c r="G10" s="7">
-        <v>58333333.329999998</v>
-      </c>
+      <c r="F10" s="3">
+        <v>0</v>
+      </c>
+      <c r="G10" s="3">
+        <f>+F10-E10</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="G11" s="3"/>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="G12" s="3"/>
     </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
@@ -821,17 +851,17 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:D16"/>
+  <dimension ref="A1:E17"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="41.33203125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="17" customWidth="1"/>
     <col min="3" max="3" width="21.109375" customWidth="1"/>
     <col min="4" max="4" width="20" customWidth="1"/>
-    <col min="5" max="5" width="10.6640625" customWidth="1"/>
+    <col min="5" max="5" width="14.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1" s="10" t="s">
         <v>23</v>
       </c>
@@ -844,205 +874,286 @@
       <c r="D1" s="10" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A2" s="8" t="s">
+      <c r="E1" s="10" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2" s="7" t="s">
         <v>7</v>
       </c>
       <c r="B2" s="4">
         <v>1.5227644098857831</v>
       </c>
-      <c r="C2" s="9">
+      <c r="C2" s="8">
         <v>58333333.333330713</v>
       </c>
       <c r="D2" s="3">
         <v>88827923.909999967</v>
       </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A3" s="8" t="s">
+      <c r="E2" s="9">
+        <f>+D2-C2</f>
+        <v>30494590.576669253</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A3" s="7" t="s">
         <v>9</v>
       </c>
       <c r="B3" s="4">
         <v>0.68582768232238245</v>
       </c>
-      <c r="C3" s="9">
+      <c r="C3" s="8">
         <v>506666666.66665643</v>
       </c>
       <c r="D3" s="3">
         <v>347486025.70999908</v>
       </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A4" s="8" t="s">
+      <c r="E3" s="9">
+        <f>+D3-C3</f>
+        <v>-159180640.95665735</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A4" s="7" t="s">
         <v>6</v>
       </c>
       <c r="B4" s="4">
         <v>0.34818222426316264</v>
       </c>
-      <c r="C4" s="9">
+      <c r="C4" s="8">
         <v>506666666.66665989</v>
       </c>
       <c r="D4" s="3">
         <v>176412326.96000004</v>
       </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A5" s="8" t="s">
+      <c r="E4" s="9">
+        <f>+D4-C4</f>
+        <v>-330254339.70665985</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A5" s="7" t="s">
         <v>8</v>
       </c>
       <c r="B5" s="4">
         <v>0.21726992437037176</v>
       </c>
-      <c r="C5" s="9">
+      <c r="C5" s="8">
         <v>134999999.99999911</v>
       </c>
       <c r="D5" s="3">
         <v>29331439.789999962</v>
       </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A6" s="8" t="s">
+      <c r="E5" s="9">
+        <f>+D5-C5</f>
+        <v>-105668560.20999914</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A6" s="7" t="s">
         <v>11</v>
       </c>
       <c r="B6" s="4">
         <v>0.21633626109805196</v>
       </c>
-      <c r="C6" s="9">
+      <c r="C6" s="8">
         <v>127499999.99999246</v>
       </c>
       <c r="D6" s="3">
         <v>27582873.289999902</v>
       </c>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A7" s="8" t="s">
+      <c r="E6" s="9">
+        <f>+D6-C6</f>
+        <v>-99917126.709992558</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A7" s="7" t="s">
         <v>14</v>
       </c>
       <c r="B7" s="4">
         <v>0.20864588275962204</v>
       </c>
-      <c r="C7" s="9">
+      <c r="C7" s="8">
         <v>346666666.66665554</v>
       </c>
       <c r="D7" s="3">
         <v>72330572.6899997</v>
       </c>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A8" s="8" t="s">
+      <c r="E7" s="9">
+        <f>+D7-C7</f>
+        <v>-274336093.97665584</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A8" s="7" t="s">
         <v>10</v>
       </c>
       <c r="B8" s="4">
         <v>0</v>
       </c>
-      <c r="C8" s="9">
+      <c r="C8" s="8">
         <v>44999999.999995984</v>
       </c>
       <c r="D8" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A9" s="8" t="s">
+      <c r="E8" s="9">
+        <f>+D8-C8</f>
+        <v>-44999999.999995984</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A9" s="7" t="s">
         <v>15</v>
       </c>
       <c r="B9" s="4">
         <v>0</v>
       </c>
-      <c r="C9" s="9">
+      <c r="C9" s="8">
         <v>506666666.66665959</v>
       </c>
       <c r="D9" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A10" s="8" t="s">
+      <c r="E9" s="9">
+        <f>+D9-C9</f>
+        <v>-506666666.66665959</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A10" s="7" t="s">
         <v>12</v>
       </c>
       <c r="B10" s="4">
         <v>0</v>
       </c>
-      <c r="C10" s="9">
+      <c r="C10" s="8">
         <v>28333333.333328005</v>
       </c>
       <c r="D10" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A11" s="8" t="s">
+      <c r="E10" s="9">
+        <f>+D10-C10</f>
+        <v>-28333333.333328005</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A11" s="7" t="s">
         <v>25</v>
       </c>
       <c r="B11" s="4"/>
-      <c r="C11" s="9">
+      <c r="C11" s="8">
         <v>0</v>
       </c>
       <c r="D11" s="3">
         <v>95628322.180000007</v>
       </c>
-    </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A12" s="8" t="s">
+      <c r="E11" s="9">
+        <f>+D11-C11</f>
+        <v>95628322.180000007</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A12" s="7" t="s">
         <v>26</v>
       </c>
       <c r="B12" s="4"/>
-      <c r="C12" s="9">
+      <c r="C12" s="8">
         <v>0</v>
       </c>
       <c r="D12" s="3">
         <v>4801100</v>
       </c>
-    </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A13" s="8" t="s">
+      <c r="E12" s="9">
+        <f>+D12-C12</f>
+        <v>4801100</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A13" s="7" t="s">
         <v>27</v>
       </c>
       <c r="B13" s="4"/>
-      <c r="C13" s="9">
+      <c r="C13" s="8">
         <v>0</v>
       </c>
       <c r="D13" s="3">
         <v>9745638.3800000101</v>
       </c>
-    </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A14" s="8" t="s">
+      <c r="E13" s="9">
+        <f>+D13-C13</f>
+        <v>9745638.3800000101</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A14" s="7" t="s">
         <v>28</v>
       </c>
       <c r="B14" s="4"/>
-      <c r="C14" s="9">
+      <c r="C14" s="8">
         <v>0</v>
       </c>
       <c r="D14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A15" s="8" t="s">
+      <c r="E14" s="9">
+        <f>+D14-C14</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A15" s="7" t="s">
         <v>16</v>
       </c>
       <c r="B15" s="4"/>
-      <c r="C15" s="9">
+      <c r="C15" s="8">
         <v>0</v>
       </c>
       <c r="D15" s="3">
         <v>-112955.9999999993</v>
       </c>
-    </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A16" s="8" t="s">
+      <c r="E15" s="9">
+        <f>+D15-C15</f>
+        <v>-112955.9999999993</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A16" s="7" t="s">
         <v>13</v>
       </c>
       <c r="B16" s="4">
         <v>0</v>
       </c>
-      <c r="C16" s="9">
+      <c r="C16" s="8">
         <v>245833333.33331507</v>
       </c>
       <c r="D16" s="3">
         <v>0</v>
+      </c>
+      <c r="E16" s="9">
+        <f>+D16-C16</f>
+        <v>-245833333.33331507</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A17" s="11" t="s">
+        <v>30</v>
+      </c>
+      <c r="B17" s="12">
+        <v>0.33990688839495686</v>
+      </c>
+      <c r="C17" s="13">
+        <v>2506666666.6665926</v>
+      </c>
+      <c r="D17" s="14">
+        <v>852033266.90999889</v>
+      </c>
+      <c r="E17" s="15">
+        <f>+SUM(E2:E16)</f>
+        <v>-1654633399.7565939</v>
       </c>
     </row>
   </sheetData>

--- a/copa_copilot_datos.xlsx
+++ b/copa_copilot_datos.xlsx
@@ -1,24 +1,27 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30327"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://controlesempresarialesltda-my.sharepoint.com/personal/marango_coem_co/Documents/GitHub/COEM/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="409" documentId="11_7B0F6A10CFB5B9B3AED9E795B9A4719BFA1CF949" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6C087213-8B4B-4E89-BFC6-85113B3735C4}"/>
+  <xr:revisionPtr revIDLastSave="434" documentId="11_7B0F6A10CFB5B9B3AED9E795B9A4719BFA1CF949" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7BCAC33D-FF2A-4A9A-9C8B-015FAFC5A2ED}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView minimized="1" xWindow="24" yWindow="24" windowWidth="23016" windowHeight="12216" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Copa Copilot" sheetId="1" r:id="rId1"/>
     <sheet name="Actividad Semanal" sheetId="2" r:id="rId2"/>
     <sheet name="Estados" sheetId="3" r:id="rId3"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="191028"/>
   <extLst>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
+      <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
         <xcalcf:feature name="microsoft.com:RD"/>
@@ -35,99 +38,93 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="29">
   <si>
     <t>Pos</t>
   </si>
   <si>
+    <t>Comercial</t>
+  </si>
+  <si>
+    <t>% de cumplimiento</t>
+  </si>
+  <si>
+    <t>Cuota</t>
+  </si>
+  <si>
+    <t>Utilidad Bruta</t>
+  </si>
+  <si>
+    <t>Compromiso</t>
+  </si>
+  <si>
+    <t>Falta</t>
+  </si>
+  <si>
+    <t>RODRIGUEZ CONTRERAS JENIFFER LORENA</t>
+  </si>
+  <si>
+    <t>ECHEVERRY SANDRA</t>
+  </si>
+  <si>
+    <t>CORREA CORPUS WILLIAM ERNESTO</t>
+  </si>
+  <si>
+    <t>MENDOZA SALAZAR ROMY VALENTINA</t>
+  </si>
+  <si>
+    <t>NN OCCIDE_SMC_001 1</t>
+  </si>
+  <si>
+    <t>CHARRY OCHOA VIVIANA ANDREA</t>
+  </si>
+  <si>
+    <t>ESPINOSA ORTIZ DEISON FERNANDO</t>
+  </si>
+  <si>
+    <t>NN OCCIDE_CORPO_001 1</t>
+  </si>
+  <si>
+    <t>NN OCCIDE_ENTER_001 1</t>
+  </si>
+  <si>
+    <t>Vendedor</t>
+  </si>
+  <si>
+    <t>% Cump</t>
+  </si>
+  <si>
+    <t>Gap</t>
+  </si>
+  <si>
+    <t>COLLAZOS PRIETO JUAN FELIPE</t>
+  </si>
+  <si>
+    <t>NN OCCIDE_SMC_001 2</t>
+  </si>
+  <si>
+    <t>DIRECTOS CALI DIRECTOS CALI</t>
+  </si>
+  <si>
+    <t>SOTO FERNANDO</t>
+  </si>
+  <si>
+    <t>LOZANO GARCIA JULIO ERNESTO</t>
+  </si>
+  <si>
+    <t>VALERO VELA LUZ EDIT</t>
+  </si>
+  <si>
+    <t>Total general</t>
+  </si>
+  <si>
+    <t>Clasificado</t>
+  </si>
+  <si>
     <t>En Carrera</t>
   </si>
   <si>
-    <t>Clasificado</t>
-  </si>
-  <si>
-    <t>Comercial</t>
-  </si>
-  <si>
-    <t>Cuota</t>
-  </si>
-  <si>
     <t>Valle de la oportunidad</t>
-  </si>
-  <si>
-    <t>ECHEVERRY SANDRA</t>
-  </si>
-  <si>
-    <t>RODRIGUEZ CONTRERAS JENIFFER LORENA</t>
-  </si>
-  <si>
-    <t>ESPINOSA ORTIZ DEISON FERNANDO</t>
-  </si>
-  <si>
-    <t>MENDOZA SALAZAR ROMY VALENTINA</t>
-  </si>
-  <si>
-    <t>NN OCCIDE_SMC_001 1</t>
-  </si>
-  <si>
-    <t>COLLAZOS PRIETO JUAN FELIPE</t>
-  </si>
-  <si>
-    <t>NN OCCIDE_SMC_001 2</t>
-  </si>
-  <si>
-    <t>NN OCCIDE_CORPO_001 2</t>
-  </si>
-  <si>
-    <t>CORREA CORPUS WILLIAM ERNESTO</t>
-  </si>
-  <si>
-    <t>NN OCCIDE_ENTER_001</t>
-  </si>
-  <si>
-    <t>CHARRY OCHOA VIVIANA ANDREA</t>
-  </si>
-  <si>
-    <t>% de cumplimiento</t>
-  </si>
-  <si>
-    <t>Utilidad Bruta</t>
-  </si>
-  <si>
-    <t>Compromiso</t>
-  </si>
-  <si>
-    <t>Falta</t>
-  </si>
-  <si>
-    <t>NN OCCIDE_ENTER_001 1</t>
-  </si>
-  <si>
-    <t>NN OCCIDE_CORPO_001 1</t>
-  </si>
-  <si>
-    <t>Vendedor</t>
-  </si>
-  <si>
-    <t>% Cump</t>
-  </si>
-  <si>
-    <t>DIRECTOS CALI DIRECTOS CALI</t>
-  </si>
-  <si>
-    <t>SOTO FERNANDO</t>
-  </si>
-  <si>
-    <t>LOZANO GARCIA JULIO ERNESTO</t>
-  </si>
-  <si>
-    <t>VALERO VELA LUZ EDIT</t>
-  </si>
-  <si>
-    <t>Gap</t>
-  </si>
-  <si>
-    <t>Total general</t>
   </si>
 </sst>
 </file>
@@ -135,11 +132,11 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="3">
-    <numFmt numFmtId="6" formatCode="&quot;$&quot;\ #,##0;[Red]\-&quot;$&quot;\ #,##0"/>
-    <numFmt numFmtId="169" formatCode="&quot;$&quot;#,##0"/>
-    <numFmt numFmtId="170" formatCode="&quot;$&quot;#,##0;[Red]\-&quot;$&quot;#,##0"/>
+    <numFmt numFmtId="164" formatCode="&quot;$&quot;\ #,##0;[Red]\-&quot;$&quot;\ #,##0"/>
+    <numFmt numFmtId="165" formatCode="&quot;$&quot;#,##0"/>
+    <numFmt numFmtId="166" formatCode="&quot;$&quot;#,##0;[Red]\-&quot;$&quot;#,##0"/>
   </numFmts>
-  <fonts count="7" x14ac:knownFonts="1">
+  <fonts count="7">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -260,7 +257,7 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="6" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -271,8 +268,8 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="169" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="170" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -280,9 +277,9 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="10" fontId="3" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="169" fontId="3" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="6" fontId="3" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="170" fontId="6" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="165" fontId="3" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="164" fontId="3" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="166" fontId="6" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -298,10 +295,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -590,41 +583,41 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:G12"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="14.45"/>
   <cols>
     <col min="1" max="1" width="6" customWidth="1"/>
-    <col min="2" max="2" width="36.88671875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="19.109375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.5546875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.109375" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="13.33203125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="12.5546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="36.85546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="19.140625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.5703125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.140625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="13.28515625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="17.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7" ht="15.6">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="C1" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="D1" s="5" t="s">
+      <c r="E1" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="E1" s="5" t="s">
-        <v>18</v>
-      </c>
       <c r="F1" s="5" t="s">
-        <v>19</v>
+        <v>5</v>
       </c>
       <c r="G1" s="6" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" ht="15">
       <c r="A2" s="2">
         <v>1</v>
       </c>
@@ -632,47 +625,47 @@
         <v>7</v>
       </c>
       <c r="C2" s="4">
-        <v>0.42515786460001193</v>
+        <v>0.42795192960001205</v>
       </c>
       <c r="D2" s="8">
         <v>16666666.666666199</v>
       </c>
       <c r="E2" s="3">
-        <v>7085964.4100000039</v>
+        <v>7132532.1600000113</v>
       </c>
       <c r="F2" s="3">
         <v>7500000</v>
       </c>
       <c r="G2" s="3">
         <f>+F2-E2</f>
-        <v>414035.58999999613</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
+        <v>367467.83999998868</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" ht="15">
       <c r="A3" s="2">
         <v>2</v>
       </c>
       <c r="B3" s="7" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C3" s="4">
-        <v>0.13657475911579028</v>
+        <v>0.13657475911579026</v>
       </c>
       <c r="D3" s="8">
-        <v>79166666.666666195</v>
+        <v>79166666.66666621</v>
       </c>
       <c r="E3" s="3">
         <v>10812168.430000007</v>
       </c>
       <c r="F3" s="3">
-        <v>10812168.43</v>
+        <v>10812168.430000007</v>
       </c>
       <c r="G3" s="3">
         <f>+F3-E3</f>
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:7" ht="15">
       <c r="A4" s="2">
         <v>3</v>
       </c>
@@ -680,58 +673,58 @@
         <v>9</v>
       </c>
       <c r="C4" s="4">
-        <v>9.0843144252632818E-2</v>
+        <v>0.12726489138461788</v>
       </c>
       <c r="D4" s="8">
-        <v>79166666.666665599</v>
+        <v>54166666.666665599</v>
       </c>
       <c r="E4" s="3">
-        <v>7191748.9199999943</v>
+        <v>6893514.950000003</v>
       </c>
       <c r="F4" s="3">
-        <v>35000000</v>
+        <v>119500000</v>
       </c>
       <c r="G4" s="3">
         <f>+F4-E4</f>
-        <v>27808251.080000006</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
+        <v>112606485.05</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" ht="15">
       <c r="A5" s="2">
         <v>4</v>
       </c>
       <c r="B5" s="7" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="C5" s="4">
-        <v>8.4914693538463218E-2</v>
+        <v>9.0843144252632804E-2</v>
       </c>
       <c r="D5" s="8">
-        <v>54166666.666665591</v>
+        <v>79166666.666665599</v>
       </c>
       <c r="E5" s="3">
-        <v>4599545.900000006</v>
+        <v>7191748.9199999869</v>
       </c>
       <c r="F5" s="3">
-        <v>119500000</v>
+        <v>35000000</v>
       </c>
       <c r="G5" s="3">
         <f>+F5-E5</f>
-        <v>114900454.09999999</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
+        <v>27808251.080000013</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" ht="15">
       <c r="A6" s="2">
         <v>5</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C6" s="4">
         <v>0</v>
       </c>
       <c r="D6" s="8">
-        <v>25000000.000000101</v>
+        <v>25000000.000000097</v>
       </c>
       <c r="E6" s="3">
         <v>0</v>
@@ -744,36 +737,34 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:7" ht="15">
       <c r="A7" s="2">
         <v>6</v>
       </c>
       <c r="B7" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="C7" s="4">
-        <v>0</v>
-      </c>
+        <v>12</v>
+      </c>
+      <c r="C7" s="4"/>
       <c r="D7" s="8">
-        <v>79166666.666666195</v>
+        <v>0</v>
       </c>
       <c r="E7" s="3">
-        <v>0</v>
+        <v>-112955.9999999993</v>
       </c>
       <c r="F7" s="3">
-        <v>0</v>
+        <v>-112955.9999999993</v>
       </c>
       <c r="G7" s="3">
         <f>+F7-E7</f>
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:7" ht="15">
       <c r="A8" s="2">
         <v>7</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="C8" s="4"/>
       <c r="D8" s="8">
@@ -783,47 +774,49 @@
         <v>67216.850000000093</v>
       </c>
       <c r="F8" s="3">
-        <v>67216.850000000006</v>
+        <v>67216.850000000093</v>
       </c>
       <c r="G8" s="3">
         <f>+F8-E8</f>
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:7" ht="15">
       <c r="A9" s="2">
         <v>8</v>
       </c>
       <c r="B9" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="C9" s="4"/>
+        <v>14</v>
+      </c>
+      <c r="C9" s="4">
+        <v>0</v>
+      </c>
       <c r="D9" s="8">
-        <v>0</v>
+        <v>58333333.333329797</v>
       </c>
       <c r="E9" s="3">
-        <v>-112955.9999999993</v>
+        <v>0</v>
       </c>
       <c r="F9" s="3">
-        <v>-112956</v>
+        <v>0</v>
       </c>
       <c r="G9" s="3">
         <f>+F9-E9</f>
-        <v>-6.9849193096160889E-10</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" ht="15">
       <c r="A10" s="2">
         <v>9</v>
       </c>
       <c r="B10" s="7" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="C10" s="4">
         <v>0</v>
       </c>
       <c r="D10" s="8">
-        <v>58333333.333329812</v>
+        <v>79166666.66666621</v>
       </c>
       <c r="E10" s="3">
         <v>0</v>
@@ -836,10 +829,10 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:7" ht="15">
       <c r="G11" s="3"/>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:7" ht="15">
       <c r="G12" s="3"/>
     </row>
   </sheetData>
@@ -852,159 +845,152 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:E17"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="14.45"/>
   <cols>
-    <col min="1" max="1" width="41.33203125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="41.28515625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="17" customWidth="1"/>
-    <col min="3" max="3" width="21.109375" customWidth="1"/>
+    <col min="3" max="3" width="21.140625" customWidth="1"/>
     <col min="4" max="4" width="20" customWidth="1"/>
-    <col min="5" max="5" width="14.33203125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="16.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:5">
       <c r="A1" s="10" t="s">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="B1" s="10" t="s">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="C1" s="10" t="s">
+        <v>3</v>
+      </c>
+      <c r="D1" s="10" t="s">
         <v>4</v>
       </c>
-      <c r="D1" s="10" t="s">
+      <c r="E1" s="10" t="s">
         <v>18</v>
       </c>
-      <c r="E1" s="10" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+    </row>
+    <row r="2" spans="1:5" ht="15">
       <c r="A2" s="7" t="s">
         <v>7</v>
       </c>
       <c r="B2" s="4">
-        <v>1.5227644098857831</v>
+        <v>1.5235627141714976</v>
       </c>
       <c r="C2" s="8">
-        <v>58333333.333330713</v>
+        <v>58333333.333330706</v>
       </c>
       <c r="D2" s="3">
-        <v>88827923.909999967</v>
+        <v>88874491.659999847</v>
       </c>
       <c r="E2" s="9">
-        <f>+D2-C2</f>
-        <v>30494590.576669253</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+        <v>30541158.326669142</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" ht="15">
       <c r="A3" s="7" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B3" s="4">
-        <v>0.68582768232238245</v>
+        <v>0.68582768232238223</v>
       </c>
       <c r="C3" s="8">
-        <v>506666666.66665643</v>
+        <v>506666666.66665649</v>
       </c>
       <c r="D3" s="3">
-        <v>347486025.70999908</v>
+        <v>347486025.70999885</v>
       </c>
       <c r="E3" s="9">
-        <f>+D3-C3</f>
-        <v>-159180640.95665735</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
+        <v>-159180640.95665765</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" ht="15">
       <c r="A4" s="7" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="B4" s="4">
-        <v>0.34818222426316264</v>
+        <v>0.34818222426316275</v>
       </c>
       <c r="C4" s="8">
-        <v>506666666.66665989</v>
+        <v>506666666.66665971</v>
       </c>
       <c r="D4" s="3">
-        <v>176412326.96000004</v>
+        <v>176412326.96000147</v>
       </c>
       <c r="E4" s="9">
-        <f>+D4-C4</f>
-        <v>-330254339.70665985</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
+        <v>-330254339.70665824</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" ht="15">
       <c r="A5" s="7" t="s">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="B5" s="4">
-        <v>0.21726992437037176</v>
+        <v>0.21726992437037174</v>
       </c>
       <c r="C5" s="8">
-        <v>134999999.99999911</v>
+        <v>134999999.99999914</v>
       </c>
       <c r="D5" s="3">
-        <v>29331439.789999962</v>
+        <v>29331439.789999902</v>
       </c>
       <c r="E5" s="9">
-        <f>+D5-C5</f>
-        <v>-105668560.20999914</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
+        <v>-105668560.20999923</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" ht="15">
       <c r="A6" s="7" t="s">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="B6" s="4">
-        <v>0.21633626109805196</v>
+        <v>0.21633626109805201</v>
       </c>
       <c r="C6" s="8">
         <v>127499999.99999246</v>
       </c>
       <c r="D6" s="3">
-        <v>27582873.289999902</v>
+        <v>27582873.289999932</v>
       </c>
       <c r="E6" s="9">
-        <f>+D6-C6</f>
-        <v>-99917126.709992558</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
+        <v>-99917126.709992528</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" ht="15">
       <c r="A7" s="7" t="s">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="B7" s="4">
-        <v>0.20864588275962204</v>
+        <v>0.21526310117308381</v>
       </c>
       <c r="C7" s="8">
-        <v>346666666.66665554</v>
+        <v>346666666.66665542</v>
       </c>
       <c r="D7" s="3">
-        <v>72330572.6899997</v>
+        <v>74624541.739999771</v>
       </c>
       <c r="E7" s="9">
-        <f>+D7-C7</f>
-        <v>-274336093.97665584</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
+        <v>-272042124.92665565</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" ht="15">
       <c r="A8" s="7" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B8" s="4">
         <v>0</v>
       </c>
       <c r="C8" s="8">
-        <v>44999999.999995984</v>
+        <v>44999999.999995992</v>
       </c>
       <c r="D8" s="3">
         <v>0</v>
       </c>
       <c r="E8" s="9">
-        <f>+D8-C8</f>
-        <v>-44999999.999995984</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
+        <v>-44999999.999995992</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" ht="15">
       <c r="A9" s="7" t="s">
         <v>15</v>
       </c>
@@ -1012,37 +998,35 @@
         <v>0</v>
       </c>
       <c r="C9" s="8">
-        <v>506666666.66665959</v>
+        <v>506666666.66665965</v>
       </c>
       <c r="D9" s="3">
         <v>0</v>
       </c>
       <c r="E9" s="9">
-        <f>+D9-C9</f>
-        <v>-506666666.66665959</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
+        <v>-506666666.66665965</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" ht="15">
       <c r="A10" s="7" t="s">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="B10" s="4">
         <v>0</v>
       </c>
       <c r="C10" s="8">
-        <v>28333333.333328005</v>
+        <v>28333333.333328009</v>
       </c>
       <c r="D10" s="3">
         <v>0</v>
       </c>
       <c r="E10" s="9">
-        <f>+D10-C10</f>
-        <v>-28333333.333328005</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
+        <v>-28333333.333328009</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" ht="15">
       <c r="A11" s="7" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="B11" s="4"/>
       <c r="C11" s="8">
@@ -1052,13 +1036,12 @@
         <v>95628322.180000007</v>
       </c>
       <c r="E11" s="9">
-        <f>+D11-C11</f>
         <v>95628322.180000007</v>
       </c>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:5" ht="15">
       <c r="A12" s="7" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="B12" s="4"/>
       <c r="C12" s="8">
@@ -1068,13 +1051,12 @@
         <v>4801100</v>
       </c>
       <c r="E12" s="9">
-        <f>+D12-C12</f>
         <v>4801100</v>
       </c>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:5" ht="15">
       <c r="A13" s="7" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="B13" s="4"/>
       <c r="C13" s="8">
@@ -1084,13 +1066,12 @@
         <v>9745638.3800000101</v>
       </c>
       <c r="E13" s="9">
-        <f>+D13-C13</f>
         <v>9745638.3800000101</v>
       </c>
     </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:5" ht="15">
       <c r="A14" s="7" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="B14" s="4"/>
       <c r="C14" s="8">
@@ -1100,13 +1081,12 @@
         <v>0</v>
       </c>
       <c r="E14" s="9">
-        <f>+D14-C14</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" ht="15">
       <c r="A15" s="7" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="B15" s="4"/>
       <c r="C15" s="8">
@@ -1116,44 +1096,41 @@
         <v>-112955.9999999993</v>
       </c>
       <c r="E15" s="9">
-        <f>+D15-C15</f>
         <v>-112955.9999999993</v>
       </c>
     </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:5" ht="15">
       <c r="A16" s="7" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B16" s="4">
         <v>0</v>
       </c>
       <c r="C16" s="8">
-        <v>245833333.33331507</v>
+        <v>245833333.33331513</v>
       </c>
       <c r="D16" s="3">
         <v>0</v>
       </c>
       <c r="E16" s="9">
-        <f>+D16-C16</f>
-        <v>-245833333.33331507</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
+        <v>-245833333.33331513</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" ht="15">
       <c r="A17" s="11" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="B17" s="12">
-        <v>0.33990688839495686</v>
+        <v>0.34084061318219094</v>
       </c>
       <c r="C17" s="13">
         <v>2506666666.6665926</v>
       </c>
       <c r="D17" s="14">
-        <v>852033266.90999889</v>
+        <v>854373803.71000004</v>
       </c>
       <c r="E17" s="15">
-        <f>+SUM(E2:E16)</f>
-        <v>-1654633399.7565939</v>
+        <v>-1652292862.9565928</v>
       </c>
     </row>
   </sheetData>
@@ -1166,24 +1143,24 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9E6B92DB-9C5C-437E-84B0-C727C5D5C893}">
   <dimension ref="A1:A3"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="14.45"/>
   <cols>
-    <col min="1" max="1" width="23.33203125" customWidth="1"/>
+    <col min="1" max="1" width="23.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:1">
       <c r="A1" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1">
       <c r="A2" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.3">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1">
       <c r="A3" t="s">
-        <v>5</v>
+        <v>28</v>
       </c>
     </row>
   </sheetData>

--- a/copa_copilot_datos.xlsx
+++ b/copa_copilot_datos.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://controlesempresarialesltda-my.sharepoint.com/personal/marango_coem_co/Documents/GitHub/COEM/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="434" documentId="11_7B0F6A10CFB5B9B3AED9E795B9A4719BFA1CF949" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7BCAC33D-FF2A-4A9A-9C8B-015FAFC5A2ED}"/>
+  <xr:revisionPtr revIDLastSave="435" documentId="11_7B0F6A10CFB5B9B3AED9E795B9A4719BFA1CF949" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8E4EFBF1-4129-4C05-8BE5-4F395EEACFEA}"/>
   <bookViews>
     <workbookView minimized="1" xWindow="24" yWindow="24" windowWidth="23016" windowHeight="12216" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="31">
   <si>
     <t>Pos</t>
   </si>
@@ -61,15 +61,15 @@
     <t>Falta</t>
   </si>
   <si>
+    <t>CORREA CORPUS WILLIAM ERNESTO</t>
+  </si>
+  <si>
     <t>RODRIGUEZ CONTRERAS JENIFFER LORENA</t>
   </si>
   <si>
     <t>ECHEVERRY SANDRA</t>
   </si>
   <si>
-    <t>CORREA CORPUS WILLIAM ERNESTO</t>
-  </si>
-  <si>
     <t>MENDOZA SALAZAR ROMY VALENTINA</t>
   </si>
   <si>
@@ -82,37 +82,43 @@
     <t>ESPINOSA ORTIZ DEISON FERNANDO</t>
   </si>
   <si>
+    <t>NN OCCIDE_CORPO_001 2</t>
+  </si>
+  <si>
+    <t>NN OCCIDE_ENTER_001</t>
+  </si>
+  <si>
+    <t>Vendedor</t>
+  </si>
+  <si>
+    <t>% Cump</t>
+  </si>
+  <si>
+    <t>Gap</t>
+  </si>
+  <si>
+    <t>COLLAZOS PRIETO JUAN FELIPE</t>
+  </si>
+  <si>
+    <t>NN OCCIDE_ENTER_001 1</t>
+  </si>
+  <si>
+    <t>NN OCCIDE_SMC_001 2</t>
+  </si>
+  <si>
+    <t>DIRECTOS CALI DIRECTOS CALI</t>
+  </si>
+  <si>
+    <t>SOTO FERNANDO</t>
+  </si>
+  <si>
+    <t>LOZANO GARCIA JULIO ERNESTO</t>
+  </si>
+  <si>
+    <t>VALERO VELA LUZ EDIT</t>
+  </si>
+  <si>
     <t>NN OCCIDE_CORPO_001 1</t>
-  </si>
-  <si>
-    <t>NN OCCIDE_ENTER_001 1</t>
-  </si>
-  <si>
-    <t>Vendedor</t>
-  </si>
-  <si>
-    <t>% Cump</t>
-  </si>
-  <si>
-    <t>Gap</t>
-  </si>
-  <si>
-    <t>COLLAZOS PRIETO JUAN FELIPE</t>
-  </si>
-  <si>
-    <t>NN OCCIDE_SMC_001 2</t>
-  </si>
-  <si>
-    <t>DIRECTOS CALI DIRECTOS CALI</t>
-  </si>
-  <si>
-    <t>SOTO FERNANDO</t>
-  </si>
-  <si>
-    <t>LOZANO GARCIA JULIO ERNESTO</t>
-  </si>
-  <si>
-    <t>VALERO VELA LUZ EDIT</t>
   </si>
   <si>
     <t>Total general</t>
@@ -625,20 +631,19 @@
         <v>7</v>
       </c>
       <c r="C2" s="4">
-        <v>0.42795192960001205</v>
+        <v>0.58408911156924226</v>
       </c>
       <c r="D2" s="8">
-        <v>16666666.666666199</v>
+        <v>54166666.666665599</v>
       </c>
       <c r="E2" s="3">
-        <v>7132532.1600000113</v>
+        <v>31638160.210000038</v>
       </c>
       <c r="F2" s="3">
-        <v>7500000</v>
+        <v>119500000</v>
       </c>
       <c r="G2" s="3">
-        <f>+F2-E2</f>
-        <v>367467.83999998868</v>
+        <v>87861839.789999962</v>
       </c>
     </row>
     <row r="3" spans="1:7" ht="15">
@@ -649,20 +654,19 @@
         <v>8</v>
       </c>
       <c r="C3" s="4">
-        <v>0.13657475911579026</v>
+        <v>0.4279519296000121</v>
       </c>
       <c r="D3" s="8">
-        <v>79166666.66666621</v>
+        <v>16666666.666666199</v>
       </c>
       <c r="E3" s="3">
-        <v>10812168.430000007</v>
+        <v>7132532.1599999964</v>
       </c>
       <c r="F3" s="3">
-        <v>10812168.430000007</v>
+        <v>7500000</v>
       </c>
       <c r="G3" s="3">
-        <f>+F3-E3</f>
-        <v>0</v>
+        <v>367467.84000000358</v>
       </c>
     </row>
     <row r="4" spans="1:7" ht="15">
@@ -673,20 +677,19 @@
         <v>9</v>
       </c>
       <c r="C4" s="4">
-        <v>0.12726489138461788</v>
+        <v>0.13657475911579028</v>
       </c>
       <c r="D4" s="8">
-        <v>54166666.666665599</v>
+        <v>79166666.666666195</v>
       </c>
       <c r="E4" s="3">
-        <v>6893514.950000003</v>
+        <v>10812168.430000007</v>
       </c>
       <c r="F4" s="3">
-        <v>119500000</v>
+        <v>10812168.430000007</v>
       </c>
       <c r="G4" s="3">
-        <f>+F4-E4</f>
-        <v>112606485.05</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:7" ht="15">
@@ -697,20 +700,19 @@
         <v>10</v>
       </c>
       <c r="C5" s="4">
-        <v>9.0843144252632804E-2</v>
+        <v>9.0843144252632818E-2</v>
       </c>
       <c r="D5" s="8">
         <v>79166666.666665599</v>
       </c>
       <c r="E5" s="3">
-        <v>7191748.9199999869</v>
+        <v>7191748.9199999943</v>
       </c>
       <c r="F5" s="3">
         <v>35000000</v>
       </c>
       <c r="G5" s="3">
-        <f>+F5-E5</f>
-        <v>27808251.080000013</v>
+        <v>27808251.080000006</v>
       </c>
     </row>
     <row r="6" spans="1:7" ht="15">
@@ -724,7 +726,7 @@
         <v>0</v>
       </c>
       <c r="D6" s="8">
-        <v>25000000.000000097</v>
+        <v>25000000.000000101</v>
       </c>
       <c r="E6" s="3">
         <v>0</v>
@@ -733,7 +735,6 @@
         <v>0</v>
       </c>
       <c r="G6" s="3">
-        <f>+F6-E6</f>
         <v>0</v>
       </c>
     </row>
@@ -755,7 +756,6 @@
         <v>-112955.9999999993</v>
       </c>
       <c r="G7" s="3">
-        <f>+F7-E7</f>
         <v>0</v>
       </c>
     </row>
@@ -777,7 +777,6 @@
         <v>67216.850000000093</v>
       </c>
       <c r="G8" s="3">
-        <f>+F8-E8</f>
         <v>0</v>
       </c>
     </row>
@@ -792,7 +791,7 @@
         <v>0</v>
       </c>
       <c r="D9" s="8">
-        <v>58333333.333329797</v>
+        <v>58333333.333329804</v>
       </c>
       <c r="E9" s="3">
         <v>0</v>
@@ -801,7 +800,6 @@
         <v>0</v>
       </c>
       <c r="G9" s="3">
-        <f>+F9-E9</f>
         <v>0</v>
       </c>
     </row>
@@ -825,7 +823,6 @@
         <v>0</v>
       </c>
       <c r="G10" s="3">
-        <f>+F10-E10</f>
         <v>0</v>
       </c>
     </row>
@@ -873,7 +870,7 @@
     </row>
     <row r="2" spans="1:5" ht="15">
       <c r="A2" s="7" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B2" s="4">
         <v>1.5235627141714976</v>
@@ -907,7 +904,7 @@
     </row>
     <row r="4" spans="1:5" ht="15">
       <c r="A4" s="7" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B4" s="4">
         <v>0.34818222426316275</v>
@@ -958,7 +955,7 @@
     </row>
     <row r="7" spans="1:5" ht="15">
       <c r="A7" s="7" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="B7" s="4">
         <v>0.21526310117308381</v>
@@ -992,7 +989,7 @@
     </row>
     <row r="9" spans="1:5" ht="15">
       <c r="A9" s="7" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="B9" s="4">
         <v>0</v>
@@ -1009,7 +1006,7 @@
     </row>
     <row r="10" spans="1:5" ht="15">
       <c r="A10" s="7" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B10" s="4">
         <v>0</v>
@@ -1026,7 +1023,7 @@
     </row>
     <row r="11" spans="1:5" ht="15">
       <c r="A11" s="7" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B11" s="4"/>
       <c r="C11" s="8">
@@ -1041,7 +1038,7 @@
     </row>
     <row r="12" spans="1:5" ht="15">
       <c r="A12" s="7" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B12" s="4"/>
       <c r="C12" s="8">
@@ -1056,7 +1053,7 @@
     </row>
     <row r="13" spans="1:5" ht="15">
       <c r="A13" s="7" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B13" s="4"/>
       <c r="C13" s="8">
@@ -1071,7 +1068,7 @@
     </row>
     <row r="14" spans="1:5" ht="15">
       <c r="A14" s="7" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B14" s="4"/>
       <c r="C14" s="8">
@@ -1101,7 +1098,7 @@
     </row>
     <row r="16" spans="1:5" ht="15">
       <c r="A16" s="7" t="s">
-        <v>14</v>
+        <v>26</v>
       </c>
       <c r="B16" s="4">
         <v>0</v>
@@ -1118,7 +1115,7 @@
     </row>
     <row r="17" spans="1:5" ht="15">
       <c r="A17" s="11" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="B17" s="12">
         <v>0.34084061318219094</v>
@@ -1150,17 +1147,17 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
     </row>
     <row r="2" spans="1:1">
       <c r="A2" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
     </row>
   </sheetData>

--- a/copa_copilot_datos.xlsx
+++ b/copa_copilot_datos.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://controlesempresarialesltda-my.sharepoint.com/personal/marango_coem_co/Documents/GitHub/COEM/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="435" documentId="11_7B0F6A10CFB5B9B3AED9E795B9A4719BFA1CF949" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8E4EFBF1-4129-4C05-8BE5-4F395EEACFEA}"/>
+  <xr:revisionPtr revIDLastSave="436" documentId="11_7B0F6A10CFB5B9B3AED9E795B9A4719BFA1CF949" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9E8AD1E5-904E-44BB-89F1-F220268C17A5}"/>
   <bookViews>
     <workbookView minimized="1" xWindow="24" yWindow="24" windowWidth="23016" windowHeight="12216" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -67,10 +67,13 @@
     <t>RODRIGUEZ CONTRERAS JENIFFER LORENA</t>
   </si>
   <si>
+    <t>MENDOZA SALAZAR ROMY VALENTINA</t>
+  </si>
+  <si>
     <t>ECHEVERRY SANDRA</t>
   </si>
   <si>
-    <t>MENDOZA SALAZAR ROMY VALENTINA</t>
+    <t>NN OCCIDE_ENTER_001</t>
   </si>
   <si>
     <t>NN OCCIDE_SMC_001 1</t>
@@ -83,9 +86,6 @@
   </si>
   <si>
     <t>NN OCCIDE_CORPO_001 2</t>
-  </si>
-  <si>
-    <t>NN OCCIDE_ENTER_001</t>
   </si>
   <si>
     <t>Vendedor</t>
@@ -631,19 +631,19 @@
         <v>7</v>
       </c>
       <c r="C2" s="4">
-        <v>0.58408911156924226</v>
+        <v>0.58408911156924237</v>
       </c>
       <c r="D2" s="8">
-        <v>54166666.666665599</v>
+        <v>54166666.666665591</v>
       </c>
       <c r="E2" s="3">
-        <v>31638160.210000038</v>
+        <v>31638160.210000008</v>
       </c>
       <c r="F2" s="3">
         <v>119500000</v>
       </c>
       <c r="G2" s="3">
-        <v>87861839.789999962</v>
+        <v>87861839.789999992</v>
       </c>
     </row>
     <row r="3" spans="1:7" ht="15">
@@ -677,19 +677,19 @@
         <v>9</v>
       </c>
       <c r="C4" s="4">
-        <v>0.13657475911579028</v>
+        <v>0.2703738711157932</v>
       </c>
       <c r="D4" s="8">
-        <v>79166666.666666195</v>
+        <v>79166666.666665584</v>
       </c>
       <c r="E4" s="3">
-        <v>10812168.430000007</v>
+        <v>21404598.129999995</v>
       </c>
       <c r="F4" s="3">
-        <v>10812168.430000007</v>
+        <v>35000000</v>
       </c>
       <c r="G4" s="3">
-        <v>0</v>
+        <v>13595401.870000005</v>
       </c>
     </row>
     <row r="5" spans="1:7" ht="15">
@@ -700,19 +700,19 @@
         <v>10</v>
       </c>
       <c r="C5" s="4">
-        <v>9.0843144252632818E-2</v>
+        <v>0.13657475911579028</v>
       </c>
       <c r="D5" s="8">
-        <v>79166666.666665599</v>
+        <v>79166666.666666195</v>
       </c>
       <c r="E5" s="3">
-        <v>7191748.9199999943</v>
+        <v>10812168.429999992</v>
       </c>
       <c r="F5" s="3">
-        <v>35000000</v>
+        <v>10812168.429999992</v>
       </c>
       <c r="G5" s="3">
-        <v>27808251.080000006</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:7" ht="15">
@@ -726,7 +726,7 @@
         <v>0</v>
       </c>
       <c r="D6" s="8">
-        <v>25000000.000000101</v>
+        <v>79166666.666666225</v>
       </c>
       <c r="E6" s="3">
         <v>0</v>
@@ -745,15 +745,17 @@
       <c r="B7" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="C7" s="4"/>
+      <c r="C7" s="4">
+        <v>0</v>
+      </c>
       <c r="D7" s="8">
-        <v>0</v>
+        <v>25000000.000000101</v>
       </c>
       <c r="E7" s="3">
-        <v>-112955.9999999993</v>
+        <v>0</v>
       </c>
       <c r="F7" s="3">
-        <v>-112955.9999999993</v>
+        <v>0</v>
       </c>
       <c r="G7" s="3">
         <v>0</v>
@@ -771,10 +773,10 @@
         <v>0</v>
       </c>
       <c r="E8" s="3">
-        <v>67216.850000000093</v>
+        <v>-112955.9999999993</v>
       </c>
       <c r="F8" s="3">
-        <v>67216.850000000093</v>
+        <v>-112955.9999999993</v>
       </c>
       <c r="G8" s="3">
         <v>0</v>
@@ -787,17 +789,15 @@
       <c r="B9" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="C9" s="4">
-        <v>0</v>
-      </c>
+      <c r="C9" s="4"/>
       <c r="D9" s="8">
-        <v>58333333.333329804</v>
+        <v>0</v>
       </c>
       <c r="E9" s="3">
-        <v>0</v>
+        <v>67216.850000000093</v>
       </c>
       <c r="F9" s="3">
-        <v>0</v>
+        <v>67216.850000000093</v>
       </c>
       <c r="G9" s="3">
         <v>0</v>
@@ -814,7 +814,7 @@
         <v>0</v>
       </c>
       <c r="D10" s="8">
-        <v>79166666.66666621</v>
+        <v>58333333.333329797</v>
       </c>
       <c r="E10" s="3">
         <v>0</v>
@@ -887,7 +887,7 @@
     </row>
     <row r="3" spans="1:5" ht="15">
       <c r="A3" s="7" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B3" s="4">
         <v>0.68582768232238223</v>
@@ -904,7 +904,7 @@
     </row>
     <row r="4" spans="1:5" ht="15">
       <c r="A4" s="7" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B4" s="4">
         <v>0.34818222426316275</v>
@@ -921,7 +921,7 @@
     </row>
     <row r="5" spans="1:5" ht="15">
       <c r="A5" s="7" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B5" s="4">
         <v>0.21726992437037174</v>
@@ -972,7 +972,7 @@
     </row>
     <row r="8" spans="1:5" ht="15">
       <c r="A8" s="7" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B8" s="4">
         <v>0</v>
@@ -1083,7 +1083,7 @@
     </row>
     <row r="15" spans="1:5" ht="15">
       <c r="A15" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B15" s="4"/>
       <c r="C15" s="8">

--- a/copa_copilot_datos.xlsx
+++ b/copa_copilot_datos.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://controlesempresarialesltda-my.sharepoint.com/personal/marango_coem_co/Documents/GitHub/COEM/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="436" documentId="11_7B0F6A10CFB5B9B3AED9E795B9A4719BFA1CF949" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9E8AD1E5-904E-44BB-89F1-F220268C17A5}"/>
+  <xr:revisionPtr revIDLastSave="439" documentId="11_7B0F6A10CFB5B9B3AED9E795B9A4719BFA1CF949" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{19164616-BC4D-4189-80F3-D8A37A32F4F9}"/>
   <bookViews>
     <workbookView minimized="1" xWindow="24" yWindow="24" windowWidth="23016" windowHeight="12216" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="29">
   <si>
     <t>Pos</t>
   </si>
@@ -100,25 +100,19 @@
     <t>COLLAZOS PRIETO JUAN FELIPE</t>
   </si>
   <si>
-    <t>NN OCCIDE_ENTER_001 1</t>
-  </si>
-  <si>
     <t>NN OCCIDE_SMC_001 2</t>
   </si>
   <si>
+    <t>SOTO FERNANDO</t>
+  </si>
+  <si>
     <t>DIRECTOS CALI DIRECTOS CALI</t>
   </si>
   <si>
-    <t>SOTO FERNANDO</t>
-  </si>
-  <si>
     <t>LOZANO GARCIA JULIO ERNESTO</t>
   </si>
   <si>
     <t>VALERO VELA LUZ EDIT</t>
-  </si>
-  <si>
-    <t>NN OCCIDE_CORPO_001 1</t>
   </si>
   <si>
     <t>Total general</t>
@@ -873,16 +867,16 @@
         <v>8</v>
       </c>
       <c r="B2" s="4">
-        <v>1.5235627141714976</v>
+        <v>1.5235627141714974</v>
       </c>
       <c r="C2" s="8">
-        <v>58333333.333330706</v>
+        <v>58333333.333330713</v>
       </c>
       <c r="D2" s="3">
-        <v>88874491.659999847</v>
+        <v>88874491.660000086</v>
       </c>
       <c r="E2" s="9">
-        <v>30541158.326669142</v>
+        <v>30541158.326669373</v>
       </c>
     </row>
     <row r="3" spans="1:5" ht="15">
@@ -890,16 +884,16 @@
         <v>9</v>
       </c>
       <c r="B3" s="4">
-        <v>0.68582768232238223</v>
+        <v>0.71387935839475125</v>
       </c>
       <c r="C3" s="8">
-        <v>506666666.66665649</v>
+        <v>506666666.66665637</v>
       </c>
       <c r="D3" s="3">
-        <v>347486025.70999885</v>
+        <v>361698874.91999936</v>
       </c>
       <c r="E3" s="9">
-        <v>-159180640.95665765</v>
+        <v>-144967791.74665701</v>
       </c>
     </row>
     <row r="4" spans="1:5" ht="15">
@@ -907,84 +901,84 @@
         <v>10</v>
       </c>
       <c r="B4" s="4">
-        <v>0.34818222426316275</v>
+        <v>0.34818222426316253</v>
       </c>
       <c r="C4" s="8">
-        <v>506666666.66665971</v>
+        <v>506666666.66665995</v>
       </c>
       <c r="D4" s="3">
-        <v>176412326.96000147</v>
+        <v>176412326.96000004</v>
       </c>
       <c r="E4" s="9">
-        <v>-330254339.70665824</v>
+        <v>-330254339.70665991</v>
       </c>
     </row>
     <row r="5" spans="1:5" ht="15">
       <c r="A5" s="7" t="s">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="B5" s="4">
-        <v>0.21726992437037174</v>
+        <v>0.28664188557693249</v>
       </c>
       <c r="C5" s="8">
-        <v>134999999.99999914</v>
+        <v>346666666.6666553</v>
       </c>
       <c r="D5" s="3">
-        <v>29331439.789999902</v>
+        <v>99369187</v>
       </c>
       <c r="E5" s="9">
-        <v>-105668560.20999923</v>
+        <v>-247297479.6666553</v>
       </c>
     </row>
     <row r="6" spans="1:5" ht="15">
       <c r="A6" s="7" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="B6" s="4">
-        <v>0.21633626109805201</v>
+        <v>0.21726992437037171</v>
       </c>
       <c r="C6" s="8">
-        <v>127499999.99999246</v>
+        <v>134999999.99999917</v>
       </c>
       <c r="D6" s="3">
-        <v>27582873.289999932</v>
+        <v>29331439.789999962</v>
       </c>
       <c r="E6" s="9">
-        <v>-99917126.709992528</v>
+        <v>-105668560.2099992</v>
       </c>
     </row>
     <row r="7" spans="1:5" ht="15">
       <c r="A7" s="7" t="s">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="B7" s="4">
-        <v>0.21526310117308381</v>
+        <v>0.21633626109805204</v>
       </c>
       <c r="C7" s="8">
-        <v>346666666.66665542</v>
+        <v>127499999.99999245</v>
       </c>
       <c r="D7" s="3">
-        <v>74624541.739999771</v>
+        <v>27582873.289999962</v>
       </c>
       <c r="E7" s="9">
-        <v>-272042124.92665565</v>
+        <v>-99917126.709992483</v>
       </c>
     </row>
     <row r="8" spans="1:5" ht="15">
       <c r="A8" s="7" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B8" s="4">
         <v>0</v>
       </c>
       <c r="C8" s="8">
-        <v>44999999.999995992</v>
+        <v>506666666.66665959</v>
       </c>
       <c r="D8" s="3">
         <v>0</v>
       </c>
       <c r="E8" s="9">
-        <v>-44999999.999995992</v>
+        <v>-506666666.66665959</v>
       </c>
     </row>
     <row r="9" spans="1:5" ht="15">
@@ -995,65 +989,65 @@
         <v>0</v>
       </c>
       <c r="C9" s="8">
-        <v>506666666.66665965</v>
+        <v>28333333.333328005</v>
       </c>
       <c r="D9" s="3">
         <v>0</v>
       </c>
       <c r="E9" s="9">
-        <v>-506666666.66665965</v>
+        <v>-28333333.333328005</v>
       </c>
     </row>
     <row r="10" spans="1:5" ht="15">
       <c r="A10" s="7" t="s">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="B10" s="4">
         <v>0</v>
       </c>
       <c r="C10" s="8">
-        <v>28333333.333328009</v>
+        <v>44999999.999996006</v>
       </c>
       <c r="D10" s="3">
         <v>0</v>
       </c>
       <c r="E10" s="9">
-        <v>-28333333.333328009</v>
+        <v>-44999999.999996006</v>
       </c>
     </row>
     <row r="11" spans="1:5" ht="15">
       <c r="A11" s="7" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B11" s="4"/>
       <c r="C11" s="8">
         <v>0</v>
       </c>
       <c r="D11" s="3">
-        <v>95628322.180000007</v>
+        <v>4801100</v>
       </c>
       <c r="E11" s="9">
-        <v>95628322.180000007</v>
+        <v>4801100</v>
       </c>
     </row>
     <row r="12" spans="1:5" ht="15">
       <c r="A12" s="7" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B12" s="4"/>
       <c r="C12" s="8">
         <v>0</v>
       </c>
       <c r="D12" s="3">
-        <v>4801100</v>
+        <v>95628322.180000007</v>
       </c>
       <c r="E12" s="9">
-        <v>4801100</v>
+        <v>95628322.180000007</v>
       </c>
     </row>
     <row r="13" spans="1:5" ht="15">
       <c r="A13" s="7" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B13" s="4"/>
       <c r="C13" s="8">
@@ -1068,7 +1062,7 @@
     </row>
     <row r="14" spans="1:5" ht="15">
       <c r="A14" s="7" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B14" s="4"/>
       <c r="C14" s="8">
@@ -1098,7 +1092,7 @@
     </row>
     <row r="16" spans="1:5" ht="15">
       <c r="A16" s="7" t="s">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="B16" s="4">
         <v>0</v>
@@ -1115,19 +1109,19 @@
     </row>
     <row r="17" spans="1:5" ht="15">
       <c r="A17" s="11" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="B17" s="12">
-        <v>0.34084061318219094</v>
+        <v>0.35638216682713819</v>
       </c>
       <c r="C17" s="13">
         <v>2506666666.6665926</v>
       </c>
       <c r="D17" s="14">
-        <v>854373803.71000004</v>
+        <v>893331298.18000031</v>
       </c>
       <c r="E17" s="15">
-        <v>-1652292862.9565928</v>
+        <v>-1613335368.4865932</v>
       </c>
     </row>
   </sheetData>
@@ -1147,17 +1141,17 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
     </row>
     <row r="2" spans="1:1">
       <c r="A2" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
     </row>
   </sheetData>

--- a/copa_copilot_datos.xlsx
+++ b/copa_copilot_datos.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://controlesempresarialesltda-my.sharepoint.com/personal/marango_coem_co/Documents/GitHub/COEM/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="439" documentId="11_7B0F6A10CFB5B9B3AED9E795B9A4719BFA1CF949" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{19164616-BC4D-4189-80F3-D8A37A32F4F9}"/>
+  <xr:revisionPtr revIDLastSave="444" documentId="11_7B0F6A10CFB5B9B3AED9E795B9A4719BFA1CF949" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{03890D6E-556B-4CB6-9E90-C8D700F67107}"/>
   <bookViews>
-    <workbookView minimized="1" xWindow="24" yWindow="24" windowWidth="23016" windowHeight="12216" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView minimized="1" xWindow="24" yWindow="24" windowWidth="23016" windowHeight="12216" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Copa Copilot" sheetId="1" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="29">
   <si>
     <t>Pos</t>
   </si>
@@ -73,19 +73,25 @@
     <t>ECHEVERRY SANDRA</t>
   </si>
   <si>
-    <t>NN OCCIDE_ENTER_001</t>
+    <t>NN OCCIDE_ENTER_001 1</t>
+  </si>
+  <si>
+    <t>NN OCCIDE_SMC_001 2</t>
   </si>
   <si>
     <t>NN OCCIDE_SMC_001 1</t>
   </si>
   <si>
+    <t>CAMACHO BENAVIDES RUBEN DARIO</t>
+  </si>
+  <si>
+    <t>ESPINOSA ORTIZ DEISON FERNANDO</t>
+  </si>
+  <si>
     <t>CHARRY OCHOA VIVIANA ANDREA</t>
   </si>
   <si>
-    <t>ESPINOSA ORTIZ DEISON FERNANDO</t>
-  </si>
-  <si>
-    <t>NN OCCIDE_CORPO_001 2</t>
+    <t>NN OCCIDE_CORPO_001 1</t>
   </si>
   <si>
     <t>Vendedor</t>
@@ -100,22 +106,16 @@
     <t>COLLAZOS PRIETO JUAN FELIPE</t>
   </si>
   <si>
-    <t>NN OCCIDE_SMC_001 2</t>
-  </si>
-  <si>
     <t>SOTO FERNANDO</t>
   </si>
   <si>
+    <t>VALERO VELA LUZ EDIT</t>
+  </si>
+  <si>
     <t>DIRECTOS CALI DIRECTOS CALI</t>
   </si>
   <si>
     <t>LOZANO GARCIA JULIO ERNESTO</t>
-  </si>
-  <si>
-    <t>VALERO VELA LUZ EDIT</t>
-  </si>
-  <si>
-    <t>Total general</t>
   </si>
   <si>
     <t>Clasificado</t>
@@ -159,14 +159,6 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
       <family val="2"/>
@@ -185,8 +177,14 @@
       <name val="Aptos Narrow"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="5">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -201,12 +199,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="4" tint="0.79998168889431442"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="3" tint="0.79998168889431442"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -249,20 +241,20 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -270,16 +262,17 @@
     </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="10" fontId="3" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="165" fontId="3" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="164" fontId="3" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="166" fontId="6" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="166" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -625,19 +618,19 @@
         <v>7</v>
       </c>
       <c r="C2" s="4">
-        <v>0.58408911156924237</v>
+        <v>2.2860202013538915</v>
       </c>
       <c r="D2" s="8">
-        <v>54166666.666665591</v>
+        <v>54166666.666665599</v>
       </c>
       <c r="E2" s="3">
-        <v>31638160.210000008</v>
-      </c>
-      <c r="F2" s="3">
-        <v>119500000</v>
-      </c>
-      <c r="G2" s="3">
-        <v>87861839.789999992</v>
+        <v>123826094.24000072</v>
+      </c>
+      <c r="F2">
+        <v>124000000</v>
+      </c>
+      <c r="G2">
+        <v>173905.75999927521</v>
       </c>
     </row>
     <row r="3" spans="1:7" ht="15">
@@ -648,19 +641,19 @@
         <v>8</v>
       </c>
       <c r="C3" s="4">
-        <v>0.4279519296000121</v>
+        <v>0.46658586780001304</v>
       </c>
       <c r="D3" s="8">
-        <v>16666666.666666199</v>
+        <v>16666666.6666662</v>
       </c>
       <c r="E3" s="3">
-        <v>7132532.1599999964</v>
-      </c>
-      <c r="F3" s="3">
-        <v>7500000</v>
-      </c>
-      <c r="G3" s="3">
-        <v>367467.84000000358</v>
+        <v>7776431.1299999952</v>
+      </c>
+      <c r="F3">
+        <v>9000000</v>
+      </c>
+      <c r="G3">
+        <v>1223568.8700000048</v>
       </c>
     </row>
     <row r="4" spans="1:7" ht="15">
@@ -671,19 +664,19 @@
         <v>9</v>
       </c>
       <c r="C4" s="4">
-        <v>0.2703738711157932</v>
+        <v>0.34126075503158271</v>
       </c>
       <c r="D4" s="8">
-        <v>79166666.666665584</v>
+        <v>79166666.666665792</v>
       </c>
       <c r="E4" s="3">
-        <v>21404598.129999995</v>
-      </c>
-      <c r="F4" s="3">
-        <v>35000000</v>
-      </c>
-      <c r="G4" s="3">
-        <v>13595401.870000005</v>
+        <v>27016476.439999998</v>
+      </c>
+      <c r="F4">
+        <v>38000000</v>
+      </c>
+      <c r="G4">
+        <v>10983523.560000002</v>
       </c>
     </row>
     <row r="5" spans="1:7" ht="15">
@@ -700,12 +693,12 @@
         <v>79166666.666666195</v>
       </c>
       <c r="E5" s="3">
-        <v>10812168.429999992</v>
-      </c>
-      <c r="F5" s="3">
-        <v>10812168.429999992</v>
-      </c>
-      <c r="G5" s="3">
+        <v>10812168.430000007</v>
+      </c>
+      <c r="F5">
+        <v>10812168.430000007</v>
+      </c>
+      <c r="G5">
         <v>0</v>
       </c>
     </row>
@@ -720,15 +713,15 @@
         <v>0</v>
       </c>
       <c r="D6" s="8">
-        <v>79166666.666666225</v>
+        <v>79166666.66666621</v>
       </c>
       <c r="E6" s="3">
         <v>0</v>
       </c>
-      <c r="F6" s="3">
-        <v>0</v>
-      </c>
-      <c r="G6" s="3">
+      <c r="F6">
+        <v>0</v>
+      </c>
+      <c r="G6">
         <v>0</v>
       </c>
     </row>
@@ -739,19 +732,17 @@
       <c r="B7" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="C7" s="4">
-        <v>0</v>
-      </c>
+      <c r="C7" s="4"/>
       <c r="D7" s="8">
-        <v>25000000.000000101</v>
+        <v>0</v>
       </c>
       <c r="E7" s="3">
         <v>0</v>
       </c>
-      <c r="F7" s="3">
-        <v>0</v>
-      </c>
-      <c r="G7" s="3">
+      <c r="F7">
+        <v>0</v>
+      </c>
+      <c r="G7">
         <v>0</v>
       </c>
     </row>
@@ -762,17 +753,19 @@
       <c r="B8" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="C8" s="4"/>
+      <c r="C8" s="4">
+        <v>0</v>
+      </c>
       <c r="D8" s="8">
-        <v>0</v>
+        <v>25000000.000000089</v>
       </c>
       <c r="E8" s="3">
-        <v>-112955.9999999993</v>
-      </c>
-      <c r="F8" s="3">
-        <v>-112955.9999999993</v>
-      </c>
-      <c r="G8" s="3">
+        <v>0</v>
+      </c>
+      <c r="F8">
+        <v>0</v>
+      </c>
+      <c r="G8">
         <v>0</v>
       </c>
     </row>
@@ -788,12 +781,12 @@
         <v>0</v>
       </c>
       <c r="E9" s="3">
-        <v>67216.850000000093</v>
-      </c>
-      <c r="F9" s="3">
-        <v>67216.850000000093</v>
-      </c>
-      <c r="G9" s="3">
+        <v>0</v>
+      </c>
+      <c r="F9">
+        <v>0</v>
+      </c>
+      <c r="G9">
         <v>0</v>
       </c>
     </row>
@@ -804,27 +797,56 @@
       <c r="B10" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="C10" s="4">
-        <v>0</v>
-      </c>
+      <c r="C10" s="4"/>
       <c r="D10" s="8">
-        <v>58333333.333329797</v>
+        <v>0</v>
       </c>
       <c r="E10" s="3">
-        <v>0</v>
-      </c>
-      <c r="F10" s="3">
-        <v>0</v>
-      </c>
-      <c r="G10" s="3">
+        <v>67216.850000000093</v>
+      </c>
+      <c r="F10">
+        <v>67216.850000000093</v>
+      </c>
+      <c r="G10">
         <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:7" ht="15">
-      <c r="G11" s="3"/>
+      <c r="B11" t="s">
+        <v>16</v>
+      </c>
+      <c r="D11">
+        <v>0</v>
+      </c>
+      <c r="E11">
+        <v>-112955.9999999993</v>
+      </c>
+      <c r="F11">
+        <v>-112955.9999999993</v>
+      </c>
+      <c r="G11">
+        <v>0</v>
+      </c>
     </row>
     <row r="12" spans="1:7" ht="15">
-      <c r="G12" s="3"/>
+      <c r="B12" t="s">
+        <v>17</v>
+      </c>
+      <c r="C12">
+        <v>0</v>
+      </c>
+      <c r="D12">
+        <v>58333333.333329812</v>
+      </c>
+      <c r="E12">
+        <v>0</v>
+      </c>
+      <c r="F12">
+        <v>0</v>
+      </c>
+      <c r="G12">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
@@ -847,10 +869,10 @@
   <sheetData>
     <row r="1" spans="1:5">
       <c r="A1" s="10" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="B1" s="10" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="C1" s="10" t="s">
         <v>3</v>
@@ -859,7 +881,7 @@
         <v>4</v>
       </c>
       <c r="E1" s="10" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
     </row>
     <row r="2" spans="1:5" ht="15">
@@ -867,16 +889,16 @@
         <v>8</v>
       </c>
       <c r="B2" s="4">
-        <v>1.5235627141714974</v>
+        <v>1.5346009822286402</v>
       </c>
       <c r="C2" s="8">
-        <v>58333333.333330713</v>
+        <v>58333333.333330736</v>
       </c>
       <c r="D2" s="3">
-        <v>88874491.660000086</v>
+        <v>89518390.629999995</v>
       </c>
       <c r="E2" s="9">
-        <v>30541158.326669373</v>
+        <v>31185057.29666926</v>
       </c>
     </row>
     <row r="3" spans="1:5" ht="15">
@@ -884,72 +906,72 @@
         <v>9</v>
       </c>
       <c r="B3" s="4">
-        <v>0.71387935839475125</v>
+        <v>0.72495543400659257</v>
       </c>
       <c r="C3" s="8">
-        <v>506666666.66665637</v>
+        <v>506666666.66665709</v>
       </c>
       <c r="D3" s="3">
-        <v>361698874.91999936</v>
+        <v>367310753.23000002</v>
       </c>
       <c r="E3" s="9">
-        <v>-144967791.74665701</v>
+        <v>-139355913.43665707</v>
       </c>
     </row>
     <row r="4" spans="1:5" ht="15">
       <c r="A4" s="7" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="B4" s="4">
-        <v>0.34818222426316253</v>
+        <v>0.55256861835578663</v>
       </c>
       <c r="C4" s="8">
-        <v>506666666.66665995</v>
+        <v>346666666.66665572</v>
       </c>
       <c r="D4" s="3">
-        <v>176412326.96000004</v>
+        <v>191557121.03000069</v>
       </c>
       <c r="E4" s="9">
-        <v>-330254339.70665991</v>
+        <v>-155109545.63665503</v>
       </c>
     </row>
     <row r="5" spans="1:5" ht="15">
       <c r="A5" s="7" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="B5" s="4">
-        <v>0.28664188557693249</v>
+        <v>0.34818222426316259</v>
       </c>
       <c r="C5" s="8">
-        <v>346666666.6666553</v>
+        <v>506666666.66665983</v>
       </c>
       <c r="D5" s="3">
-        <v>99369187</v>
+        <v>176412326.95999956</v>
       </c>
       <c r="E5" s="9">
-        <v>-247297479.6666553</v>
+        <v>-330254339.70666027</v>
       </c>
     </row>
     <row r="6" spans="1:5" ht="15">
       <c r="A6" s="7" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B6" s="4">
-        <v>0.21726992437037171</v>
+        <v>0.2172699243703719</v>
       </c>
       <c r="C6" s="8">
-        <v>134999999.99999917</v>
+        <v>134999999.99999905</v>
       </c>
       <c r="D6" s="3">
-        <v>29331439.789999962</v>
+        <v>29331439.790000021</v>
       </c>
       <c r="E6" s="9">
-        <v>-105668560.2099992</v>
+        <v>-105668560.20999902</v>
       </c>
     </row>
     <row r="7" spans="1:5" ht="15">
       <c r="A7" s="7" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="B7" s="4">
         <v>0.21633626109805204</v>
@@ -972,156 +994,154 @@
         <v>0</v>
       </c>
       <c r="C8" s="8">
-        <v>506666666.66665959</v>
+        <v>506666666.66665965</v>
       </c>
       <c r="D8" s="3">
         <v>0</v>
       </c>
       <c r="E8" s="9">
-        <v>-506666666.66665959</v>
+        <v>-506666666.66665965</v>
       </c>
     </row>
     <row r="9" spans="1:5" ht="15">
       <c r="A9" s="7" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="B9" s="4">
         <v>0</v>
       </c>
       <c r="C9" s="8">
-        <v>28333333.333328005</v>
+        <v>28333333.333327994</v>
       </c>
       <c r="D9" s="3">
         <v>0</v>
       </c>
       <c r="E9" s="9">
-        <v>-28333333.333328005</v>
+        <v>-28333333.333327994</v>
       </c>
     </row>
     <row r="10" spans="1:5" ht="15">
       <c r="A10" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="B10" s="4">
-        <v>0</v>
-      </c>
+        <v>22</v>
+      </c>
+      <c r="B10" s="4"/>
       <c r="C10" s="8">
-        <v>44999999.999996006</v>
+        <v>0</v>
       </c>
       <c r="D10" s="3">
-        <v>0</v>
+        <v>4801100</v>
       </c>
       <c r="E10" s="9">
-        <v>-44999999.999996006</v>
+        <v>4801100</v>
       </c>
     </row>
     <row r="11" spans="1:5" ht="15">
       <c r="A11" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="B11" s="4"/>
+        <v>13</v>
+      </c>
+      <c r="B11" s="4">
+        <v>0</v>
+      </c>
       <c r="C11" s="8">
-        <v>0</v>
+        <v>44999999.999995992</v>
       </c>
       <c r="D11" s="3">
-        <v>4801100</v>
+        <v>0</v>
       </c>
       <c r="E11" s="9">
-        <v>4801100</v>
+        <v>-44999999.999995992</v>
       </c>
     </row>
     <row r="12" spans="1:5" ht="15">
       <c r="A12" s="7" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B12" s="4"/>
       <c r="C12" s="8">
         <v>0</v>
       </c>
       <c r="D12" s="3">
-        <v>95628322.180000007</v>
+        <v>0</v>
       </c>
       <c r="E12" s="9">
-        <v>95628322.180000007</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13" spans="1:5" ht="15">
       <c r="A13" s="7" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B13" s="4"/>
       <c r="C13" s="8">
         <v>0</v>
       </c>
       <c r="D13" s="3">
-        <v>9745638.3800000101</v>
+        <v>95628322.180000007</v>
       </c>
       <c r="E13" s="9">
-        <v>9745638.3800000101</v>
+        <v>95628322.180000007</v>
       </c>
     </row>
     <row r="14" spans="1:5" ht="15">
       <c r="A14" s="7" t="s">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="B14" s="4"/>
       <c r="C14" s="8">
         <v>0</v>
       </c>
       <c r="D14" s="3">
-        <v>0</v>
+        <v>-112955.9999999993</v>
       </c>
       <c r="E14" s="9">
-        <v>0</v>
+        <v>-112955.9999999993</v>
       </c>
     </row>
     <row r="15" spans="1:5" ht="15">
       <c r="A15" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="B15" s="4"/>
+        <v>17</v>
+      </c>
+      <c r="B15" s="4">
+        <v>0</v>
+      </c>
       <c r="C15" s="8">
-        <v>0</v>
+        <v>245833333.33331487</v>
       </c>
       <c r="D15" s="3">
-        <v>-112955.9999999993</v>
+        <v>0</v>
       </c>
       <c r="E15" s="9">
-        <v>-112955.9999999993</v>
+        <v>-245833333.33331487</v>
       </c>
     </row>
     <row r="16" spans="1:5" ht="15">
       <c r="A16" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="B16" s="4">
-        <v>0</v>
-      </c>
+        <v>14</v>
+      </c>
+      <c r="B16" s="4"/>
       <c r="C16" s="8">
-        <v>245833333.33331513</v>
+        <v>0</v>
       </c>
       <c r="D16" s="3">
         <v>0</v>
       </c>
       <c r="E16" s="9">
-        <v>-245833333.33331513</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5" ht="15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" s="16" customFormat="1" ht="15">
       <c r="A17" s="11" t="s">
         <v>25</v>
       </c>
-      <c r="B17" s="12">
-        <v>0.35638216682713819</v>
-      </c>
+      <c r="B17" s="12"/>
       <c r="C17" s="13">
-        <v>2506666666.6665926</v>
+        <v>0</v>
       </c>
       <c r="D17" s="14">
-        <v>893331298.18000031</v>
+        <v>9745638.3800000101</v>
       </c>
       <c r="E17" s="15">
-        <v>-1613335368.4865932</v>
+        <v>9745638.3800000101</v>
       </c>
     </row>
   </sheetData>

--- a/copa_copilot_datos.xlsx
+++ b/copa_copilot_datos.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30327"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://controlesempresarialesltda-my.sharepoint.com/personal/marango_coem_co/Documents/GitHub/COEM/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="444" documentId="11_7B0F6A10CFB5B9B3AED9E795B9A4719BFA1CF949" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{03890D6E-556B-4CB6-9E90-C8D700F67107}"/>
+  <xr:revisionPtr revIDLastSave="446" documentId="11_7B0F6A10CFB5B9B3AED9E795B9A4719BFA1CF949" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9EEF3065-3BCC-436D-8455-D35AD5705552}"/>
   <bookViews>
-    <workbookView minimized="1" xWindow="24" yWindow="24" windowWidth="23016" windowHeight="12216" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView minimized="1" xWindow="120" yWindow="120" windowWidth="23016" windowHeight="12216" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Copa Copilot" sheetId="1" r:id="rId1"/>
@@ -73,58 +73,58 @@
     <t>ECHEVERRY SANDRA</t>
   </si>
   <si>
+    <t>NN OCCIDE_SMC_001 1</t>
+  </si>
+  <si>
+    <t>CHARRY OCHOA VIVIANA ANDREA</t>
+  </si>
+  <si>
+    <t>ESPINOSA ORTIZ DEISON FERNANDO</t>
+  </si>
+  <si>
+    <t>Vendedor</t>
+  </si>
+  <si>
+    <t>% Cump</t>
+  </si>
+  <si>
+    <t>Gap</t>
+  </si>
+  <si>
+    <t>COLLAZOS PRIETO JUAN FELIPE</t>
+  </si>
+  <si>
+    <t>NN OCCIDE_SMC_001 2</t>
+  </si>
+  <si>
+    <t>SOTO FERNANDO</t>
+  </si>
+  <si>
+    <t>DIRECTOS CALI DIRECTOS CALI</t>
+  </si>
+  <si>
+    <t>LOZANO GARCIA JULIO ERNESTO</t>
+  </si>
+  <si>
+    <t>VALERO VELA LUZ EDIT</t>
+  </si>
+  <si>
+    <t>Clasificado</t>
+  </si>
+  <si>
+    <t>En Carrera</t>
+  </si>
+  <si>
+    <t>Valle de la oportunidad</t>
+  </si>
+  <si>
     <t>NN OCCIDE_ENTER_001 1</t>
   </si>
   <si>
-    <t>NN OCCIDE_SMC_001 2</t>
-  </si>
-  <si>
-    <t>NN OCCIDE_SMC_001 1</t>
-  </si>
-  <si>
     <t>CAMACHO BENAVIDES RUBEN DARIO</t>
   </si>
   <si>
-    <t>ESPINOSA ORTIZ DEISON FERNANDO</t>
-  </si>
-  <si>
-    <t>CHARRY OCHOA VIVIANA ANDREA</t>
-  </si>
-  <si>
     <t>NN OCCIDE_CORPO_001 1</t>
-  </si>
-  <si>
-    <t>Vendedor</t>
-  </si>
-  <si>
-    <t>% Cump</t>
-  </si>
-  <si>
-    <t>Gap</t>
-  </si>
-  <si>
-    <t>COLLAZOS PRIETO JUAN FELIPE</t>
-  </si>
-  <si>
-    <t>SOTO FERNANDO</t>
-  </si>
-  <si>
-    <t>VALERO VELA LUZ EDIT</t>
-  </si>
-  <si>
-    <t>DIRECTOS CALI DIRECTOS CALI</t>
-  </si>
-  <si>
-    <t>LOZANO GARCIA JULIO ERNESTO</t>
-  </si>
-  <si>
-    <t>Clasificado</t>
-  </si>
-  <si>
-    <t>En Carrera</t>
-  </si>
-  <si>
-    <t>Valle de la oportunidad</t>
   </si>
 </sst>
 </file>
@@ -132,11 +132,11 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="3">
-    <numFmt numFmtId="164" formatCode="&quot;$&quot;\ #,##0;[Red]\-&quot;$&quot;\ #,##0"/>
-    <numFmt numFmtId="165" formatCode="&quot;$&quot;#,##0"/>
-    <numFmt numFmtId="166" formatCode="&quot;$&quot;#,##0;[Red]\-&quot;$&quot;#,##0"/>
+    <numFmt numFmtId="6" formatCode="&quot;$&quot;\ #,##0;[Red]\-&quot;$&quot;\ #,##0"/>
+    <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0"/>
+    <numFmt numFmtId="165" formatCode="&quot;$&quot;#,##0;[Red]\-&quot;$&quot;#,##0"/>
   </numFmts>
-  <fonts count="7">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -149,6 +149,7 @@
       <sz val="12"/>
       <color rgb="FFFFD700"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="8"/>
@@ -249,7 +250,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="6" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -260,8 +261,8 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -269,9 +270,9 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="166" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="6" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="165" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
@@ -288,6 +289,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -576,18 +581,18 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:G12"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="14.45"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="6" customWidth="1"/>
-    <col min="2" max="2" width="36.85546875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="19.140625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.5703125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.140625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="13.28515625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="17.140625" customWidth="1"/>
+    <col min="2" max="2" width="36.88671875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="19.109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.5546875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.109375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="13.33203125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="17.109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="15.6">
+    <row r="1" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -610,7 +615,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:7" ht="15">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A2" s="2">
         <v>1</v>
       </c>
@@ -633,7 +638,7 @@
         <v>173905.75999927521</v>
       </c>
     </row>
-    <row r="3" spans="1:7" ht="15">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3" s="2">
         <v>2</v>
       </c>
@@ -656,7 +661,7 @@
         <v>1223568.8700000048</v>
       </c>
     </row>
-    <row r="4" spans="1:7" ht="15">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A4" s="2">
         <v>3</v>
       </c>
@@ -679,7 +684,7 @@
         <v>10983523.560000002</v>
       </c>
     </row>
-    <row r="5" spans="1:7" ht="15">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A5" s="2">
         <v>4</v>
       </c>
@@ -702,12 +707,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:7" ht="15">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A6" s="2">
         <v>5</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>11</v>
+        <v>26</v>
       </c>
       <c r="C6" s="4">
         <v>0</v>
@@ -725,12 +730,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:7" ht="15">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A7" s="2">
         <v>6</v>
       </c>
       <c r="B7" s="7" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="C7" s="4"/>
       <c r="D7" s="8">
@@ -746,12 +751,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:7" ht="15">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A8" s="2">
         <v>7</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C8" s="4">
         <v>0</v>
@@ -769,12 +774,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:7" ht="15">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A9" s="2">
         <v>8</v>
       </c>
       <c r="B9" s="7" t="s">
-        <v>14</v>
+        <v>27</v>
       </c>
       <c r="C9" s="4"/>
       <c r="D9" s="8">
@@ -790,12 +795,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:7" ht="15">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A10" s="2">
         <v>9</v>
       </c>
       <c r="B10" s="7" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C10" s="4"/>
       <c r="D10" s="8">
@@ -811,9 +816,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:7" ht="15">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A11" s="2">
+        <v>10</v>
+      </c>
       <c r="B11" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="D11">
         <v>0</v>
@@ -828,9 +836,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:7" ht="15">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A12" s="2">
+        <v>11</v>
+      </c>
       <c r="B12" t="s">
-        <v>17</v>
+        <v>28</v>
       </c>
       <c r="C12">
         <v>0</v>
@@ -858,21 +869,21 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:E17"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="14.45"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="41.28515625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="41.33203125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="17" customWidth="1"/>
-    <col min="3" max="3" width="21.140625" customWidth="1"/>
+    <col min="3" max="3" width="21.109375" customWidth="1"/>
     <col min="4" max="4" width="20" customWidth="1"/>
-    <col min="5" max="5" width="16.7109375" customWidth="1"/>
+    <col min="5" max="5" width="16.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1" s="10" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="B1" s="10" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="C1" s="10" t="s">
         <v>3</v>
@@ -881,10 +892,10 @@
         <v>4</v>
       </c>
       <c r="E1" s="10" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5" ht="15">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2" s="7" t="s">
         <v>8</v>
       </c>
@@ -901,7 +912,7 @@
         <v>31185057.29666926</v>
       </c>
     </row>
-    <row r="3" spans="1:5" ht="15">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A3" s="7" t="s">
         <v>9</v>
       </c>
@@ -918,7 +929,7 @@
         <v>-139355913.43665707</v>
       </c>
     </row>
-    <row r="4" spans="1:5" ht="15">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A4" s="7" t="s">
         <v>7</v>
       </c>
@@ -935,7 +946,7 @@
         <v>-155109545.63665503</v>
       </c>
     </row>
-    <row r="5" spans="1:5" ht="15">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A5" s="7" t="s">
         <v>10</v>
       </c>
@@ -952,9 +963,9 @@
         <v>-330254339.70666027</v>
       </c>
     </row>
-    <row r="6" spans="1:5" ht="15">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A6" s="7" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="B6" s="4">
         <v>0.2172699243703719</v>
@@ -969,9 +980,9 @@
         <v>-105668560.20999902</v>
       </c>
     </row>
-    <row r="7" spans="1:5" ht="15">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A7" s="7" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="B7" s="4">
         <v>0.21633626109805204</v>
@@ -986,9 +997,9 @@
         <v>-99917126.709992483</v>
       </c>
     </row>
-    <row r="8" spans="1:5" ht="15">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A8" s="7" t="s">
-        <v>11</v>
+        <v>26</v>
       </c>
       <c r="B8" s="4">
         <v>0</v>
@@ -1003,9 +1014,9 @@
         <v>-506666666.66665965</v>
       </c>
     </row>
-    <row r="9" spans="1:5" ht="15">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A9" s="7" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="B9" s="4">
         <v>0</v>
@@ -1020,9 +1031,9 @@
         <v>-28333333.333327994</v>
       </c>
     </row>
-    <row r="10" spans="1:5" ht="15">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A10" s="7" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="B10" s="4"/>
       <c r="C10" s="8">
@@ -1035,9 +1046,9 @@
         <v>4801100</v>
       </c>
     </row>
-    <row r="11" spans="1:5" ht="15">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A11" s="7" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="B11" s="4">
         <v>0</v>
@@ -1052,9 +1063,9 @@
         <v>-44999999.999995992</v>
       </c>
     </row>
-    <row r="12" spans="1:5" ht="15">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A12" s="7" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B12" s="4"/>
       <c r="C12" s="8">
@@ -1067,9 +1078,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:5" ht="15">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A13" s="7" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="B13" s="4"/>
       <c r="C13" s="8">
@@ -1082,9 +1093,9 @@
         <v>95628322.180000007</v>
       </c>
     </row>
-    <row r="14" spans="1:5" ht="15">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A14" s="7" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="B14" s="4"/>
       <c r="C14" s="8">
@@ -1097,9 +1108,9 @@
         <v>-112955.9999999993</v>
       </c>
     </row>
-    <row r="15" spans="1:5" ht="15">
+    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A15" s="7" t="s">
-        <v>17</v>
+        <v>28</v>
       </c>
       <c r="B15" s="4">
         <v>0</v>
@@ -1114,9 +1125,9 @@
         <v>-245833333.33331487</v>
       </c>
     </row>
-    <row r="16" spans="1:5" ht="15">
+    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A16" s="7" t="s">
-        <v>14</v>
+        <v>27</v>
       </c>
       <c r="B16" s="4"/>
       <c r="C16" s="8">
@@ -1129,9 +1140,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:5" s="16" customFormat="1" ht="15">
+    <row r="17" spans="1:5" s="16" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A17" s="11" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="B17" s="12"/>
       <c r="C17" s="13">
@@ -1154,24 +1165,24 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9E6B92DB-9C5C-437E-84B0-C727C5D5C893}">
   <dimension ref="A1:A3"/>
-  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="14.45"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.44140625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="23.28515625" customWidth="1"/>
+    <col min="1" max="1" width="23.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="2" spans="1:1">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="3" spans="1:1">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
     </row>
   </sheetData>

--- a/copa_copilot_datos.xlsx
+++ b/copa_copilot_datos.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30327"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://controlesempresarialesltda-my.sharepoint.com/personal/marango_coem_co/Documents/GitHub/COEM/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="446" documentId="11_7B0F6A10CFB5B9B3AED9E795B9A4719BFA1CF949" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9EEF3065-3BCC-436D-8455-D35AD5705552}"/>
+  <xr:revisionPtr revIDLastSave="451" documentId="11_7B0F6A10CFB5B9B3AED9E795B9A4719BFA1CF949" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{44C75392-74F6-4559-A971-DD8771FBDF87}"/>
   <bookViews>
-    <workbookView minimized="1" xWindow="120" yWindow="120" windowWidth="23016" windowHeight="12216" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView minimized="1" xWindow="120" yWindow="120" windowWidth="23016" windowHeight="12216" firstSheet="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Copa Copilot" sheetId="1" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="29">
   <si>
     <t>Pos</t>
   </si>
@@ -73,12 +73,27 @@
     <t>ECHEVERRY SANDRA</t>
   </si>
   <si>
+    <t>NN OCCIDE_CORPO_001 1</t>
+  </si>
+  <si>
     <t>NN OCCIDE_SMC_001 1</t>
   </si>
   <si>
+    <t>NN OCCIDE_ENTER_001 1</t>
+  </si>
+  <si>
+    <t>COLLAZOS PRIETO JUAN FELIPE</t>
+  </si>
+  <si>
+    <t>NN OCCIDE_SMC_001 2</t>
+  </si>
+  <si>
     <t>CHARRY OCHOA VIVIANA ANDREA</t>
   </si>
   <si>
+    <t>CAMACHO BENAVIDES RUBEN DARIO</t>
+  </si>
+  <si>
     <t>ESPINOSA ORTIZ DEISON FERNANDO</t>
   </si>
   <si>
@@ -91,24 +106,18 @@
     <t>Gap</t>
   </si>
   <si>
-    <t>COLLAZOS PRIETO JUAN FELIPE</t>
-  </si>
-  <si>
-    <t>NN OCCIDE_SMC_001 2</t>
-  </si>
-  <si>
     <t>SOTO FERNANDO</t>
   </si>
   <si>
+    <t>VALERO VELA LUZ EDIT</t>
+  </si>
+  <si>
     <t>DIRECTOS CALI DIRECTOS CALI</t>
   </si>
   <si>
     <t>LOZANO GARCIA JULIO ERNESTO</t>
   </si>
   <si>
-    <t>VALERO VELA LUZ EDIT</t>
-  </si>
-  <si>
     <t>Clasificado</t>
   </si>
   <si>
@@ -116,15 +125,6 @@
   </si>
   <si>
     <t>Valle de la oportunidad</t>
-  </si>
-  <si>
-    <t>NN OCCIDE_ENTER_001 1</t>
-  </si>
-  <si>
-    <t>CAMACHO BENAVIDES RUBEN DARIO</t>
-  </si>
-  <si>
-    <t>NN OCCIDE_CORPO_001 1</t>
   </si>
 </sst>
 </file>
@@ -132,11 +132,11 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="3">
-    <numFmt numFmtId="6" formatCode="&quot;$&quot;\ #,##0;[Red]\-&quot;$&quot;\ #,##0"/>
-    <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0"/>
-    <numFmt numFmtId="165" formatCode="&quot;$&quot;#,##0;[Red]\-&quot;$&quot;#,##0"/>
+    <numFmt numFmtId="164" formatCode="&quot;$&quot;\ #,##0;[Red]\-&quot;$&quot;\ #,##0"/>
+    <numFmt numFmtId="165" formatCode="&quot;$&quot;#,##0"/>
+    <numFmt numFmtId="166" formatCode="&quot;$&quot;#,##0;[Red]\-&quot;$&quot;#,##0"/>
   </numFmts>
-  <fonts count="7" x14ac:knownFonts="1">
+  <fonts count="6">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -161,13 +161,6 @@
       <b/>
       <sz val="11"/>
       <color rgb="FF000000"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="12"/>
-      <color rgb="FFFFD700"/>
       <name val="Calibri"/>
       <family val="2"/>
     </font>
@@ -242,7 +235,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -250,30 +243,20 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="6" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
+    <xf numFmtId="166" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="6" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="165" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -289,10 +272,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -580,248 +559,250 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G12"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:G13"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="14.45"/>
   <cols>
     <col min="1" max="1" width="6" customWidth="1"/>
-    <col min="2" max="2" width="36.88671875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="19.109375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.5546875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.109375" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="13.33203125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="17.109375" customWidth="1"/>
+    <col min="2" max="2" width="36.85546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="19.140625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.5703125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.140625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="13.28515625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="17.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7" ht="15.6">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="5" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="5" t="s">
+      <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="5" t="s">
+      <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="5" t="s">
+      <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="6" t="s">
+      <c r="G1" s="10" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:7" ht="15">
       <c r="A2" s="2">
         <v>1</v>
       </c>
-      <c r="B2" s="7" t="s">
+      <c r="B2" s="5" t="s">
         <v>7</v>
       </c>
       <c r="C2" s="4">
         <v>2.2860202013538915</v>
       </c>
-      <c r="D2" s="8">
-        <v>54166666.666665599</v>
+      <c r="D2" s="6">
+        <v>54166666.666665591</v>
       </c>
       <c r="E2" s="3">
         <v>123826094.24000072</v>
       </c>
-      <c r="F2">
-        <v>124000000</v>
-      </c>
-      <c r="G2">
-        <v>173905.75999927521</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="F2" s="7">
+        <v>123826094.24000072</v>
+      </c>
+      <c r="G2" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" ht="15">
       <c r="A3" s="2">
         <v>2</v>
       </c>
-      <c r="B3" s="7" t="s">
+      <c r="B3" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C3" s="4">
-        <v>0.46658586780001304</v>
-      </c>
-      <c r="D3" s="8">
+        <v>0.639637767600018</v>
+      </c>
+      <c r="D3" s="6">
         <v>16666666.6666662</v>
       </c>
       <c r="E3" s="3">
-        <v>7776431.1299999952</v>
-      </c>
-      <c r="F3">
-        <v>9000000</v>
-      </c>
-      <c r="G3">
-        <v>1223568.8700000048</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
+        <v>10660629.459999993</v>
+      </c>
+      <c r="F3" s="7">
+        <v>10660629.459999993</v>
+      </c>
+      <c r="G3" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" ht="15">
       <c r="A4" s="2">
         <v>3</v>
       </c>
-      <c r="B4" s="7" t="s">
+      <c r="B4" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C4" s="4">
-        <v>0.34126075503158271</v>
-      </c>
-      <c r="D4" s="8">
-        <v>79166666.666665792</v>
+        <v>0.52079148189474245</v>
+      </c>
+      <c r="D4" s="6">
+        <v>79166666.666665807</v>
       </c>
       <c r="E4" s="3">
-        <v>27016476.439999998</v>
-      </c>
-      <c r="F4">
-        <v>38000000</v>
-      </c>
-      <c r="G4">
-        <v>10983523.560000002</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
+        <v>41229325.649999991</v>
+      </c>
+      <c r="F4" s="7">
+        <v>41229325.649999991</v>
+      </c>
+      <c r="G4" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" ht="15">
       <c r="A5" s="2">
         <v>4</v>
       </c>
-      <c r="B5" s="7" t="s">
+      <c r="B5" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C5" s="4">
         <v>0.13657475911579028</v>
       </c>
-      <c r="D5" s="8">
+      <c r="D5" s="6">
         <v>79166666.666666195</v>
       </c>
       <c r="E5" s="3">
         <v>10812168.430000007</v>
       </c>
-      <c r="F5">
+      <c r="F5" s="7">
         <v>10812168.430000007</v>
       </c>
-      <c r="G5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="G5" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" ht="15">
       <c r="A6" s="2">
         <v>5</v>
       </c>
-      <c r="B6" s="7" t="s">
-        <v>26</v>
+      <c r="B6" s="5" t="s">
+        <v>11</v>
       </c>
       <c r="C6" s="4">
         <v>0</v>
       </c>
-      <c r="D6" s="8">
-        <v>79166666.66666621</v>
+      <c r="D6" s="6">
+        <v>58333333.333329804</v>
       </c>
       <c r="E6" s="3">
         <v>0</v>
       </c>
-      <c r="F6">
-        <v>0</v>
-      </c>
-      <c r="G6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="F6" s="7">
+        <v>0</v>
+      </c>
+      <c r="G6" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" ht="15">
       <c r="A7" s="2">
         <v>6</v>
       </c>
-      <c r="B7" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="C7" s="4"/>
-      <c r="D7" s="8">
-        <v>0</v>
+      <c r="B7" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="C7" s="4">
+        <v>0</v>
+      </c>
+      <c r="D7" s="6">
+        <v>25000000.000000104</v>
       </c>
       <c r="E7" s="3">
         <v>0</v>
       </c>
-      <c r="F7">
-        <v>0</v>
-      </c>
-      <c r="G7">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="F7" s="7">
+        <v>0</v>
+      </c>
+      <c r="G7" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" ht="15">
       <c r="A8" s="2">
         <v>7</v>
       </c>
-      <c r="B8" s="7" t="s">
-        <v>11</v>
+      <c r="B8" s="5" t="s">
+        <v>13</v>
       </c>
       <c r="C8" s="4">
         <v>0</v>
       </c>
-      <c r="D8" s="8">
-        <v>25000000.000000089</v>
+      <c r="D8" s="6">
+        <v>79166666.666666195</v>
       </c>
       <c r="E8" s="3">
         <v>0</v>
       </c>
-      <c r="F8">
-        <v>0</v>
-      </c>
-      <c r="G8">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="F8" s="7">
+        <v>0</v>
+      </c>
+      <c r="G8" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" ht="15">
       <c r="A9" s="2">
         <v>8</v>
       </c>
-      <c r="B9" s="7" t="s">
-        <v>27</v>
+      <c r="B9" s="5" t="s">
+        <v>14</v>
       </c>
       <c r="C9" s="4"/>
-      <c r="D9" s="8">
+      <c r="D9" s="6">
         <v>0</v>
       </c>
       <c r="E9" s="3">
         <v>0</v>
       </c>
-      <c r="F9">
-        <v>0</v>
-      </c>
-      <c r="G9">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="F9" s="7">
+        <v>0</v>
+      </c>
+      <c r="G9" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" ht="15">
       <c r="A10" s="2">
         <v>9</v>
       </c>
-      <c r="B10" s="7" t="s">
-        <v>13</v>
+      <c r="B10" s="5" t="s">
+        <v>15</v>
       </c>
       <c r="C10" s="4"/>
-      <c r="D10" s="8">
+      <c r="D10" s="6">
         <v>0</v>
       </c>
       <c r="E10" s="3">
-        <v>67216.850000000093</v>
-      </c>
-      <c r="F10">
-        <v>67216.850000000093</v>
-      </c>
-      <c r="G10">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
+        <v>0</v>
+      </c>
+      <c r="F10" s="7">
+        <v>0</v>
+      </c>
+      <c r="G10" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" ht="15">
       <c r="A11" s="2">
         <v>10</v>
       </c>
       <c r="B11" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="D11">
         <v>0</v>
@@ -829,33 +810,47 @@
       <c r="E11">
         <v>-112955.9999999993</v>
       </c>
-      <c r="F11">
+      <c r="F11" s="7">
         <v>-112955.9999999993</v>
       </c>
-      <c r="G11">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="G11" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" ht="15">
       <c r="A12" s="2">
         <v>11</v>
       </c>
       <c r="B12" t="s">
-        <v>28</v>
-      </c>
-      <c r="C12">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="D12">
-        <v>58333333.333329812</v>
+        <v>0</v>
       </c>
       <c r="E12">
         <v>0</v>
       </c>
-      <c r="F12">
-        <v>0</v>
-      </c>
-      <c r="G12">
+      <c r="F12" s="7">
+        <v>0</v>
+      </c>
+      <c r="G12" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" ht="15">
+      <c r="B13" t="s">
+        <v>18</v>
+      </c>
+      <c r="D13">
+        <v>0</v>
+      </c>
+      <c r="E13">
+        <v>67216.850000000093</v>
+      </c>
+      <c r="F13" s="7">
+        <v>67216.850000000093</v>
+      </c>
+      <c r="G13" s="3">
         <v>0</v>
       </c>
     </row>
@@ -869,289 +864,289 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:E17"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="14.45"/>
   <cols>
-    <col min="1" max="1" width="41.33203125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="41.28515625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="17" customWidth="1"/>
-    <col min="3" max="3" width="21.109375" customWidth="1"/>
+    <col min="3" max="3" width="21.140625" customWidth="1"/>
     <col min="4" max="4" width="20" customWidth="1"/>
-    <col min="5" max="5" width="16.6640625" customWidth="1"/>
+    <col min="5" max="5" width="16.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A1" s="10" t="s">
-        <v>14</v>
-      </c>
-      <c r="B1" s="10" t="s">
-        <v>15</v>
-      </c>
-      <c r="C1" s="10" t="s">
+    <row r="1" spans="1:5">
+      <c r="A1" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="B1" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="C1" s="8" t="s">
         <v>3</v>
       </c>
-      <c r="D1" s="10" t="s">
+      <c r="D1" s="8" t="s">
         <v>4</v>
       </c>
-      <c r="E1" s="10" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A2" s="7" t="s">
+      <c r="E1" s="8" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" ht="15">
+      <c r="A2" s="5" t="s">
         <v>8</v>
       </c>
       <c r="B2" s="4">
-        <v>1.5346009822286402</v>
-      </c>
-      <c r="C2" s="8">
+        <v>1.5840443821714993</v>
+      </c>
+      <c r="C2" s="6">
         <v>58333333.333330736</v>
       </c>
       <c r="D2" s="3">
-        <v>89518390.629999995</v>
-      </c>
-      <c r="E2" s="9">
-        <v>31185057.29666926</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A3" s="7" t="s">
+        <v>92402588.959999919</v>
+      </c>
+      <c r="E2" s="7">
+        <v>34069255.626669183</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" ht="15">
+      <c r="A3" s="5" t="s">
         <v>9</v>
       </c>
       <c r="B3" s="4">
-        <v>0.72495543400659257</v>
-      </c>
-      <c r="C3" s="8">
-        <v>506666666.66665709</v>
+        <v>0.75300711007896193</v>
+      </c>
+      <c r="C3" s="6">
+        <v>506666666.66665697</v>
       </c>
       <c r="D3" s="3">
-        <v>367310753.23000002</v>
-      </c>
-      <c r="E3" s="9">
-        <v>-139355913.43665707</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A4" s="7" t="s">
+        <v>381523602.43999887</v>
+      </c>
+      <c r="E3" s="7">
+        <v>-125143064.22665811</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" ht="15">
+      <c r="A4" s="5" t="s">
         <v>7</v>
       </c>
       <c r="B4" s="4">
-        <v>0.55256861835578663</v>
-      </c>
-      <c r="C4" s="8">
-        <v>346666666.66665572</v>
+        <v>0.55256861835578641</v>
+      </c>
+      <c r="C4" s="6">
+        <v>346666666.66665584</v>
       </c>
       <c r="D4" s="3">
-        <v>191557121.03000069</v>
-      </c>
-      <c r="E4" s="9">
-        <v>-155109545.63665503</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A5" s="7" t="s">
+        <v>191557121.02999973</v>
+      </c>
+      <c r="E4" s="7">
+        <v>-155109545.63665611</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" ht="15">
+      <c r="A5" s="5" t="s">
         <v>10</v>
       </c>
       <c r="B5" s="4">
-        <v>0.34818222426316259</v>
-      </c>
-      <c r="C5" s="8">
-        <v>506666666.66665983</v>
+        <v>0.3481822242631627</v>
+      </c>
+      <c r="C5" s="6">
+        <v>506666666.66665971</v>
       </c>
       <c r="D5" s="3">
-        <v>176412326.95999956</v>
-      </c>
-      <c r="E5" s="9">
-        <v>-330254339.70666027</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A6" s="7" t="s">
-        <v>13</v>
+        <v>176412326.96000099</v>
+      </c>
+      <c r="E5" s="7">
+        <v>-330254339.70665872</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" ht="15">
+      <c r="A6" s="5" t="s">
+        <v>18</v>
       </c>
       <c r="B6" s="4">
         <v>0.2172699243703719</v>
       </c>
-      <c r="C6" s="8">
+      <c r="C6" s="6">
         <v>134999999.99999905</v>
       </c>
       <c r="D6" s="3">
         <v>29331439.790000021</v>
       </c>
-      <c r="E6" s="9">
+      <c r="E6" s="7">
         <v>-105668560.20999902</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A7" s="7" t="s">
-        <v>17</v>
+    <row r="7" spans="1:5" ht="15">
+      <c r="A7" s="5" t="s">
+        <v>14</v>
       </c>
       <c r="B7" s="4">
-        <v>0.21633626109805204</v>
-      </c>
-      <c r="C7" s="8">
-        <v>127499999.99999245</v>
+        <v>0.21633626109805201</v>
+      </c>
+      <c r="C7" s="6">
+        <v>127499999.99999247</v>
       </c>
       <c r="D7" s="3">
-        <v>27582873.289999962</v>
-      </c>
-      <c r="E7" s="9">
+        <v>27582873.289999992</v>
+      </c>
+      <c r="E7" s="7">
         <v>-99917126.709992483</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A8" s="7" t="s">
-        <v>26</v>
+    <row r="8" spans="1:5" ht="15">
+      <c r="A8" s="5" t="s">
+        <v>13</v>
       </c>
       <c r="B8" s="4">
         <v>0</v>
       </c>
-      <c r="C8" s="8">
-        <v>506666666.66665965</v>
+      <c r="C8" s="6">
+        <v>506666666.66665989</v>
       </c>
       <c r="D8" s="3">
         <v>0</v>
       </c>
-      <c r="E8" s="9">
-        <v>-506666666.66665965</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A9" s="7" t="s">
-        <v>18</v>
+      <c r="E8" s="7">
+        <v>-506666666.66665989</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" ht="15">
+      <c r="A9" s="5" t="s">
+        <v>15</v>
       </c>
       <c r="B9" s="4">
         <v>0</v>
       </c>
-      <c r="C9" s="8">
-        <v>28333333.333327994</v>
+      <c r="C9" s="6">
+        <v>28333333.333328031</v>
       </c>
       <c r="D9" s="3">
         <v>0</v>
       </c>
-      <c r="E9" s="9">
-        <v>-28333333.333327994</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A10" s="7" t="s">
-        <v>19</v>
+      <c r="E9" s="7">
+        <v>-28333333.333328031</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" ht="15">
+      <c r="A10" s="5" t="s">
+        <v>22</v>
       </c>
       <c r="B10" s="4"/>
-      <c r="C10" s="8">
+      <c r="C10" s="6">
         <v>0</v>
       </c>
       <c r="D10" s="3">
         <v>4801100</v>
       </c>
-      <c r="E10" s="9">
+      <c r="E10" s="7">
         <v>4801100</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A11" s="7" t="s">
-        <v>11</v>
+    <row r="11" spans="1:5" ht="15">
+      <c r="A11" s="5" t="s">
+        <v>12</v>
       </c>
       <c r="B11" s="4">
         <v>0</v>
       </c>
-      <c r="C11" s="8">
-        <v>44999999.999995992</v>
+      <c r="C11" s="6">
+        <v>44999999.999995999</v>
       </c>
       <c r="D11" s="3">
         <v>0</v>
       </c>
-      <c r="E11" s="9">
-        <v>-44999999.999995992</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A12" s="7" t="s">
-        <v>22</v>
+      <c r="E11" s="7">
+        <v>-44999999.999995999</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" ht="15">
+      <c r="A12" s="5" t="s">
+        <v>23</v>
       </c>
       <c r="B12" s="4"/>
-      <c r="C12" s="8">
+      <c r="C12" s="6">
         <v>0</v>
       </c>
       <c r="D12" s="3">
         <v>0</v>
       </c>
-      <c r="E12" s="9">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A13" s="7" t="s">
-        <v>20</v>
+      <c r="E12" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" ht="15">
+      <c r="A13" s="5" t="s">
+        <v>24</v>
       </c>
       <c r="B13" s="4"/>
-      <c r="C13" s="8">
+      <c r="C13" s="6">
         <v>0</v>
       </c>
       <c r="D13" s="3">
         <v>95628322.180000007</v>
       </c>
-      <c r="E13" s="9">
+      <c r="E13" s="7">
         <v>95628322.180000007</v>
       </c>
     </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A14" s="7" t="s">
-        <v>12</v>
+    <row r="14" spans="1:5" ht="15">
+      <c r="A14" s="5" t="s">
+        <v>16</v>
       </c>
       <c r="B14" s="4"/>
-      <c r="C14" s="8">
+      <c r="C14" s="6">
         <v>0</v>
       </c>
       <c r="D14" s="3">
         <v>-112955.9999999993</v>
       </c>
-      <c r="E14" s="9">
+      <c r="E14" s="7">
         <v>-112955.9999999993</v>
       </c>
     </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A15" s="7" t="s">
-        <v>28</v>
+    <row r="15" spans="1:5" ht="15">
+      <c r="A15" s="5" t="s">
+        <v>11</v>
       </c>
       <c r="B15" s="4">
         <v>0</v>
       </c>
-      <c r="C15" s="8">
-        <v>245833333.33331487</v>
+      <c r="C15" s="6">
+        <v>245833333.3333151</v>
       </c>
       <c r="D15" s="3">
         <v>0</v>
       </c>
-      <c r="E15" s="9">
-        <v>-245833333.33331487</v>
-      </c>
-    </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A16" s="7" t="s">
-        <v>27</v>
+      <c r="E15" s="7">
+        <v>-245833333.3333151</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" ht="15">
+      <c r="A16" s="5" t="s">
+        <v>17</v>
       </c>
       <c r="B16" s="4"/>
-      <c r="C16" s="8">
+      <c r="C16" s="6">
         <v>0</v>
       </c>
       <c r="D16" s="3">
         <v>0</v>
       </c>
-      <c r="E16" s="9">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5" s="16" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="11" t="s">
-        <v>21</v>
-      </c>
-      <c r="B17" s="12"/>
-      <c r="C17" s="13">
-        <v>0</v>
-      </c>
-      <c r="D17" s="14">
+      <c r="E16" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" ht="15">
+      <c r="A17" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="B17" s="4"/>
+      <c r="C17" s="6">
+        <v>0</v>
+      </c>
+      <c r="D17" s="3">
         <v>9745638.3800000101</v>
       </c>
-      <c r="E17" s="15">
+      <c r="E17" s="9">
         <v>9745638.3800000101</v>
       </c>
     </row>
@@ -1165,24 +1160,24 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9E6B92DB-9C5C-437E-84B0-C727C5D5C893}">
   <dimension ref="A1:A3"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.44140625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="14.45"/>
   <cols>
-    <col min="1" max="1" width="23.33203125" customWidth="1"/>
+    <col min="1" max="1" width="23.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:1">
       <c r="A1" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1">
       <c r="A2" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.3">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1">
       <c r="A3" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
     </row>
   </sheetData>

--- a/copa_copilot_datos.xlsx
+++ b/copa_copilot_datos.xlsx
@@ -1,21 +1,23 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30327"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://controlesempresarialesltda-my.sharepoint.com/personal/marango_coem_co/Documents/GitHub/COEM/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="451" documentId="11_7B0F6A10CFB5B9B3AED9E795B9A4719BFA1CF949" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{44C75392-74F6-4559-A971-DD8771FBDF87}"/>
+  <xr:revisionPtr revIDLastSave="481" documentId="11_7B0F6A10CFB5B9B3AED9E795B9A4719BFA1CF949" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7AEA0780-7C84-4719-9BCB-39F780251E5F}"/>
   <bookViews>
-    <workbookView minimized="1" xWindow="120" yWindow="120" windowWidth="23016" windowHeight="12216" firstSheet="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Copa Copilot" sheetId="1" r:id="rId1"/>
     <sheet name="Actividad Semanal" sheetId="2" r:id="rId2"/>
     <sheet name="Estados" sheetId="3" r:id="rId3"/>
+    <sheet name="Dominios Acumulado" sheetId="4" r:id="rId4"/>
+    <sheet name="Dominio Mes" sheetId="5" r:id="rId5"/>
   </sheets>
   <calcPr calcId="191028"/>
   <extLst>
@@ -38,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="95" uniqueCount="50">
   <si>
     <t>Pos</t>
   </si>
@@ -125,18 +127,85 @@
   </si>
   <si>
     <t>Valle de la oportunidad</t>
+  </si>
+  <si>
+    <t>2025</t>
+  </si>
+  <si>
+    <t>2026</t>
+  </si>
+  <si>
+    <t>Etiquetas de fila</t>
+  </si>
+  <si>
+    <t>Volumen</t>
+  </si>
+  <si>
+    <t>% UB</t>
+  </si>
+  <si>
+    <t>Y to Y Ub</t>
+  </si>
+  <si>
+    <t>%crec/dec</t>
+  </si>
+  <si>
+    <t>VALLE</t>
+  </si>
+  <si>
+    <t>SECURITY MS</t>
+  </si>
+  <si>
+    <t>CYBERSECURITY &amp; NETWORKING</t>
+  </si>
+  <si>
+    <t>AI BUSINESS SOLUTIONS</t>
+  </si>
+  <si>
+    <t>XAAS</t>
+  </si>
+  <si>
+    <t>DATA CENTER &amp; CLOUD</t>
+  </si>
+  <si>
+    <t>CLOUD &amp; AI PLATFORMS</t>
+  </si>
+  <si>
+    <t>SERVICIOS COEM</t>
+  </si>
+  <si>
+    <t>WORKSPACE</t>
+  </si>
+  <si>
+    <t>NO DOMAIN</t>
+  </si>
+  <si>
+    <t>DIGITAL TRANSFORMATION</t>
+  </si>
+  <si>
+    <t>Total VALLE</t>
+  </si>
+  <si>
+    <t>Etiquetas de columna</t>
+  </si>
+  <si>
+    <t>% Part</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="3">
-    <numFmt numFmtId="164" formatCode="&quot;$&quot;\ #,##0;[Red]\-&quot;$&quot;\ #,##0"/>
+  <numFmts count="7">
+    <numFmt numFmtId="6" formatCode="&quot;$&quot;\ #,##0;[Red]\-&quot;$&quot;\ #,##0"/>
+    <numFmt numFmtId="164" formatCode="_-* #,##0\ &quot;€&quot;_-;\-* #,##0\ &quot;€&quot;_-;_-* &quot;-&quot;\ &quot;€&quot;_-;_-@_-"/>
     <numFmt numFmtId="165" formatCode="&quot;$&quot;#,##0"/>
     <numFmt numFmtId="166" formatCode="&quot;$&quot;#,##0;[Red]\-&quot;$&quot;#,##0"/>
+    <numFmt numFmtId="167" formatCode="&quot;$&quot;\ #,##0"/>
+    <numFmt numFmtId="168" formatCode="_-&quot;$&quot;\ * #,##0_-;\-&quot;$&quot;\ * #,##0_-;_-&quot;$&quot;\ * &quot;-&quot;_-;_-@_-"/>
+    <numFmt numFmtId="171" formatCode="_-&quot;$&quot;* #,##0.00_-;\-&quot;$&quot;* #,##0.00_-;_-&quot;$&quot;* &quot;-&quot;??_-;_-@_-"/>
   </numFmts>
-  <fonts count="6">
+  <fonts count="9" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -177,8 +246,31 @@
       <name val="Aptos Narrow"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="4">
+  <fills count="8">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -193,6 +285,30 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="4" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC000"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.59999389629810485"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -232,10 +348,15 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="171" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="168" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="171" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="61">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -243,7 +364,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="6" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -257,9 +378,100 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="167" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="3" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="166" fontId="7" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="9" fontId="7" fillId="4" borderId="0" xfId="2" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" indent="1"/>
+    </xf>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="9" fontId="7" fillId="0" borderId="0" xfId="2" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="167" fontId="0" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="3" fontId="0" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="166" fontId="7" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="9" fontId="7" fillId="5" borderId="0" xfId="2" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="164" fontId="7" fillId="6" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="7" fillId="6" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="10" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="10" fontId="8" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="168" fontId="7" fillId="7" borderId="0" xfId="4" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="7" fillId="7" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" indent="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="7" fillId="0" borderId="0" xfId="2" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="167" fontId="0" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="3" fontId="0" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="166" fontId="7" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="9" fontId="7" fillId="5" borderId="0" xfId="2" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="167" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="3" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="166" fontId="7" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="9" fontId="7" fillId="4" borderId="0" xfId="2" applyFont="1" applyFill="1"/>
+    <xf numFmtId="10" fontId="0" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="6">
+    <cellStyle name="Moneda [0]" xfId="1" builtinId="7"/>
+    <cellStyle name="Moneda [0] 2" xfId="4" xr:uid="{0CCB16E3-81C2-4951-B834-94F35D3AC9B1}"/>
+    <cellStyle name="Moneda 2" xfId="3" xr:uid="{E3481F5F-7FEF-4617-8D16-A7A96E887278}"/>
+    <cellStyle name="Moneda 3" xfId="5" xr:uid="{F307236A-65B4-4AB6-879A-D24F4D74FE5A}"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Porcentaje" xfId="2" builtinId="5"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
@@ -560,18 +772,18 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:G13"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="14.45"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.1796875" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="6" customWidth="1"/>
-    <col min="2" max="2" width="36.85546875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="19.140625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.5703125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.140625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="13.28515625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="17.140625" customWidth="1"/>
+    <col min="2" max="2" width="36.81640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="19.1796875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.54296875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.1796875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="13.26953125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="17.1796875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="15.6">
+    <row r="1" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -594,7 +806,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:7" ht="15">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A2" s="2">
         <v>1</v>
       </c>
@@ -617,7 +829,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:7" ht="15">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A3" s="2">
         <v>2</v>
       </c>
@@ -640,7 +852,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:7" ht="15">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A4" s="2">
         <v>3</v>
       </c>
@@ -663,7 +875,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:7" ht="15">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A5" s="2">
         <v>4</v>
       </c>
@@ -686,7 +898,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:7" ht="15">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A6" s="2">
         <v>5</v>
       </c>
@@ -709,7 +921,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:7" ht="15">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A7" s="2">
         <v>6</v>
       </c>
@@ -732,7 +944,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:7" ht="15">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A8" s="2">
         <v>7</v>
       </c>
@@ -755,7 +967,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:7" ht="15">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A9" s="2">
         <v>8</v>
       </c>
@@ -776,7 +988,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:7" ht="15">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A10" s="2">
         <v>9</v>
       </c>
@@ -797,7 +1009,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:7" ht="15">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A11" s="2">
         <v>10</v>
       </c>
@@ -817,7 +1029,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:7" ht="15">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A12" s="2">
         <v>11</v>
       </c>
@@ -837,7 +1049,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:7" ht="15">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.35">
       <c r="B13" t="s">
         <v>18</v>
       </c>
@@ -864,16 +1076,16 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:E17"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="14.45"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.1796875" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="41.28515625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="41.26953125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="17" customWidth="1"/>
-    <col min="3" max="3" width="21.140625" customWidth="1"/>
+    <col min="3" max="3" width="21.1796875" customWidth="1"/>
     <col min="4" max="4" width="20" customWidth="1"/>
-    <col min="5" max="5" width="16.7109375" customWidth="1"/>
+    <col min="5" max="5" width="16.7265625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A1" s="8" t="s">
         <v>19</v>
       </c>
@@ -890,7 +1102,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="2" spans="1:5" ht="15">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A2" s="5" t="s">
         <v>8</v>
       </c>
@@ -907,7 +1119,7 @@
         <v>34069255.626669183</v>
       </c>
     </row>
-    <row r="3" spans="1:5" ht="15">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A3" s="5" t="s">
         <v>9</v>
       </c>
@@ -924,7 +1136,7 @@
         <v>-125143064.22665811</v>
       </c>
     </row>
-    <row r="4" spans="1:5" ht="15">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A4" s="5" t="s">
         <v>7</v>
       </c>
@@ -941,7 +1153,7 @@
         <v>-155109545.63665611</v>
       </c>
     </row>
-    <row r="5" spans="1:5" ht="15">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A5" s="5" t="s">
         <v>10</v>
       </c>
@@ -958,7 +1170,7 @@
         <v>-330254339.70665872</v>
       </c>
     </row>
-    <row r="6" spans="1:5" ht="15">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A6" s="5" t="s">
         <v>18</v>
       </c>
@@ -975,7 +1187,7 @@
         <v>-105668560.20999902</v>
       </c>
     </row>
-    <row r="7" spans="1:5" ht="15">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A7" s="5" t="s">
         <v>14</v>
       </c>
@@ -992,7 +1204,7 @@
         <v>-99917126.709992483</v>
       </c>
     </row>
-    <row r="8" spans="1:5" ht="15">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A8" s="5" t="s">
         <v>13</v>
       </c>
@@ -1009,7 +1221,7 @@
         <v>-506666666.66665989</v>
       </c>
     </row>
-    <row r="9" spans="1:5" ht="15">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A9" s="5" t="s">
         <v>15</v>
       </c>
@@ -1026,7 +1238,7 @@
         <v>-28333333.333328031</v>
       </c>
     </row>
-    <row r="10" spans="1:5" ht="15">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A10" s="5" t="s">
         <v>22</v>
       </c>
@@ -1041,7 +1253,7 @@
         <v>4801100</v>
       </c>
     </row>
-    <row r="11" spans="1:5" ht="15">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A11" s="5" t="s">
         <v>12</v>
       </c>
@@ -1058,7 +1270,7 @@
         <v>-44999999.999995999</v>
       </c>
     </row>
-    <row r="12" spans="1:5" ht="15">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A12" s="5" t="s">
         <v>23</v>
       </c>
@@ -1073,7 +1285,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:5" ht="15">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A13" s="5" t="s">
         <v>24</v>
       </c>
@@ -1088,7 +1300,7 @@
         <v>95628322.180000007</v>
       </c>
     </row>
-    <row r="14" spans="1:5" ht="15">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A14" s="5" t="s">
         <v>16</v>
       </c>
@@ -1103,7 +1315,7 @@
         <v>-112955.9999999993</v>
       </c>
     </row>
-    <row r="15" spans="1:5" ht="15">
+    <row r="15" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A15" s="5" t="s">
         <v>11</v>
       </c>
@@ -1120,7 +1332,7 @@
         <v>-245833333.3333151</v>
       </c>
     </row>
-    <row r="16" spans="1:5" ht="15">
+    <row r="16" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A16" s="5" t="s">
         <v>17</v>
       </c>
@@ -1135,7 +1347,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:5" ht="15">
+    <row r="17" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A17" s="5" t="s">
         <v>25</v>
       </c>
@@ -1160,22 +1372,22 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9E6B92DB-9C5C-437E-84B0-C727C5D5C893}">
   <dimension ref="A1:A3"/>
-  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="14.45"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.453125" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="23.28515625" customWidth="1"/>
+    <col min="1" max="1" width="23.26953125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="2" spans="1:1">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="3" spans="1:1">
+    <row r="3" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>28</v>
       </c>
@@ -1184,4 +1396,1039 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3A6B287E-8354-44FE-9F9E-5D7B10F86778}">
+  <dimension ref="A1:K14"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.7265625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="31.81640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="3" width="13.7265625" customWidth="1"/>
+    <col min="4" max="4" width="10.81640625" customWidth="1"/>
+    <col min="5" max="5" width="7.54296875" customWidth="1"/>
+    <col min="6" max="7" width="13.7265625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="12" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="8.54296875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="13.26953125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="10.7265625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A1" s="29"/>
+      <c r="B1" s="34" t="s">
+        <v>29</v>
+      </c>
+      <c r="C1" s="35"/>
+      <c r="D1" s="35"/>
+      <c r="E1" s="35"/>
+      <c r="F1" s="34" t="s">
+        <v>30</v>
+      </c>
+      <c r="G1" s="35"/>
+      <c r="H1" s="35"/>
+      <c r="I1" s="35"/>
+      <c r="J1" s="31"/>
+      <c r="K1" s="26"/>
+    </row>
+    <row r="2" spans="1:11" ht="29" x14ac:dyDescent="0.35">
+      <c r="A2" s="29" t="s">
+        <v>31</v>
+      </c>
+      <c r="B2" s="30" t="s">
+        <v>32</v>
+      </c>
+      <c r="C2" s="30" t="s">
+        <v>3</v>
+      </c>
+      <c r="D2" s="30" t="s">
+        <v>4</v>
+      </c>
+      <c r="E2" s="30" t="s">
+        <v>33</v>
+      </c>
+      <c r="F2" s="30" t="s">
+        <v>32</v>
+      </c>
+      <c r="G2" s="30" t="s">
+        <v>3</v>
+      </c>
+      <c r="H2" s="30" t="s">
+        <v>4</v>
+      </c>
+      <c r="I2" s="30" t="s">
+        <v>33</v>
+      </c>
+      <c r="J2" s="27" t="s">
+        <v>34</v>
+      </c>
+      <c r="K2" s="28" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A3" s="11" t="s">
+        <v>36</v>
+      </c>
+      <c r="B3" s="12"/>
+      <c r="C3" s="12"/>
+      <c r="D3" s="13"/>
+      <c r="E3" s="14"/>
+      <c r="F3" s="12"/>
+      <c r="G3" s="12"/>
+      <c r="H3" s="13"/>
+      <c r="I3" s="14"/>
+      <c r="J3" s="15"/>
+      <c r="K3" s="16"/>
+    </row>
+    <row r="4" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A4" s="17" t="s">
+        <v>37</v>
+      </c>
+      <c r="B4" s="18">
+        <v>32031200</v>
+      </c>
+      <c r="C4" s="18">
+        <v>155554762.09087983</v>
+      </c>
+      <c r="D4" s="19">
+        <v>17280945.280000001</v>
+      </c>
+      <c r="E4" s="32">
+        <v>0.11109235775053898</v>
+      </c>
+      <c r="F4" s="18">
+        <v>491317709.61000001</v>
+      </c>
+      <c r="G4" s="18">
+        <v>178695483.03435776</v>
+      </c>
+      <c r="H4" s="19">
+        <v>273840105.59000003</v>
+      </c>
+      <c r="I4" s="32">
+        <v>1.5324399975871177</v>
+      </c>
+      <c r="J4" s="7">
+        <f t="shared" ref="J4:J14" si="0">+H4-D4</f>
+        <v>256559160.31000003</v>
+      </c>
+      <c r="K4" s="20">
+        <f>+H4/D4-1</f>
+        <v>14.846361478091552</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A5" s="17" t="s">
+        <v>38</v>
+      </c>
+      <c r="B5" s="18">
+        <v>270753570.92000002</v>
+      </c>
+      <c r="C5" s="18">
+        <v>98007249.257327542</v>
+      </c>
+      <c r="D5" s="19">
+        <v>40519848.060000002</v>
+      </c>
+      <c r="E5" s="32">
+        <v>0.41343725456074387</v>
+      </c>
+      <c r="F5" s="18">
+        <v>152194527.36000001</v>
+      </c>
+      <c r="G5" s="18">
+        <v>102390317.7004329</v>
+      </c>
+      <c r="H5" s="19">
+        <v>26230565.129999995</v>
+      </c>
+      <c r="I5" s="32">
+        <v>0.25618208556343902</v>
+      </c>
+      <c r="J5" s="7">
+        <f t="shared" si="0"/>
+        <v>-14289282.930000007</v>
+      </c>
+      <c r="K5" s="20">
+        <f t="shared" ref="K5:K14" si="1">+H5/D5-1</f>
+        <v>-0.35264897609786361</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A6" s="17" t="s">
+        <v>39</v>
+      </c>
+      <c r="B6" s="18">
+        <v>28723460.379999999</v>
+      </c>
+      <c r="C6" s="18">
+        <v>161643372.1596604</v>
+      </c>
+      <c r="D6" s="19">
+        <v>12001091.959999999</v>
+      </c>
+      <c r="E6" s="32">
+        <v>7.4244256350616919E-2</v>
+      </c>
+      <c r="F6" s="18">
+        <v>35546402</v>
+      </c>
+      <c r="G6" s="18">
+        <v>184248397.08953407</v>
+      </c>
+      <c r="H6" s="19">
+        <v>15695338.329999998</v>
+      </c>
+      <c r="I6" s="32">
+        <v>8.518575237521861E-2</v>
+      </c>
+      <c r="J6" s="7">
+        <f t="shared" si="0"/>
+        <v>3694246.3699999992</v>
+      </c>
+      <c r="K6" s="20">
+        <f t="shared" si="1"/>
+        <v>0.30782585304012611</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A7" s="17" t="s">
+        <v>40</v>
+      </c>
+      <c r="B7" s="18">
+        <v>28375785.32</v>
+      </c>
+      <c r="C7" s="18">
+        <v>99188993.120685354</v>
+      </c>
+      <c r="D7" s="19">
+        <v>2894625.75</v>
+      </c>
+      <c r="E7" s="32">
+        <v>2.9182933094986128E-2</v>
+      </c>
+      <c r="F7" s="18">
+        <v>52154789.370000005</v>
+      </c>
+      <c r="G7" s="18">
+        <v>106940998.48712452</v>
+      </c>
+      <c r="H7" s="19">
+        <v>7902152.7400000095</v>
+      </c>
+      <c r="I7" s="32">
+        <v>7.3892640351131592E-2</v>
+      </c>
+      <c r="J7" s="7">
+        <f t="shared" si="0"/>
+        <v>5007526.9900000095</v>
+      </c>
+      <c r="K7" s="20">
+        <f t="shared" si="1"/>
+        <v>1.7299393505360787</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A8" s="17" t="s">
+        <v>41</v>
+      </c>
+      <c r="B8" s="18">
+        <v>117141234</v>
+      </c>
+      <c r="C8" s="18">
+        <v>57501386.9996728</v>
+      </c>
+      <c r="D8" s="19">
+        <v>19677900.039999992</v>
+      </c>
+      <c r="E8" s="32">
+        <v>0.34221609367634859</v>
+      </c>
+      <c r="F8" s="18">
+        <v>30396086</v>
+      </c>
+      <c r="G8" s="18">
+        <v>85487789.064166516</v>
+      </c>
+      <c r="H8" s="19">
+        <v>5420486</v>
+      </c>
+      <c r="I8" s="32">
+        <v>6.3406552670714433E-2</v>
+      </c>
+      <c r="J8" s="7">
+        <f t="shared" si="0"/>
+        <v>-14257414.039999992</v>
+      </c>
+      <c r="K8" s="20">
+        <f t="shared" si="1"/>
+        <v>-0.72453940771212477</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A9" s="17" t="s">
+        <v>42</v>
+      </c>
+      <c r="B9" s="18">
+        <v>0</v>
+      </c>
+      <c r="C9" s="18">
+        <v>155554762.09087223</v>
+      </c>
+      <c r="D9" s="19">
+        <v>0</v>
+      </c>
+      <c r="E9" s="32">
+        <v>0</v>
+      </c>
+      <c r="F9" s="18">
+        <v>8800000</v>
+      </c>
+      <c r="G9" s="18">
+        <v>191697428.13917199</v>
+      </c>
+      <c r="H9" s="19">
+        <v>4224000</v>
+      </c>
+      <c r="I9" s="32">
+        <v>2.2034724414421374E-2</v>
+      </c>
+      <c r="J9" s="7">
+        <f t="shared" si="0"/>
+        <v>4224000</v>
+      </c>
+      <c r="K9" s="20" t="e">
+        <f t="shared" si="1"/>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A10" s="17" t="s">
+        <v>43</v>
+      </c>
+      <c r="B10" s="18">
+        <v>1722908.62</v>
+      </c>
+      <c r="C10" s="18">
+        <v>47463483.036268912</v>
+      </c>
+      <c r="D10" s="19">
+        <v>441144.18000000017</v>
+      </c>
+      <c r="E10" s="32">
+        <v>9.2943912199385473E-3</v>
+      </c>
+      <c r="F10" s="18">
+        <v>0</v>
+      </c>
+      <c r="G10" s="18">
+        <v>0</v>
+      </c>
+      <c r="H10" s="19">
+        <v>0</v>
+      </c>
+      <c r="I10" s="32"/>
+      <c r="J10" s="7">
+        <f t="shared" si="0"/>
+        <v>-441144.18000000017</v>
+      </c>
+      <c r="K10" s="20">
+        <f t="shared" si="1"/>
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A11" s="17" t="s">
+        <v>44</v>
+      </c>
+      <c r="B11" s="18">
+        <v>0</v>
+      </c>
+      <c r="C11" s="18">
+        <v>0</v>
+      </c>
+      <c r="D11" s="19">
+        <v>0</v>
+      </c>
+      <c r="E11" s="32"/>
+      <c r="F11" s="18">
+        <v>0</v>
+      </c>
+      <c r="G11" s="18">
+        <v>0</v>
+      </c>
+      <c r="H11" s="19">
+        <v>0</v>
+      </c>
+      <c r="I11" s="32"/>
+      <c r="J11" s="7">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="K11" s="20" t="e">
+        <f t="shared" si="1"/>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A12" s="17" t="s">
+        <v>45</v>
+      </c>
+      <c r="B12" s="18">
+        <v>29552</v>
+      </c>
+      <c r="C12" s="18">
+        <v>0</v>
+      </c>
+      <c r="D12" s="19">
+        <v>29552</v>
+      </c>
+      <c r="E12" s="32"/>
+      <c r="F12" s="18"/>
+      <c r="G12" s="18"/>
+      <c r="H12" s="19"/>
+      <c r="I12" s="32"/>
+      <c r="J12" s="7">
+        <f t="shared" si="0"/>
+        <v>-29552</v>
+      </c>
+      <c r="K12" s="20">
+        <f t="shared" si="1"/>
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A13" s="17" t="s">
+        <v>46</v>
+      </c>
+      <c r="B13" s="18"/>
+      <c r="C13" s="18"/>
+      <c r="D13" s="19"/>
+      <c r="E13" s="32"/>
+      <c r="F13" s="18">
+        <v>0</v>
+      </c>
+      <c r="G13" s="18">
+        <v>22753403.933430597</v>
+      </c>
+      <c r="H13" s="19">
+        <v>0</v>
+      </c>
+      <c r="I13" s="32">
+        <v>0</v>
+      </c>
+      <c r="J13" s="7">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="K13" s="20" t="e">
+        <f t="shared" si="1"/>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A14" s="21" t="s">
+        <v>47</v>
+      </c>
+      <c r="B14" s="22">
+        <v>478777711.24000001</v>
+      </c>
+      <c r="C14" s="22">
+        <v>774914008.75536704</v>
+      </c>
+      <c r="D14" s="23">
+        <v>92845107.270000041</v>
+      </c>
+      <c r="E14" s="33">
+        <v>0.11981343248539765</v>
+      </c>
+      <c r="F14" s="22">
+        <v>770409514.34000003</v>
+      </c>
+      <c r="G14" s="22">
+        <v>872213817.44821835</v>
+      </c>
+      <c r="H14" s="23">
+        <v>333312647.79000002</v>
+      </c>
+      <c r="I14" s="33">
+        <v>0.38214557155853374</v>
+      </c>
+      <c r="J14" s="24">
+        <f t="shared" si="0"/>
+        <v>240467540.51999998</v>
+      </c>
+      <c r="K14" s="25">
+        <f t="shared" si="1"/>
+        <v>2.5899861348719608</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="B1:E1"/>
+    <mergeCell ref="F1:I1"/>
+  </mergeCells>
+  <conditionalFormatting sqref="E4:E14">
+    <cfRule type="colorScale" priority="2">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I4:I14">
+    <cfRule type="colorScale" priority="1">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{120C2AAA-1B62-49E5-A9DB-A8B675BAA0E0}">
+  <dimension ref="A1:L15"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="29.54296875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="19" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.36328125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9.90625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="6.7265625" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="12.36328125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="9.90625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="7.7265625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="11.54296875" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="9.36328125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A1" s="36"/>
+      <c r="B1" s="36" t="s">
+        <v>48</v>
+      </c>
+      <c r="C1" s="36"/>
+      <c r="D1" s="36"/>
+      <c r="E1" s="36"/>
+      <c r="F1" s="36"/>
+      <c r="G1" s="36"/>
+      <c r="H1" s="36"/>
+      <c r="I1" s="36"/>
+      <c r="J1" s="39"/>
+      <c r="K1" s="39"/>
+      <c r="L1" s="39"/>
+    </row>
+    <row r="2" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A2" s="36"/>
+      <c r="B2" s="37" t="s">
+        <v>29</v>
+      </c>
+      <c r="C2" s="38"/>
+      <c r="D2" s="38"/>
+      <c r="E2" s="38"/>
+      <c r="F2" s="37" t="s">
+        <v>30</v>
+      </c>
+      <c r="G2" s="38"/>
+      <c r="H2" s="38"/>
+      <c r="I2" s="38"/>
+      <c r="J2" s="39"/>
+      <c r="K2" s="39"/>
+      <c r="L2" s="39"/>
+    </row>
+    <row r="3" spans="1:12" ht="29" x14ac:dyDescent="0.35">
+      <c r="A3" s="36" t="s">
+        <v>31</v>
+      </c>
+      <c r="B3" s="40" t="s">
+        <v>32</v>
+      </c>
+      <c r="C3" s="40" t="s">
+        <v>3</v>
+      </c>
+      <c r="D3" s="40" t="s">
+        <v>4</v>
+      </c>
+      <c r="E3" s="40" t="s">
+        <v>33</v>
+      </c>
+      <c r="F3" s="40" t="s">
+        <v>32</v>
+      </c>
+      <c r="G3" s="40" t="s">
+        <v>3</v>
+      </c>
+      <c r="H3" s="40" t="s">
+        <v>4</v>
+      </c>
+      <c r="I3" s="40" t="s">
+        <v>33</v>
+      </c>
+      <c r="J3" s="44" t="s">
+        <v>34</v>
+      </c>
+      <c r="K3" s="45" t="s">
+        <v>35</v>
+      </c>
+      <c r="L3" s="45" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A4" s="54" t="s">
+        <v>36</v>
+      </c>
+      <c r="B4" s="55"/>
+      <c r="C4" s="55"/>
+      <c r="D4" s="56"/>
+      <c r="E4" s="60"/>
+      <c r="F4" s="55"/>
+      <c r="G4" s="55"/>
+      <c r="H4" s="56"/>
+      <c r="I4" s="60"/>
+      <c r="J4" s="57"/>
+      <c r="K4" s="58"/>
+      <c r="L4" s="58"/>
+    </row>
+    <row r="5" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A5" s="47" t="s">
+        <v>39</v>
+      </c>
+      <c r="B5" s="41">
+        <v>739925955.98999989</v>
+      </c>
+      <c r="C5" s="41">
+        <v>116712575.07946891</v>
+      </c>
+      <c r="D5" s="43">
+        <v>52240926.689999819</v>
+      </c>
+      <c r="E5" s="42">
+        <v>0.44760323944895797</v>
+      </c>
+      <c r="F5" s="41">
+        <v>293567149.97000003</v>
+      </c>
+      <c r="G5" s="41">
+        <v>91800842.878753603</v>
+      </c>
+      <c r="H5" s="43">
+        <v>30823146.090000033</v>
+      </c>
+      <c r="I5" s="42">
+        <v>0.335761035775127</v>
+      </c>
+      <c r="J5" s="46">
+        <v>-21417780.599999785</v>
+      </c>
+      <c r="K5" s="48">
+        <v>-0.40998087049821935</v>
+      </c>
+      <c r="L5" s="48">
+        <v>0.57402412453272655</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A6" s="47" t="s">
+        <v>42</v>
+      </c>
+      <c r="B6" s="41">
+        <v>225036765.16000003</v>
+      </c>
+      <c r="C6" s="41">
+        <v>96089866.55070281</v>
+      </c>
+      <c r="D6" s="43">
+        <v>17941257.580000043</v>
+      </c>
+      <c r="E6" s="42">
+        <v>0.18671331560787535</v>
+      </c>
+      <c r="F6" s="41">
+        <v>144640230.25</v>
+      </c>
+      <c r="G6" s="41">
+        <v>83577281.896116406</v>
+      </c>
+      <c r="H6" s="43">
+        <v>13594203.789999992</v>
+      </c>
+      <c r="I6" s="42">
+        <v>0.16265429410467203</v>
+      </c>
+      <c r="J6" s="46">
+        <v>-4347053.7900000513</v>
+      </c>
+      <c r="K6" s="48">
+        <v>-0.2422937060357416</v>
+      </c>
+      <c r="L6" s="48">
+        <v>0.25316691899292787</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A7" s="47" t="s">
+        <v>38</v>
+      </c>
+      <c r="B7" s="41">
+        <v>2577961.44</v>
+      </c>
+      <c r="C7" s="41">
+        <v>48743897.797445603</v>
+      </c>
+      <c r="D7" s="43">
+        <v>176020.43999999994</v>
+      </c>
+      <c r="E7" s="42">
+        <v>3.6111277093893845E-3</v>
+      </c>
+      <c r="F7" s="41">
+        <v>36181684.129999995</v>
+      </c>
+      <c r="G7" s="41">
+        <v>50069339.384766802</v>
+      </c>
+      <c r="H7" s="43">
+        <v>6397684.1299999952</v>
+      </c>
+      <c r="I7" s="42">
+        <v>0.12777648374458972</v>
+      </c>
+      <c r="J7" s="46">
+        <v>6221663.6899999958</v>
+      </c>
+      <c r="K7" s="48">
+        <v>35.346256889256715</v>
+      </c>
+      <c r="L7" s="48">
+        <v>0.11914504187979735</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A8" s="47" t="s">
+        <v>41</v>
+      </c>
+      <c r="B8" s="41">
+        <v>286279133.75999999</v>
+      </c>
+      <c r="C8" s="41">
+        <v>32570651.823400989</v>
+      </c>
+      <c r="D8" s="43">
+        <v>6463298.4300000072</v>
+      </c>
+      <c r="E8" s="42">
+        <v>0.19843933320844145</v>
+      </c>
+      <c r="F8" s="41">
+        <v>11296680</v>
+      </c>
+      <c r="G8" s="41">
+        <v>36043152.510621198</v>
+      </c>
+      <c r="H8" s="43">
+        <v>1920440</v>
+      </c>
+      <c r="I8" s="42">
+        <v>5.3281687816682646E-2</v>
+      </c>
+      <c r="J8" s="46">
+        <v>-4542858.4300000072</v>
+      </c>
+      <c r="K8" s="48">
+        <v>-0.70286997872694579</v>
+      </c>
+      <c r="L8" s="48">
+        <v>3.5764645390149667E-2</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A9" s="47" t="s">
+        <v>46</v>
+      </c>
+      <c r="B9" s="41"/>
+      <c r="C9" s="41"/>
+      <c r="D9" s="43"/>
+      <c r="E9" s="42"/>
+      <c r="F9" s="41">
+        <v>0</v>
+      </c>
+      <c r="G9" s="41">
+        <v>3555219.3645986998</v>
+      </c>
+      <c r="H9" s="43">
+        <v>0</v>
+      </c>
+      <c r="I9" s="42">
+        <v>0</v>
+      </c>
+      <c r="J9" s="46">
+        <v>0</v>
+      </c>
+      <c r="K9" s="48" t="e">
+        <v>#DIV/0!</v>
+      </c>
+      <c r="L9" s="48">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A10" s="47" t="s">
+        <v>45</v>
+      </c>
+      <c r="B10" s="41">
+        <v>885906</v>
+      </c>
+      <c r="C10" s="41">
+        <v>0</v>
+      </c>
+      <c r="D10" s="43">
+        <v>118905</v>
+      </c>
+      <c r="E10" s="42"/>
+      <c r="F10" s="41"/>
+      <c r="G10" s="41"/>
+      <c r="H10" s="43"/>
+      <c r="I10" s="42"/>
+      <c r="J10" s="46">
+        <v>-118905</v>
+      </c>
+      <c r="K10" s="48">
+        <v>-1</v>
+      </c>
+      <c r="L10" s="48">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A11" s="47" t="s">
+        <v>37</v>
+      </c>
+      <c r="B11" s="41">
+        <v>0</v>
+      </c>
+      <c r="C11" s="41">
+        <v>24949068.102458403</v>
+      </c>
+      <c r="D11" s="43">
+        <v>0</v>
+      </c>
+      <c r="E11" s="42">
+        <v>0</v>
+      </c>
+      <c r="F11" s="41">
+        <v>0</v>
+      </c>
+      <c r="G11" s="41">
+        <v>75417206.973561406</v>
+      </c>
+      <c r="H11" s="43">
+        <v>0</v>
+      </c>
+      <c r="I11" s="42">
+        <v>0</v>
+      </c>
+      <c r="J11" s="46">
+        <v>0</v>
+      </c>
+      <c r="K11" s="48" t="e">
+        <v>#DIV/0!</v>
+      </c>
+      <c r="L11" s="48">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A12" s="47" t="s">
+        <v>43</v>
+      </c>
+      <c r="B12" s="41">
+        <v>0</v>
+      </c>
+      <c r="C12" s="41">
+        <v>7612558.1418069005</v>
+      </c>
+      <c r="D12" s="43">
+        <v>0</v>
+      </c>
+      <c r="E12" s="42">
+        <v>0</v>
+      </c>
+      <c r="F12" s="41">
+        <v>0</v>
+      </c>
+      <c r="G12" s="41">
+        <v>0</v>
+      </c>
+      <c r="H12" s="43">
+        <v>0</v>
+      </c>
+      <c r="I12" s="42"/>
+      <c r="J12" s="46">
+        <v>0</v>
+      </c>
+      <c r="K12" s="48" t="e">
+        <v>#DIV/0!</v>
+      </c>
+      <c r="L12" s="48">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A13" s="47" t="s">
+        <v>44</v>
+      </c>
+      <c r="B13" s="41">
+        <v>15020000</v>
+      </c>
+      <c r="C13" s="41">
+        <v>35954356.238271199</v>
+      </c>
+      <c r="D13" s="43">
+        <v>2334000</v>
+      </c>
+      <c r="E13" s="42">
+        <v>6.4915638720728946E-2</v>
+      </c>
+      <c r="F13" s="41">
+        <v>0</v>
+      </c>
+      <c r="G13" s="41">
+        <v>34494092.644621998</v>
+      </c>
+      <c r="H13" s="43">
+        <v>0</v>
+      </c>
+      <c r="I13" s="42">
+        <v>0</v>
+      </c>
+      <c r="J13" s="46">
+        <v>-2334000</v>
+      </c>
+      <c r="K13" s="48">
+        <v>-1</v>
+      </c>
+      <c r="L13" s="48">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A14" s="47" t="s">
+        <v>40</v>
+      </c>
+      <c r="B14" s="41">
+        <v>4378709.21</v>
+      </c>
+      <c r="C14" s="41">
+        <v>15908692.933081001</v>
+      </c>
+      <c r="D14" s="43">
+        <v>551390.83999999985</v>
+      </c>
+      <c r="E14" s="42">
+        <v>3.4659719834897428E-2</v>
+      </c>
+      <c r="F14" s="41">
+        <v>5870410.8700000001</v>
+      </c>
+      <c r="G14" s="41">
+        <v>16709531.013613399</v>
+      </c>
+      <c r="H14" s="43">
+        <v>961129.96999999974</v>
+      </c>
+      <c r="I14" s="42">
+        <v>5.7519865112728726E-2</v>
+      </c>
+      <c r="J14" s="46">
+        <v>409739.12999999989</v>
+      </c>
+      <c r="K14" s="48">
+        <v>0.74310108234659833</v>
+      </c>
+      <c r="L14" s="48">
+        <v>1.7899269204398563E-2</v>
+      </c>
+    </row>
+    <row r="15" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A15" s="49" t="s">
+        <v>47</v>
+      </c>
+      <c r="B15" s="50">
+        <v>1274104431.5599999</v>
+      </c>
+      <c r="C15" s="50">
+        <v>378541666.66663581</v>
+      </c>
+      <c r="D15" s="51">
+        <v>79825798.980000019</v>
+      </c>
+      <c r="E15" s="59">
+        <v>0.21087717947387521</v>
+      </c>
+      <c r="F15" s="50">
+        <v>491556155.22000003</v>
+      </c>
+      <c r="G15" s="50">
+        <v>391666666.66665351</v>
+      </c>
+      <c r="H15" s="51">
+        <v>53696603.980000019</v>
+      </c>
+      <c r="I15" s="59">
+        <v>0.13709771228936629</v>
+      </c>
+      <c r="J15" s="52">
+        <v>-26129195</v>
+      </c>
+      <c r="K15" s="53">
+        <v>-0.32732769773524656</v>
+      </c>
+      <c r="L15" s="53">
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="B2:E2"/>
+    <mergeCell ref="F2:I2"/>
+  </mergeCells>
+  <conditionalFormatting sqref="E4:E14">
+    <cfRule type="colorScale" priority="2">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I4:I14">
+    <cfRule type="colorScale" priority="1">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/copa_copilot_datos.xlsx
+++ b/copa_copilot_datos.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://controlesempresarialesltda-my.sharepoint.com/personal/marango_coem_co/Documents/GitHub/COEM/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="481" documentId="11_7B0F6A10CFB5B9B3AED9E795B9A4719BFA1CF949" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7AEA0780-7C84-4719-9BCB-39F780251E5F}"/>
+  <xr:revisionPtr revIDLastSave="488" documentId="11_7B0F6A10CFB5B9B3AED9E795B9A4719BFA1CF949" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A283316C-6BD9-475B-AD0E-514F280AE1C1}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Copa Copilot" sheetId="1" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="95" uniqueCount="50">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="79" uniqueCount="45">
   <si>
     <t>Pos</t>
   </si>
@@ -129,12 +129,6 @@
     <t>Valle de la oportunidad</t>
   </si>
   <si>
-    <t>2025</t>
-  </si>
-  <si>
-    <t>2026</t>
-  </si>
-  <si>
     <t>Etiquetas de fila</t>
   </si>
   <si>
@@ -147,9 +141,6 @@
     <t>Y to Y Ub</t>
   </si>
   <si>
-    <t>%crec/dec</t>
-  </si>
-  <si>
     <t>VALLE</t>
   </si>
   <si>
@@ -184,12 +175,6 @@
   </si>
   <si>
     <t>Total VALLE</t>
-  </si>
-  <si>
-    <t>Etiquetas de columna</t>
-  </si>
-  <si>
-    <t>% Part</t>
   </si>
 </sst>
 </file>
@@ -198,12 +183,12 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="7">
     <numFmt numFmtId="6" formatCode="&quot;$&quot;\ #,##0;[Red]\-&quot;$&quot;\ #,##0"/>
+    <numFmt numFmtId="42" formatCode="_-&quot;$&quot;\ * #,##0_-;\-&quot;$&quot;\ * #,##0_-;_-&quot;$&quot;\ * &quot;-&quot;_-;_-@_-"/>
     <numFmt numFmtId="164" formatCode="_-* #,##0\ &quot;€&quot;_-;\-* #,##0\ &quot;€&quot;_-;_-* &quot;-&quot;\ &quot;€&quot;_-;_-@_-"/>
     <numFmt numFmtId="165" formatCode="&quot;$&quot;#,##0"/>
     <numFmt numFmtId="166" formatCode="&quot;$&quot;#,##0;[Red]\-&quot;$&quot;#,##0"/>
     <numFmt numFmtId="167" formatCode="&quot;$&quot;\ #,##0"/>
-    <numFmt numFmtId="168" formatCode="_-&quot;$&quot;\ * #,##0_-;\-&quot;$&quot;\ * #,##0_-;_-&quot;$&quot;\ * &quot;-&quot;_-;_-@_-"/>
-    <numFmt numFmtId="171" formatCode="_-&quot;$&quot;* #,##0.00_-;\-&quot;$&quot;* #,##0.00_-;_-&quot;$&quot;* &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="168" formatCode="_-&quot;$&quot;* #,##0.00_-;\-&quot;$&quot;* #,##0.00_-;_-&quot;$&quot;* &quot;-&quot;??_-;_-@_-"/>
   </numFmts>
   <fonts count="9" x14ac:knownFonts="1">
     <font>
@@ -348,15 +333,14 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="6">
+  <cellStyleXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="164" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="168" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="42" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="168" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="61">
+  <cellXfs count="32">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -385,25 +369,18 @@
     <xf numFmtId="3" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="166" fontId="7" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="9" fontId="7" fillId="4" borderId="0" xfId="2" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" indent="1"/>
     </xf>
     <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="9" fontId="7" fillId="0" borderId="0" xfId="2" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="167" fontId="0" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="3" fontId="0" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="166" fontId="7" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="9" fontId="7" fillId="5" borderId="0" xfId="2" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="7" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="164" fontId="7" fillId="6" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="7" fillId="6" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -412,66 +389,25 @@
     <xf numFmtId="0" fontId="8" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="10" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="10" fontId="8" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="8" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="168" fontId="7" fillId="7" borderId="0" xfId="4" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="42" fontId="7" fillId="7" borderId="0" xfId="3" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="7" fillId="7" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" indent="1"/>
-    </xf>
-    <xf numFmtId="9" fontId="7" fillId="0" borderId="0" xfId="2" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="167" fontId="0" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="3" fontId="0" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="166" fontId="7" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="9" fontId="7" fillId="5" borderId="0" xfId="2" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="167" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="3" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="166" fontId="7" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="9" fontId="7" fillId="4" borderId="0" xfId="2" applyFont="1" applyFill="1"/>
     <xf numFmtId="10" fontId="0" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
   </cellXfs>
-  <cellStyles count="6">
+  <cellStyles count="5">
     <cellStyle name="Moneda [0]" xfId="1" builtinId="7"/>
-    <cellStyle name="Moneda [0] 2" xfId="4" xr:uid="{0CCB16E3-81C2-4951-B834-94F35D3AC9B1}"/>
-    <cellStyle name="Moneda 2" xfId="3" xr:uid="{E3481F5F-7FEF-4617-8D16-A7A96E887278}"/>
-    <cellStyle name="Moneda 3" xfId="5" xr:uid="{F307236A-65B4-4AB6-879A-D24F4D74FE5A}"/>
+    <cellStyle name="Moneda [0] 2" xfId="3" xr:uid="{0CCB16E3-81C2-4951-B834-94F35D3AC9B1}"/>
+    <cellStyle name="Moneda 2" xfId="2" xr:uid="{E3481F5F-7FEF-4617-8D16-A7A96E887278}"/>
+    <cellStyle name="Moneda 3" xfId="4" xr:uid="{F307236A-65B4-4AB6-879A-D24F4D74FE5A}"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Porcentaje" xfId="2" builtinId="5"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
@@ -772,18 +708,18 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:G13"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.1796875" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.21875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="6" customWidth="1"/>
-    <col min="2" max="2" width="36.81640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="19.1796875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.54296875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.1796875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="13.26953125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="17.1796875" customWidth="1"/>
+    <col min="2" max="2" width="36.77734375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="19.21875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.5546875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.21875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="13.21875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="17.21875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -806,7 +742,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A2" s="2">
         <v>1</v>
       </c>
@@ -829,7 +765,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3" s="2">
         <v>2</v>
       </c>
@@ -852,7 +788,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A4" s="2">
         <v>3</v>
       </c>
@@ -875,7 +811,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A5" s="2">
         <v>4</v>
       </c>
@@ -898,7 +834,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A6" s="2">
         <v>5</v>
       </c>
@@ -921,7 +857,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A7" s="2">
         <v>6</v>
       </c>
@@ -944,7 +880,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A8" s="2">
         <v>7</v>
       </c>
@@ -967,7 +903,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A9" s="2">
         <v>8</v>
       </c>
@@ -988,7 +924,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A10" s="2">
         <v>9</v>
       </c>
@@ -1009,7 +945,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A11" s="2">
         <v>10</v>
       </c>
@@ -1029,7 +965,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A12" s="2">
         <v>11</v>
       </c>
@@ -1049,7 +985,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
       <c r="B13" t="s">
         <v>18</v>
       </c>
@@ -1076,16 +1012,16 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:E17"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.1796875" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.21875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="41.26953125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="41.21875" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="17" customWidth="1"/>
-    <col min="3" max="3" width="21.1796875" customWidth="1"/>
+    <col min="3" max="3" width="21.21875" customWidth="1"/>
     <col min="4" max="4" width="20" customWidth="1"/>
-    <col min="5" max="5" width="16.7265625" customWidth="1"/>
+    <col min="5" max="5" width="16.77734375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1" s="8" t="s">
         <v>19</v>
       </c>
@@ -1102,7 +1038,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2" s="5" t="s">
         <v>8</v>
       </c>
@@ -1119,7 +1055,7 @@
         <v>34069255.626669183</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A3" s="5" t="s">
         <v>9</v>
       </c>
@@ -1136,7 +1072,7 @@
         <v>-125143064.22665811</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A4" s="5" t="s">
         <v>7</v>
       </c>
@@ -1153,7 +1089,7 @@
         <v>-155109545.63665611</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A5" s="5" t="s">
         <v>10</v>
       </c>
@@ -1170,7 +1106,7 @@
         <v>-330254339.70665872</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A6" s="5" t="s">
         <v>18</v>
       </c>
@@ -1187,7 +1123,7 @@
         <v>-105668560.20999902</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A7" s="5" t="s">
         <v>14</v>
       </c>
@@ -1204,7 +1140,7 @@
         <v>-99917126.709992483</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A8" s="5" t="s">
         <v>13</v>
       </c>
@@ -1221,7 +1157,7 @@
         <v>-506666666.66665989</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A9" s="5" t="s">
         <v>15</v>
       </c>
@@ -1238,7 +1174,7 @@
         <v>-28333333.333328031</v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A10" s="5" t="s">
         <v>22</v>
       </c>
@@ -1253,7 +1189,7 @@
         <v>4801100</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A11" s="5" t="s">
         <v>12</v>
       </c>
@@ -1270,7 +1206,7 @@
         <v>-44999999.999995999</v>
       </c>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A12" s="5" t="s">
         <v>23</v>
       </c>
@@ -1285,7 +1221,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A13" s="5" t="s">
         <v>24</v>
       </c>
@@ -1300,7 +1236,7 @@
         <v>95628322.180000007</v>
       </c>
     </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A14" s="5" t="s">
         <v>16</v>
       </c>
@@ -1315,7 +1251,7 @@
         <v>-112955.9999999993</v>
       </c>
     </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A15" s="5" t="s">
         <v>11</v>
       </c>
@@ -1332,7 +1268,7 @@
         <v>-245833333.3333151</v>
       </c>
     </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A16" s="5" t="s">
         <v>17</v>
       </c>
@@ -1347,7 +1283,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A17" s="5" t="s">
         <v>25</v>
       </c>
@@ -1372,22 +1308,22 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9E6B92DB-9C5C-437E-84B0-C727C5D5C893}">
   <dimension ref="A1:A3"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.453125" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.44140625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="23.26953125" customWidth="1"/>
+    <col min="1" max="1" width="23.21875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>28</v>
       </c>
@@ -1400,488 +1336,256 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3A6B287E-8354-44FE-9F9E-5D7B10F86778}">
-  <dimension ref="A1:K14"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.7265625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <dimension ref="A1:F13"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.77734375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="31.81640625" bestFit="1" customWidth="1"/>
-    <col min="2" max="3" width="13.7265625" customWidth="1"/>
-    <col min="4" max="4" width="10.81640625" customWidth="1"/>
-    <col min="5" max="5" width="7.54296875" customWidth="1"/>
-    <col min="6" max="7" width="13.7265625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="12" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="8.54296875" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="13.26953125" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="10.7265625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="31.77734375" bestFit="1" customWidth="1"/>
+    <col min="2" max="3" width="13.77734375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="12" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="8.5546875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="13.21875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A1" s="29"/>
-      <c r="B1" s="34" t="s">
+    <row r="1" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A1" s="24" t="s">
         <v>29</v>
       </c>
-      <c r="C1" s="35"/>
-      <c r="D1" s="35"/>
-      <c r="E1" s="35"/>
-      <c r="F1" s="34" t="s">
+      <c r="B1" s="25" t="s">
         <v>30</v>
       </c>
-      <c r="G1" s="35"/>
-      <c r="H1" s="35"/>
-      <c r="I1" s="35"/>
-      <c r="J1" s="31"/>
-      <c r="K1" s="26"/>
-    </row>
-    <row r="2" spans="1:11" ht="29" x14ac:dyDescent="0.35">
-      <c r="A2" s="29" t="s">
+      <c r="C1" s="25" t="s">
+        <v>3</v>
+      </c>
+      <c r="D1" s="25" t="s">
+        <v>4</v>
+      </c>
+      <c r="E1" s="25" t="s">
         <v>31</v>
       </c>
-      <c r="B2" s="30" t="s">
+      <c r="F1" s="23" t="s">
         <v>32</v>
       </c>
-      <c r="C2" s="30" t="s">
-        <v>3</v>
-      </c>
-      <c r="D2" s="30" t="s">
-        <v>4</v>
-      </c>
-      <c r="E2" s="30" t="s">
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A2" s="11" t="s">
         <v>33</v>
       </c>
-      <c r="F2" s="30" t="s">
-        <v>32</v>
-      </c>
-      <c r="G2" s="30" t="s">
-        <v>3</v>
-      </c>
-      <c r="H2" s="30" t="s">
-        <v>4</v>
-      </c>
-      <c r="I2" s="30" t="s">
-        <v>33</v>
-      </c>
-      <c r="J2" s="27" t="s">
+      <c r="B2" s="12"/>
+      <c r="C2" s="12"/>
+      <c r="D2" s="13"/>
+      <c r="E2" s="14"/>
+      <c r="F2" s="15"/>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A3" s="16" t="s">
         <v>34</v>
       </c>
-      <c r="K2" s="28" t="s">
+      <c r="B3" s="17">
+        <v>491317709.61000001</v>
+      </c>
+      <c r="C3" s="17">
+        <v>178695483.03435776</v>
+      </c>
+      <c r="D3" s="18">
+        <v>273840105.59000003</v>
+      </c>
+      <c r="E3" s="26">
+        <v>1.5324399975871177</v>
+      </c>
+      <c r="F3" s="7">
+        <v>256559160.31000003</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A4" s="16" t="s">
         <v>35</v>
       </c>
-    </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A3" s="11" t="s">
+      <c r="B4" s="17">
+        <v>152194527.36000001</v>
+      </c>
+      <c r="C4" s="17">
+        <v>102390317.7004329</v>
+      </c>
+      <c r="D4" s="18">
+        <v>26230565.129999995</v>
+      </c>
+      <c r="E4" s="26">
+        <v>0.25618208556343902</v>
+      </c>
+      <c r="F4" s="7">
+        <v>-14289282.930000007</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A5" s="16" t="s">
         <v>36</v>
       </c>
-      <c r="B3" s="12"/>
-      <c r="C3" s="12"/>
-      <c r="D3" s="13"/>
-      <c r="E3" s="14"/>
-      <c r="F3" s="12"/>
-      <c r="G3" s="12"/>
-      <c r="H3" s="13"/>
-      <c r="I3" s="14"/>
-      <c r="J3" s="15"/>
-      <c r="K3" s="16"/>
-    </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A4" s="17" t="s">
+      <c r="B5" s="17">
+        <v>35546402</v>
+      </c>
+      <c r="C5" s="17">
+        <v>184248397.08953407</v>
+      </c>
+      <c r="D5" s="18">
+        <v>15695338.329999998</v>
+      </c>
+      <c r="E5" s="26">
+        <v>8.518575237521861E-2</v>
+      </c>
+      <c r="F5" s="7">
+        <v>3694246.3699999992</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A6" s="16" t="s">
         <v>37</v>
       </c>
-      <c r="B4" s="18">
-        <v>32031200</v>
-      </c>
-      <c r="C4" s="18">
-        <v>155554762.09087983</v>
-      </c>
-      <c r="D4" s="19">
-        <v>17280945.280000001</v>
-      </c>
-      <c r="E4" s="32">
-        <v>0.11109235775053898</v>
-      </c>
-      <c r="F4" s="18">
-        <v>491317709.61000001</v>
-      </c>
-      <c r="G4" s="18">
-        <v>178695483.03435776</v>
-      </c>
-      <c r="H4" s="19">
-        <v>273840105.59000003</v>
-      </c>
-      <c r="I4" s="32">
-        <v>1.5324399975871177</v>
-      </c>
-      <c r="J4" s="7">
-        <f t="shared" ref="J4:J14" si="0">+H4-D4</f>
-        <v>256559160.31000003</v>
-      </c>
-      <c r="K4" s="20">
-        <f>+H4/D4-1</f>
-        <v>14.846361478091552</v>
-      </c>
-    </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A5" s="17" t="s">
+      <c r="B6" s="17">
+        <v>52154789.370000005</v>
+      </c>
+      <c r="C6" s="17">
+        <v>106940998.48712452</v>
+      </c>
+      <c r="D6" s="18">
+        <v>7902152.7400000095</v>
+      </c>
+      <c r="E6" s="26">
+        <v>7.3892640351131592E-2</v>
+      </c>
+      <c r="F6" s="7">
+        <v>5007526.9900000095</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A7" s="16" t="s">
         <v>38</v>
       </c>
-      <c r="B5" s="18">
-        <v>270753570.92000002</v>
-      </c>
-      <c r="C5" s="18">
-        <v>98007249.257327542</v>
-      </c>
-      <c r="D5" s="19">
-        <v>40519848.060000002</v>
-      </c>
-      <c r="E5" s="32">
-        <v>0.41343725456074387</v>
-      </c>
-      <c r="F5" s="18">
-        <v>152194527.36000001</v>
-      </c>
-      <c r="G5" s="18">
-        <v>102390317.7004329</v>
-      </c>
-      <c r="H5" s="19">
-        <v>26230565.129999995</v>
-      </c>
-      <c r="I5" s="32">
-        <v>0.25618208556343902</v>
-      </c>
-      <c r="J5" s="7">
-        <f t="shared" si="0"/>
-        <v>-14289282.930000007</v>
-      </c>
-      <c r="K5" s="20">
-        <f t="shared" ref="K5:K14" si="1">+H5/D5-1</f>
-        <v>-0.35264897609786361</v>
-      </c>
-    </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A6" s="17" t="s">
+      <c r="B7" s="17">
+        <v>30396086</v>
+      </c>
+      <c r="C7" s="17">
+        <v>85487789.064166516</v>
+      </c>
+      <c r="D7" s="18">
+        <v>5420486</v>
+      </c>
+      <c r="E7" s="26">
+        <v>6.3406552670714433E-2</v>
+      </c>
+      <c r="F7" s="7">
+        <v>-14257414.039999992</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A8" s="16" t="s">
         <v>39</v>
       </c>
-      <c r="B6" s="18">
-        <v>28723460.379999999</v>
-      </c>
-      <c r="C6" s="18">
-        <v>161643372.1596604</v>
-      </c>
-      <c r="D6" s="19">
-        <v>12001091.959999999</v>
-      </c>
-      <c r="E6" s="32">
-        <v>7.4244256350616919E-2</v>
-      </c>
-      <c r="F6" s="18">
-        <v>35546402</v>
-      </c>
-      <c r="G6" s="18">
-        <v>184248397.08953407</v>
-      </c>
-      <c r="H6" s="19">
-        <v>15695338.329999998</v>
-      </c>
-      <c r="I6" s="32">
-        <v>8.518575237521861E-2</v>
-      </c>
-      <c r="J6" s="7">
-        <f t="shared" si="0"/>
-        <v>3694246.3699999992</v>
-      </c>
-      <c r="K6" s="20">
-        <f t="shared" si="1"/>
-        <v>0.30782585304012611</v>
-      </c>
-    </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A7" s="17" t="s">
+      <c r="B8" s="17">
+        <v>8800000</v>
+      </c>
+      <c r="C8" s="17">
+        <v>191697428.13917199</v>
+      </c>
+      <c r="D8" s="18">
+        <v>4224000</v>
+      </c>
+      <c r="E8" s="26">
+        <v>2.2034724414421374E-2</v>
+      </c>
+      <c r="F8" s="7">
+        <v>4224000</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A9" s="16" t="s">
         <v>40</v>
       </c>
-      <c r="B7" s="18">
-        <v>28375785.32</v>
-      </c>
-      <c r="C7" s="18">
-        <v>99188993.120685354</v>
-      </c>
-      <c r="D7" s="19">
-        <v>2894625.75</v>
-      </c>
-      <c r="E7" s="32">
-        <v>2.9182933094986128E-2</v>
-      </c>
-      <c r="F7" s="18">
-        <v>52154789.370000005</v>
-      </c>
-      <c r="G7" s="18">
-        <v>106940998.48712452</v>
-      </c>
-      <c r="H7" s="19">
-        <v>7902152.7400000095</v>
-      </c>
-      <c r="I7" s="32">
-        <v>7.3892640351131592E-2</v>
-      </c>
-      <c r="J7" s="7">
-        <f t="shared" si="0"/>
-        <v>5007526.9900000095</v>
-      </c>
-      <c r="K7" s="20">
-        <f t="shared" si="1"/>
-        <v>1.7299393505360787</v>
-      </c>
-    </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A8" s="17" t="s">
+      <c r="B9" s="17">
+        <v>0</v>
+      </c>
+      <c r="C9" s="17">
+        <v>0</v>
+      </c>
+      <c r="D9" s="18">
+        <v>0</v>
+      </c>
+      <c r="E9" s="26"/>
+      <c r="F9" s="7">
+        <v>-441144.18000000017</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A10" s="16" t="s">
         <v>41</v>
       </c>
-      <c r="B8" s="18">
-        <v>117141234</v>
-      </c>
-      <c r="C8" s="18">
-        <v>57501386.9996728</v>
-      </c>
-      <c r="D8" s="19">
-        <v>19677900.039999992</v>
-      </c>
-      <c r="E8" s="32">
-        <v>0.34221609367634859</v>
-      </c>
-      <c r="F8" s="18">
-        <v>30396086</v>
-      </c>
-      <c r="G8" s="18">
-        <v>85487789.064166516</v>
-      </c>
-      <c r="H8" s="19">
-        <v>5420486</v>
-      </c>
-      <c r="I8" s="32">
-        <v>6.3406552670714433E-2</v>
-      </c>
-      <c r="J8" s="7">
-        <f t="shared" si="0"/>
-        <v>-14257414.039999992</v>
-      </c>
-      <c r="K8" s="20">
-        <f t="shared" si="1"/>
-        <v>-0.72453940771212477</v>
-      </c>
-    </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A9" s="17" t="s">
+      <c r="B10" s="17">
+        <v>0</v>
+      </c>
+      <c r="C10" s="17">
+        <v>0</v>
+      </c>
+      <c r="D10" s="18">
+        <v>0</v>
+      </c>
+      <c r="E10" s="26"/>
+      <c r="F10" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A11" s="16" t="s">
         <v>42</v>
       </c>
-      <c r="B9" s="18">
-        <v>0</v>
-      </c>
-      <c r="C9" s="18">
-        <v>155554762.09087223</v>
-      </c>
-      <c r="D9" s="19">
-        <v>0</v>
-      </c>
-      <c r="E9" s="32">
-        <v>0</v>
-      </c>
-      <c r="F9" s="18">
-        <v>8800000</v>
-      </c>
-      <c r="G9" s="18">
-        <v>191697428.13917199</v>
-      </c>
-      <c r="H9" s="19">
-        <v>4224000</v>
-      </c>
-      <c r="I9" s="32">
-        <v>2.2034724414421374E-2</v>
-      </c>
-      <c r="J9" s="7">
-        <f t="shared" si="0"/>
-        <v>4224000</v>
-      </c>
-      <c r="K9" s="20" t="e">
-        <f t="shared" si="1"/>
-        <v>#DIV/0!</v>
-      </c>
-    </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A10" s="17" t="s">
+      <c r="B11" s="17"/>
+      <c r="C11" s="17"/>
+      <c r="D11" s="18"/>
+      <c r="E11" s="26"/>
+      <c r="F11" s="7">
+        <v>-29552</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A12" s="16" t="s">
         <v>43</v>
       </c>
-      <c r="B10" s="18">
-        <v>1722908.62</v>
-      </c>
-      <c r="C10" s="18">
-        <v>47463483.036268912</v>
-      </c>
-      <c r="D10" s="19">
-        <v>441144.18000000017</v>
-      </c>
-      <c r="E10" s="32">
-        <v>9.2943912199385473E-3</v>
-      </c>
-      <c r="F10" s="18">
-        <v>0</v>
-      </c>
-      <c r="G10" s="18">
-        <v>0</v>
-      </c>
-      <c r="H10" s="19">
-        <v>0</v>
-      </c>
-      <c r="I10" s="32"/>
-      <c r="J10" s="7">
-        <f t="shared" si="0"/>
-        <v>-441144.18000000017</v>
-      </c>
-      <c r="K10" s="20">
-        <f t="shared" si="1"/>
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A11" s="17" t="s">
+      <c r="B12" s="17">
+        <v>0</v>
+      </c>
+      <c r="C12" s="17">
+        <v>22753403.933430597</v>
+      </c>
+      <c r="D12" s="18">
+        <v>0</v>
+      </c>
+      <c r="E12" s="26">
+        <v>0</v>
+      </c>
+      <c r="F12" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A13" s="19" t="s">
         <v>44</v>
       </c>
-      <c r="B11" s="18">
-        <v>0</v>
-      </c>
-      <c r="C11" s="18">
-        <v>0</v>
-      </c>
-      <c r="D11" s="19">
-        <v>0</v>
-      </c>
-      <c r="E11" s="32"/>
-      <c r="F11" s="18">
-        <v>0</v>
-      </c>
-      <c r="G11" s="18">
-        <v>0</v>
-      </c>
-      <c r="H11" s="19">
-        <v>0</v>
-      </c>
-      <c r="I11" s="32"/>
-      <c r="J11" s="7">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="K11" s="20" t="e">
-        <f t="shared" si="1"/>
-        <v>#DIV/0!</v>
-      </c>
-    </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A12" s="17" t="s">
-        <v>45</v>
-      </c>
-      <c r="B12" s="18">
-        <v>29552</v>
-      </c>
-      <c r="C12" s="18">
-        <v>0</v>
-      </c>
-      <c r="D12" s="19">
-        <v>29552</v>
-      </c>
-      <c r="E12" s="32"/>
-      <c r="F12" s="18"/>
-      <c r="G12" s="18"/>
-      <c r="H12" s="19"/>
-      <c r="I12" s="32"/>
-      <c r="J12" s="7">
-        <f t="shared" si="0"/>
-        <v>-29552</v>
-      </c>
-      <c r="K12" s="20">
-        <f t="shared" si="1"/>
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A13" s="17" t="s">
-        <v>46</v>
-      </c>
-      <c r="B13" s="18"/>
-      <c r="C13" s="18"/>
-      <c r="D13" s="19"/>
-      <c r="E13" s="32"/>
-      <c r="F13" s="18">
-        <v>0</v>
-      </c>
-      <c r="G13" s="18">
-        <v>22753403.933430597</v>
-      </c>
-      <c r="H13" s="19">
-        <v>0</v>
-      </c>
-      <c r="I13" s="32">
-        <v>0</v>
-      </c>
-      <c r="J13" s="7">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="K13" s="20" t="e">
-        <f t="shared" si="1"/>
-        <v>#DIV/0!</v>
-      </c>
-    </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A14" s="21" t="s">
-        <v>47</v>
-      </c>
-      <c r="B14" s="22">
-        <v>478777711.24000001</v>
-      </c>
-      <c r="C14" s="22">
-        <v>774914008.75536704</v>
-      </c>
-      <c r="D14" s="23">
-        <v>92845107.270000041</v>
-      </c>
-      <c r="E14" s="33">
-        <v>0.11981343248539765</v>
-      </c>
-      <c r="F14" s="22">
+      <c r="B13" s="20">
         <v>770409514.34000003</v>
       </c>
-      <c r="G14" s="22">
+      <c r="C13" s="20">
         <v>872213817.44821835</v>
       </c>
-      <c r="H14" s="23">
+      <c r="D13" s="21">
         <v>333312647.79000002</v>
       </c>
-      <c r="I14" s="33">
+      <c r="E13" s="27">
         <v>0.38214557155853374</v>
       </c>
-      <c r="J14" s="24">
-        <f t="shared" si="0"/>
+      <c r="F13" s="22">
         <v>240467540.51999998</v>
       </c>
-      <c r="K14" s="25">
-        <f t="shared" si="1"/>
-        <v>2.5899861348719608</v>
-      </c>
     </row>
   </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="B1:E1"/>
-    <mergeCell ref="F1:I1"/>
-  </mergeCells>
-  <conditionalFormatting sqref="E4:E14">
-    <cfRule type="colorScale" priority="2">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FFF8696B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FF63BE7B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="I4:I14">
+  <conditionalFormatting sqref="E3:E13">
     <cfRule type="colorScale" priority="1">
       <colorScale>
         <cfvo type="min"/>
@@ -1899,525 +1603,258 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{120C2AAA-1B62-49E5-A9DB-A8B675BAA0E0}">
-  <dimension ref="A1:L15"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <dimension ref="A1:F13"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="29.54296875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="19" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.36328125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="9.90625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="6.7265625" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="12.36328125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="9.90625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="7.7265625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="11.54296875" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="9.36328125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="29.5546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="3" width="12.33203125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9.88671875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="7.77734375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="11.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A1" s="36"/>
-      <c r="B1" s="36" t="s">
-        <v>48</v>
-      </c>
-      <c r="C1" s="36"/>
-      <c r="D1" s="36"/>
-      <c r="E1" s="36"/>
-      <c r="F1" s="36"/>
-      <c r="G1" s="36"/>
-      <c r="H1" s="36"/>
-      <c r="I1" s="36"/>
-      <c r="J1" s="39"/>
-      <c r="K1" s="39"/>
-      <c r="L1" s="39"/>
-    </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A2" s="36"/>
-      <c r="B2" s="37" t="s">
+    <row r="1" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A1" s="28" t="s">
         <v>29</v>
       </c>
-      <c r="C2" s="38"/>
-      <c r="D2" s="38"/>
-      <c r="E2" s="38"/>
-      <c r="F2" s="37" t="s">
+      <c r="B1" s="29" t="s">
         <v>30</v>
       </c>
-      <c r="G2" s="38"/>
-      <c r="H2" s="38"/>
-      <c r="I2" s="38"/>
-      <c r="J2" s="39"/>
-      <c r="K2" s="39"/>
-      <c r="L2" s="39"/>
-    </row>
-    <row r="3" spans="1:12" ht="29" x14ac:dyDescent="0.35">
-      <c r="A3" s="36" t="s">
+      <c r="C1" s="29" t="s">
+        <v>3</v>
+      </c>
+      <c r="D1" s="29" t="s">
+        <v>4</v>
+      </c>
+      <c r="E1" s="29" t="s">
         <v>31</v>
       </c>
-      <c r="B3" s="40" t="s">
+      <c r="F1" s="30" t="s">
         <v>32</v>
       </c>
-      <c r="C3" s="40" t="s">
-        <v>3</v>
-      </c>
-      <c r="D3" s="40" t="s">
-        <v>4</v>
-      </c>
-      <c r="E3" s="40" t="s">
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A2" s="11" t="s">
         <v>33</v>
       </c>
-      <c r="F3" s="40" t="s">
-        <v>32</v>
-      </c>
-      <c r="G3" s="40" t="s">
-        <v>3</v>
-      </c>
-      <c r="H3" s="40" t="s">
-        <v>4</v>
-      </c>
-      <c r="I3" s="40" t="s">
-        <v>33</v>
-      </c>
-      <c r="J3" s="44" t="s">
+      <c r="B2" s="12"/>
+      <c r="C2" s="12"/>
+      <c r="D2" s="13"/>
+      <c r="E2" s="14"/>
+      <c r="F2" s="15"/>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A3" s="16" t="s">
+        <v>36</v>
+      </c>
+      <c r="B3" s="17">
+        <v>293567149.97000003</v>
+      </c>
+      <c r="C3" s="17">
+        <v>91800842.878753603</v>
+      </c>
+      <c r="D3" s="18">
+        <v>30823146.090000033</v>
+      </c>
+      <c r="E3" s="4">
+        <v>0.335761035775127</v>
+      </c>
+      <c r="F3" s="7">
+        <v>-21417780.599999785</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A4" s="16" t="s">
+        <v>39</v>
+      </c>
+      <c r="B4" s="17">
+        <v>144640230.25</v>
+      </c>
+      <c r="C4" s="17">
+        <v>83577281.896116406</v>
+      </c>
+      <c r="D4" s="18">
+        <v>13594203.789999992</v>
+      </c>
+      <c r="E4" s="4">
+        <v>0.16265429410467203</v>
+      </c>
+      <c r="F4" s="7">
+        <v>-4347053.7900000513</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A5" s="16" t="s">
+        <v>35</v>
+      </c>
+      <c r="B5" s="17">
+        <v>36181684.129999995</v>
+      </c>
+      <c r="C5" s="17">
+        <v>50069339.384766802</v>
+      </c>
+      <c r="D5" s="18">
+        <v>6397684.1299999952</v>
+      </c>
+      <c r="E5" s="4">
+        <v>0.12777648374458972</v>
+      </c>
+      <c r="F5" s="7">
+        <v>6221663.6899999958</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A6" s="16" t="s">
+        <v>38</v>
+      </c>
+      <c r="B6" s="17">
+        <v>11296680</v>
+      </c>
+      <c r="C6" s="17">
+        <v>36043152.510621198</v>
+      </c>
+      <c r="D6" s="18">
+        <v>1920440</v>
+      </c>
+      <c r="E6" s="4">
+        <v>5.3281687816682646E-2</v>
+      </c>
+      <c r="F6" s="7">
+        <v>-4542858.4300000072</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A7" s="16" t="s">
+        <v>43</v>
+      </c>
+      <c r="B7" s="17">
+        <v>0</v>
+      </c>
+      <c r="C7" s="17">
+        <v>3555219.3645986998</v>
+      </c>
+      <c r="D7" s="18">
+        <v>0</v>
+      </c>
+      <c r="E7" s="4">
+        <v>0</v>
+      </c>
+      <c r="F7" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A8" s="16" t="s">
+        <v>42</v>
+      </c>
+      <c r="B8" s="17"/>
+      <c r="C8" s="17"/>
+      <c r="D8" s="18"/>
+      <c r="E8" s="4"/>
+      <c r="F8" s="7">
+        <v>-118905</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A9" s="16" t="s">
         <v>34</v>
       </c>
-      <c r="K3" s="45" t="s">
-        <v>35</v>
-      </c>
-      <c r="L3" s="45" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A4" s="54" t="s">
-        <v>36</v>
-      </c>
-      <c r="B4" s="55"/>
-      <c r="C4" s="55"/>
-      <c r="D4" s="56"/>
-      <c r="E4" s="60"/>
-      <c r="F4" s="55"/>
-      <c r="G4" s="55"/>
-      <c r="H4" s="56"/>
-      <c r="I4" s="60"/>
-      <c r="J4" s="57"/>
-      <c r="K4" s="58"/>
-      <c r="L4" s="58"/>
-    </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A5" s="47" t="s">
-        <v>39</v>
-      </c>
-      <c r="B5" s="41">
-        <v>739925955.98999989</v>
-      </c>
-      <c r="C5" s="41">
-        <v>116712575.07946891</v>
-      </c>
-      <c r="D5" s="43">
-        <v>52240926.689999819</v>
-      </c>
-      <c r="E5" s="42">
-        <v>0.44760323944895797</v>
-      </c>
-      <c r="F5" s="41">
-        <v>293567149.97000003</v>
-      </c>
-      <c r="G5" s="41">
-        <v>91800842.878753603</v>
-      </c>
-      <c r="H5" s="43">
-        <v>30823146.090000033</v>
-      </c>
-      <c r="I5" s="42">
-        <v>0.335761035775127</v>
-      </c>
-      <c r="J5" s="46">
-        <v>-21417780.599999785</v>
-      </c>
-      <c r="K5" s="48">
-        <v>-0.40998087049821935</v>
-      </c>
-      <c r="L5" s="48">
-        <v>0.57402412453272655</v>
-      </c>
-    </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A6" s="47" t="s">
-        <v>42</v>
-      </c>
-      <c r="B6" s="41">
-        <v>225036765.16000003</v>
-      </c>
-      <c r="C6" s="41">
-        <v>96089866.55070281</v>
-      </c>
-      <c r="D6" s="43">
-        <v>17941257.580000043</v>
-      </c>
-      <c r="E6" s="42">
-        <v>0.18671331560787535</v>
-      </c>
-      <c r="F6" s="41">
-        <v>144640230.25</v>
-      </c>
-      <c r="G6" s="41">
-        <v>83577281.896116406</v>
-      </c>
-      <c r="H6" s="43">
-        <v>13594203.789999992</v>
-      </c>
-      <c r="I6" s="42">
-        <v>0.16265429410467203</v>
-      </c>
-      <c r="J6" s="46">
-        <v>-4347053.7900000513</v>
-      </c>
-      <c r="K6" s="48">
-        <v>-0.2422937060357416</v>
-      </c>
-      <c r="L6" s="48">
-        <v>0.25316691899292787</v>
-      </c>
-    </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A7" s="47" t="s">
-        <v>38</v>
-      </c>
-      <c r="B7" s="41">
-        <v>2577961.44</v>
-      </c>
-      <c r="C7" s="41">
-        <v>48743897.797445603</v>
-      </c>
-      <c r="D7" s="43">
-        <v>176020.43999999994</v>
-      </c>
-      <c r="E7" s="42">
-        <v>3.6111277093893845E-3</v>
-      </c>
-      <c r="F7" s="41">
-        <v>36181684.129999995</v>
-      </c>
-      <c r="G7" s="41">
-        <v>50069339.384766802</v>
-      </c>
-      <c r="H7" s="43">
-        <v>6397684.1299999952</v>
-      </c>
-      <c r="I7" s="42">
-        <v>0.12777648374458972</v>
-      </c>
-      <c r="J7" s="46">
-        <v>6221663.6899999958</v>
-      </c>
-      <c r="K7" s="48">
-        <v>35.346256889256715</v>
-      </c>
-      <c r="L7" s="48">
-        <v>0.11914504187979735</v>
-      </c>
-    </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A8" s="47" t="s">
+      <c r="B9" s="17">
+        <v>0</v>
+      </c>
+      <c r="C9" s="17">
+        <v>75417206.973561406</v>
+      </c>
+      <c r="D9" s="18">
+        <v>0</v>
+      </c>
+      <c r="E9" s="4">
+        <v>0</v>
+      </c>
+      <c r="F9" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A10" s="16" t="s">
+        <v>40</v>
+      </c>
+      <c r="B10" s="17">
+        <v>0</v>
+      </c>
+      <c r="C10" s="17">
+        <v>0</v>
+      </c>
+      <c r="D10" s="18">
+        <v>0</v>
+      </c>
+      <c r="E10" s="4"/>
+      <c r="F10" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A11" s="16" t="s">
         <v>41</v>
       </c>
-      <c r="B8" s="41">
-        <v>286279133.75999999</v>
-      </c>
-      <c r="C8" s="41">
-        <v>32570651.823400989</v>
-      </c>
-      <c r="D8" s="43">
-        <v>6463298.4300000072</v>
-      </c>
-      <c r="E8" s="42">
-        <v>0.19843933320844145</v>
-      </c>
-      <c r="F8" s="41">
-        <v>11296680</v>
-      </c>
-      <c r="G8" s="41">
-        <v>36043152.510621198</v>
-      </c>
-      <c r="H8" s="43">
-        <v>1920440</v>
-      </c>
-      <c r="I8" s="42">
-        <v>5.3281687816682646E-2</v>
-      </c>
-      <c r="J8" s="46">
-        <v>-4542858.4300000072</v>
-      </c>
-      <c r="K8" s="48">
-        <v>-0.70286997872694579</v>
-      </c>
-      <c r="L8" s="48">
-        <v>3.5764645390149667E-2</v>
-      </c>
-    </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A9" s="47" t="s">
-        <v>46</v>
-      </c>
-      <c r="B9" s="41"/>
-      <c r="C9" s="41"/>
-      <c r="D9" s="43"/>
-      <c r="E9" s="42"/>
-      <c r="F9" s="41">
-        <v>0</v>
-      </c>
-      <c r="G9" s="41">
-        <v>3555219.3645986998</v>
-      </c>
-      <c r="H9" s="43">
-        <v>0</v>
-      </c>
-      <c r="I9" s="42">
-        <v>0</v>
-      </c>
-      <c r="J9" s="46">
-        <v>0</v>
-      </c>
-      <c r="K9" s="48" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="L9" s="48">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A10" s="47" t="s">
-        <v>45</v>
-      </c>
-      <c r="B10" s="41">
-        <v>885906</v>
-      </c>
-      <c r="C10" s="41">
-        <v>0</v>
-      </c>
-      <c r="D10" s="43">
-        <v>118905</v>
-      </c>
-      <c r="E10" s="42"/>
-      <c r="F10" s="41"/>
-      <c r="G10" s="41"/>
-      <c r="H10" s="43"/>
-      <c r="I10" s="42"/>
-      <c r="J10" s="46">
-        <v>-118905</v>
-      </c>
-      <c r="K10" s="48">
-        <v>-1</v>
-      </c>
-      <c r="L10" s="48">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A11" s="47" t="s">
+      <c r="B11" s="17">
+        <v>0</v>
+      </c>
+      <c r="C11" s="17">
+        <v>34494092.644621998</v>
+      </c>
+      <c r="D11" s="18">
+        <v>0</v>
+      </c>
+      <c r="E11" s="4">
+        <v>0</v>
+      </c>
+      <c r="F11" s="7">
+        <v>-2334000</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A12" s="16" t="s">
         <v>37</v>
       </c>
-      <c r="B11" s="41">
-        <v>0</v>
-      </c>
-      <c r="C11" s="41">
-        <v>24949068.102458403</v>
-      </c>
-      <c r="D11" s="43">
-        <v>0</v>
-      </c>
-      <c r="E11" s="42">
-        <v>0</v>
-      </c>
-      <c r="F11" s="41">
-        <v>0</v>
-      </c>
-      <c r="G11" s="41">
-        <v>75417206.973561406</v>
-      </c>
-      <c r="H11" s="43">
-        <v>0</v>
-      </c>
-      <c r="I11" s="42">
-        <v>0</v>
-      </c>
-      <c r="J11" s="46">
-        <v>0</v>
-      </c>
-      <c r="K11" s="48" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="L11" s="48">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A12" s="47" t="s">
-        <v>43</v>
-      </c>
-      <c r="B12" s="41">
-        <v>0</v>
-      </c>
-      <c r="C12" s="41">
-        <v>7612558.1418069005</v>
-      </c>
-      <c r="D12" s="43">
-        <v>0</v>
-      </c>
-      <c r="E12" s="42">
-        <v>0</v>
-      </c>
-      <c r="F12" s="41">
-        <v>0</v>
-      </c>
-      <c r="G12" s="41">
-        <v>0</v>
-      </c>
-      <c r="H12" s="43">
-        <v>0</v>
-      </c>
-      <c r="I12" s="42"/>
-      <c r="J12" s="46">
-        <v>0</v>
-      </c>
-      <c r="K12" s="48" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="L12" s="48">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A13" s="47" t="s">
+      <c r="B12" s="17">
+        <v>5870410.8700000001</v>
+      </c>
+      <c r="C12" s="17">
+        <v>16709531.013613399</v>
+      </c>
+      <c r="D12" s="18">
+        <v>961129.96999999974</v>
+      </c>
+      <c r="E12" s="4">
+        <v>5.7519865112728726E-2</v>
+      </c>
+      <c r="F12" s="7">
+        <v>409739.12999999989</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A13" s="19" t="s">
         <v>44</v>
       </c>
-      <c r="B13" s="41">
-        <v>15020000</v>
-      </c>
-      <c r="C13" s="41">
-        <v>35954356.238271199</v>
-      </c>
-      <c r="D13" s="43">
-        <v>2334000</v>
-      </c>
-      <c r="E13" s="42">
-        <v>6.4915638720728946E-2</v>
-      </c>
-      <c r="F13" s="41">
-        <v>0</v>
-      </c>
-      <c r="G13" s="41">
-        <v>34494092.644621998</v>
-      </c>
-      <c r="H13" s="43">
-        <v>0</v>
-      </c>
-      <c r="I13" s="42">
-        <v>0</v>
-      </c>
-      <c r="J13" s="46">
-        <v>-2334000</v>
-      </c>
-      <c r="K13" s="48">
-        <v>-1</v>
-      </c>
-      <c r="L13" s="48">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A14" s="47" t="s">
-        <v>40</v>
-      </c>
-      <c r="B14" s="41">
-        <v>4378709.21</v>
-      </c>
-      <c r="C14" s="41">
-        <v>15908692.933081001</v>
-      </c>
-      <c r="D14" s="43">
-        <v>551390.83999999985</v>
-      </c>
-      <c r="E14" s="42">
-        <v>3.4659719834897428E-2</v>
-      </c>
-      <c r="F14" s="41">
-        <v>5870410.8700000001</v>
-      </c>
-      <c r="G14" s="41">
-        <v>16709531.013613399</v>
-      </c>
-      <c r="H14" s="43">
-        <v>961129.96999999974</v>
-      </c>
-      <c r="I14" s="42">
-        <v>5.7519865112728726E-2</v>
-      </c>
-      <c r="J14" s="46">
-        <v>409739.12999999989</v>
-      </c>
-      <c r="K14" s="48">
-        <v>0.74310108234659833</v>
-      </c>
-      <c r="L14" s="48">
-        <v>1.7899269204398563E-2</v>
-      </c>
-    </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A15" s="49" t="s">
-        <v>47</v>
-      </c>
-      <c r="B15" s="50">
-        <v>1274104431.5599999</v>
-      </c>
-      <c r="C15" s="50">
-        <v>378541666.66663581</v>
-      </c>
-      <c r="D15" s="51">
-        <v>79825798.980000019</v>
-      </c>
-      <c r="E15" s="59">
-        <v>0.21087717947387521</v>
-      </c>
-      <c r="F15" s="50">
+      <c r="B13" s="20">
         <v>491556155.22000003</v>
       </c>
-      <c r="G15" s="50">
+      <c r="C13" s="20">
         <v>391666666.66665351</v>
       </c>
-      <c r="H15" s="51">
+      <c r="D13" s="21">
         <v>53696603.980000019</v>
       </c>
-      <c r="I15" s="59">
+      <c r="E13" s="31">
         <v>0.13709771228936629</v>
       </c>
-      <c r="J15" s="52">
+      <c r="F13" s="22">
         <v>-26129195</v>
       </c>
-      <c r="K15" s="53">
-        <v>-0.32732769773524656</v>
-      </c>
-      <c r="L15" s="53">
-        <v>1</v>
-      </c>
     </row>
   </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="B2:E2"/>
-    <mergeCell ref="F2:I2"/>
-  </mergeCells>
-  <conditionalFormatting sqref="E4:E14">
-    <cfRule type="colorScale" priority="2">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FFF8696B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FF63BE7B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="I4:I14">
+  <conditionalFormatting sqref="E2:E12">
     <cfRule type="colorScale" priority="1">
       <colorScale>
         <cfvo type="min"/>
